--- a/tools/Translations/slowniczek.xlsx
+++ b/tools/Translations/slowniczek.xlsx
@@ -4,9 +4,10 @@
   <sheets>
     <sheet name="Słowniczek" sheetId="1" r:id="rId1"/>
     <sheet name="Jak czytać" sheetId="2" r:id="rId2"/>
+    <sheet name="Zasady językowe" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Słowniczek'!$A$1:$M$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Słowniczek'!$A$1:$M$115</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -335,12 +336,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Una historia de una pequeña aldea olvidada llamada</t>
+          <t xml:space="preserve">Historia de una pequeña aldea olvidada llamada</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma história de uma pequena aldeia esquecida chamada</t>
+          <t xml:space="preserve">História de uma pequena aldeia esquecida chamada</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -474,7 +475,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouxa</t>
+          <t xml:space="preserve">Bornal</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -789,7 +790,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bohater. W czeskim i słowackim odmieniać według gramatyki (Jaromira, Jaromirovi).</t>
+          <t xml:space="preserve">Bohater. Pisownia zawsze „Jaromir” (także w cs, choć czeskie imię to „Jaromír” — nie dodawać kreski). cs: Jaromira, Jaromirovi, Jaromirem, wołacz „Jaromire!”; sk: Jaromira, Jaromirovi, Jaromirom, wołacz = mianownik. de: dopełniacz „Jaromirs”. Wołacz „Jaromirze!” w pozostałych językach = „Jaromir!”.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -856,7 +857,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zawsze forma podstawowa (bez „Hanko!”).</t>
+          <t xml:space="preserve">W językach bez wołacza zawsze „Hanka”. cs: odmiana Hanka – Hanky – Hance – Hanku – Hankou, wołacz „Hanko!” (po czesku naturalny i wymagany); sk: Hanky – Hanke – Hanku – Hankou, bez wołacza.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -923,7 +924,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zdrobnienie od Maria — wyjaśnić raz przy chrzcie, potem tylko „Marysia”. Wołacz „Marysiu!” → „Marysia!”.</t>
+          <t xml:space="preserve">Zdrobnienie od Maria — wyjaśnić raz przy chrzcie, potem tylko „Marysia”. Wołacz „Marysiu!” → „Marysia!” (en, de, es, pt, fr, it, sk), ja „マリシャ！”. cs: wołacz i odmiana do decyzji natywnego tłumacza (propozycja: Marysie – Marysii – Marysii – Marysio!); dzierżawcze cs/sk („Marysiny/Marysine”) do sprawdzenia — wzór od imion na -ia daje „Marysiin/Marysiina”, bezpieczniej użyć dopełniacza („dřeváky Marysie”).</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1124,7 +1125,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imię zostaje, „dziadek” tłumaczyć. Zawsze „Maciek” (nie „Maćka”).</t>
+          <t xml:space="preserve">Imię zostaje, „dziadek” tłumaczyć. W językach bez odmiany zawsze „Maciek” (nigdy polskie „Maćka/Maćkiem”). cs: Maciek – Maćka – Maćkovi – Maćkem; sk: Maciek – Maćka – Maćkovi – Maćkom (tak już jest w tytułach). de: „Großvater Macieks Axt”. Wołacz „dziadku!”: en „Grandfather!”, de „Großvater!”, es „¡abuelo!”, pt „vovô!”, fr „grand-père !”, it „nonno!”, cs „dědečku!”, sk „dedko!”. „Dziadku” mówi się też do obcych starców (Jaromir do Stasia, dziewczynka do starego Jaromira) — tłumaczyć tym samym słowem.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1325,7 +1326,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">„stary” tłumaczyć.</t>
+          <t xml:space="preserve">„stary” tłumaczyć. de: dopełniacz bez -s — „des alten Staś”, „Staś’ Hof” (apostrof). en: „old Staś’s”. cs/sk: zapis „Staš” (decyzja autora) — cs Staš – Staše – Stašovi – Stašem, wołacz „Staši!”, „u Stašových”; sk Staš – Staša – Stašovi – Stašom, „u Stašovcov”.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1360,17 +1361,17 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">starý Staś</t>
+          <t xml:space="preserve">starý Staš</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">starý Staś</t>
+          <t xml:space="preserve">starý Staš</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">スタシ爺</t>
+          <t xml:space="preserve">スタシじいさん</t>
         </is>
       </c>
     </row>
@@ -1392,47 +1393,47 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodzina Stasia.</t>
+          <t xml:space="preserve">Domownicy starego Stasia (w tekście „u Stasiowych” = w zagrodzie Stasia). Staś to imię, nie nazwisko — nie tworzyć od niego liczby mnogiej jak od nazwiska.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Staś family</t>
+          <t xml:space="preserve">Staś’s family</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Staśs</t>
+          <t xml:space="preserve">die Familie des alten Staś</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">los Staś</t>
+          <t xml:space="preserve">los de Staś</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">os Staś</t>
+          <t xml:space="preserve">a família de Staś</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">les Staś</t>
+          <t xml:space="preserve">ceux de chez Staś</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gli Staś</t>
+          <t xml:space="preserve">quelli di Staś</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stasiovi</t>
+          <t xml:space="preserve">Stašovi</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stasiovci</t>
+          <t xml:space="preserve">Stašovci</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1695,7 +1696,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaśka Wójcikova</t>
+          <t xml:space="preserve">Kaśka Wójciková</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -1772,7 +1773,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヴイチク爺 / ヴイチクのおかみ</t>
+          <t xml:space="preserve">ヴイチクじいさん / ヴイチクのおかみさん</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1795,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nauczyciel; „pan” = grzecznościowy tytuł.</t>
+          <t xml:space="preserve">Nauczyciel; „pan” = grzecznościowy tytuł. en „Mr Ignacy” („Master” + imię = panicz). cs: pana Ignacyho, panu Ignacymu, s panem Ignacym (odmiana przymiotnikowa jak „Jerzy – Jerzyho”); sk: pána Ignacyho, pánovi Ignacymu, s pánom Ignacym. „Księga pana Ignacego” → en „Mr Ignacy’s book”, de „Herrn Ignacys Buch”.</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Ignacy</t>
+          <t xml:space="preserve">Mr Ignacy</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1906,7 +1907,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウルバニャク旦那</t>
+          <t xml:space="preserve">ウルバニャクの旦那</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2182,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miejsca</t>
+          <t xml:space="preserve">Postacie</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">gajowy Pawlik</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2196,52 +2197,52 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wieś bohaterów. Brzmi jak prawdziwa miejscowość — nie tłumaczyć.</t>
+          <t xml:space="preserve">Leśniczy z dubeltówką przy obławie na wilka. Imię zostaje, „gajowy” tłumaczyć.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">Pawlik the gamekeeper</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">der Förster Pawlik</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">el guardabosques Pawlik</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">o guarda-florestal Pawlik</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">le garde-forestier Pawlik</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">il guardaboschi Pawlik</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">hajný Pawlik</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">horár Pawlik</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ザパドリナ</t>
+          <t xml:space="preserve">森番のパヴリク</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2254,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2263,52 +2264,52 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wieś z kościołem i targiem.</t>
+          <t xml:space="preserve">Wieś bohaterów. Brzmi jak prawdziwa miejscowość — nie tłumaczyć.</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ブコヴィエツ</t>
+          <t xml:space="preserve">ザパドリナ</t>
         </is>
       </c>
     </row>
@@ -2320,62 +2321,62 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowy Grzbiet</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nazwa opisowa — tłumaczyć.</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Beech Ridge</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Buchenkamm</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la Cresta de las Hayas</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Serra das Faias</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la Crête des Hêtres</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la Cresta dei Faggi</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bukový hřbet</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bukový hrebeň</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ブナの尾根</t>
+          <t xml:space="preserve">Wieś z kościołem i targiem.</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ブコヴィエツ</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2388,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stary Dąb</t>
+          <t xml:space="preserve">Bukowy Grzbiet</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2397,52 +2398,52 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konkretne drzewo — wielkimi literami.</t>
+          <t xml:space="preserve">Nazwa opisowa — tłumaczyć.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Old Oak</t>
+          <t xml:space="preserve">Beech Ridge</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Alte Eiche</t>
+          <t xml:space="preserve">Buchenkamm</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el Viejo Roble</t>
+          <t xml:space="preserve">la Cresta de las Hayas</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o Velho Carvalho</t>
+          <t xml:space="preserve">a Serra das Faias</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le Vieux Chêne</t>
+          <t xml:space="preserve">la Crête des Hêtres</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Vecchia Quercia</t>
+          <t xml:space="preserve">la Cresta dei Faggi</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starý dub</t>
+          <t xml:space="preserve">Bukový hřbet</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starý dub</t>
+          <t xml:space="preserve">Bukový hrebeň</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">老樫</t>
+          <t xml:space="preserve">ブナの尾根</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2455,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bór</t>
+          <t xml:space="preserve">Stary Dąb</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2464,52 +2465,52 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stary, ciemny las iglasty — zawsze ten sam wyraz w całej grze.</t>
+          <t xml:space="preserve">Konkretne drzewo — wielkimi literami.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the forest</t>
+          <t xml:space="preserve">the Old Oak</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Wald</t>
+          <t xml:space="preserve">die Alte Eiche</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el bosque</t>
+          <t xml:space="preserve">el Viejo Roble</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a floresta</t>
+          <t xml:space="preserve">o Velho Carvalho</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la forêt</t>
+          <t xml:space="preserve">le Vieux Chêne</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il bosco</t>
+          <t xml:space="preserve">la Vecchia Quercia</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bor</t>
+          <t xml:space="preserve">Starý dub</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bór</t>
+          <t xml:space="preserve">Starý dub</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">森</t>
+          <t xml:space="preserve">老樫</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2522,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">baza na starym bzie</t>
+          <t xml:space="preserve">bór</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2531,52 +2532,52 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kryjówka chłopców w dziupli starego bzu.</t>
+          <t xml:space="preserve">Stary, ciemny las iglasty — zawsze ten sam wyraz w całej grze.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the den in the old elder</t>
+          <t xml:space="preserve">the forest</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">das Versteck im alten Holunder</t>
+          <t xml:space="preserve">der Wald</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la guarida del viejo saúco</t>
+          <t xml:space="preserve">el bosque</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o esconderijo no velho sabugueiro</t>
+          <t xml:space="preserve">a floresta</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la cabane du vieux sureau</t>
+          <t xml:space="preserve">la forêt</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il rifugio nel vecchio sambuco</t>
+          <t xml:space="preserve">il bosco</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">skrýš ve starém bezu</t>
+          <t xml:space="preserve">bor</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">skrýša v starom baze</t>
+          <t xml:space="preserve">bór</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">古いニワトコの隠れ家</t>
+          <t xml:space="preserve">森</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2589,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">młodnik</t>
+          <t xml:space="preserve">baza na starym bzie</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2598,64 +2599,64 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Młody las pod borem.</t>
+          <t xml:space="preserve">Kryjówka chłopców w dziupli starego bzu.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the young wood</t>
+          <t xml:space="preserve">the den in the old elder</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">das Jungholz</t>
+          <t xml:space="preserve">das Versteck im alten Holunder</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el monte joven</t>
+          <t xml:space="preserve">la guarida del viejo saúco</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o mato novo</t>
+          <t xml:space="preserve">o esconderijo no velho sabugueiro</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le jeune bois</t>
+          <t xml:space="preserve">la cabane du vieux sureau</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il bosco giovane</t>
+          <t xml:space="preserve">il rifugio nel vecchio sambuco</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mlází</t>
+          <t xml:space="preserve">skrýš ve starém bezu</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mladina</t>
+          <t xml:space="preserve">skrýša v starom baze</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">若木の林</t>
+          <t xml:space="preserve">古いニワトコの隠れ家</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Istoty</t>
+          <t xml:space="preserve">Miejsca</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan Lasu</t>
+          <t xml:space="preserve">młodnik</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2665,52 +2666,52 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leszy. Zawsze wielkimi literami.</t>
+          <t xml:space="preserve">Młody las pod borem.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Lord of the Forest</t>
+          <t xml:space="preserve">the young wood</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Herr des Waldes</t>
+          <t xml:space="preserve">das Jungholz</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el Señor del Bosque</t>
+          <t xml:space="preserve">el monte joven</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o Senhor da Floresta</t>
+          <t xml:space="preserve">o mato novo</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le Seigneur de la Forêt</t>
+          <t xml:space="preserve">le jeune bois</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il Signore del Bosco</t>
+          <t xml:space="preserve">il bosco giovane</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pán lesa</t>
+          <t xml:space="preserve">mlází</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pán lesa</t>
+          <t xml:space="preserve">mladina</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">森の主</t>
+          <t xml:space="preserve">若木の林</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2723,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starzec w kapeluszu z mchu</t>
+          <t xml:space="preserve">Pan Lasu</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2732,52 +2733,52 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ludzka postać Pana Lasu.</t>
+          <t xml:space="preserve">Leszy. Zawsze wielkimi literami.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Old Man in the Moss Hat</t>
+          <t xml:space="preserve">the Lord of the Forest</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Alte mit dem Moosshut</t>
+          <t xml:space="preserve">der Herr des Waldes</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el Viejo del Sombrero de Musgo</t>
+          <t xml:space="preserve">el Señor del Bosque</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o Velho do Chapéu de Musgo</t>
+          <t xml:space="preserve">o Senhor da Floresta</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le Vieillard au chapeau de mousse</t>
+          <t xml:space="preserve">le Seigneur de la Forêt</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il Vecchio dal cappello di muschio</t>
+          <t xml:space="preserve">il Signore del Bosco</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stařec v klobouku z mechu</t>
+          <t xml:space="preserve">Pán lesa</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starec v klobúku z machu</t>
+          <t xml:space="preserve">Pán lesa</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">苔の帽子の老人</t>
+          <t xml:space="preserve">森の主</t>
         </is>
       </c>
     </row>
@@ -2789,62 +2790,62 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topielec</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Utopiony trup z bagna. W niemieckim tradycyjny odpowiednik.</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the Drowner</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">der Wassermann</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el Ahogado</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o Afogado</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">le Noyé</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">l’Annegato</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">utopenec</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">utopenec</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水死霊</t>
+          <t xml:space="preserve">Drugie, ludowe imię Pana Lasu (od „bór”), w tekście 7×, zawsze obok „Pan Lasu” jako ta sama istota. Wielką literą. cs/sk rodzimy przymiotnik „Borový” (odmiana: Borového, Borovému).</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borový</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borový</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ボロヴィ</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2857,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stwór z zarośli</t>
+          <t xml:space="preserve">Starzec w kapeluszu z mchu</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2866,52 +2867,52 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Ludzka postać Pana Lasu.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Thing in the Thicket</t>
+          <t xml:space="preserve">the Old Man in the Moss Hat</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">das Wesen aus dem Dickicht</t>
+          <t xml:space="preserve">der Alte mit dem Moosshut</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Criatura de la maleza</t>
+          <t xml:space="preserve">el viejo del sombrero de musgo</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Criatura do matagal</t>
+          <t xml:space="preserve">o velho do chapéu de musgo</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Créature des fourrés</t>
+          <t xml:space="preserve">le Vieillard au chapeau de mousse</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Creatura della boscaglia</t>
+          <t xml:space="preserve">il vecchio dal cappello di muschio</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stvůra z houští</t>
+          <t xml:space="preserve">Stařec v klobouku z mechu</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stvora z húštiny</t>
+          <t xml:space="preserve">Starec v klobúku z machu</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">藪の怪物</t>
+          <t xml:space="preserve">苔の帽子の老人</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2924,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zielarka znad jeziora</t>
+          <t xml:space="preserve">Topielec</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2933,52 +2934,52 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wiedźma, od której zaczęła się klątwa.</t>
+          <t xml:space="preserve">Stwór z bagna, dusza utopionego bez księdza; we śnie przewraca gliniane garnki (motyw wodnika). W niemieckim tradycyjny odpowiednik (Wassermann — on też trzyma dusze pod garnkami); w czeskim ludowy śląsko-morawski „utopec” (decyzja autora). Uwaga: w prologu „topielce uwięzione pod mułem” to ogólnie utopieni — tam de „die Ertrunkenen”, en „the drowned”, cs „utopenci”. W prozie małą literą.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Herbwoman from the Lake</t>
+          <t xml:space="preserve">the Drowned One</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Kräuterfrau vom See</t>
+          <t xml:space="preserve">der Wassermann</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Herbolaria del lago</t>
+          <t xml:space="preserve">el Ahogado</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Erveira do lago</t>
+          <t xml:space="preserve">o Afogado</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">l’Herboriste du lac</t>
+          <t xml:space="preserve">le Noyé</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">l’Erborista del lago</t>
+          <t xml:space="preserve">l’Annegato</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bylinkářka od jezera</t>
+          <t xml:space="preserve">utopec</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bylinkárka od jazera</t>
+          <t xml:space="preserve">utopenec</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">湖畔の薬草女</t>
+          <t xml:space="preserve">水死霊</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2991,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Południca</t>
+          <t xml:space="preserve">Stwór z zarośli</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3000,52 +3001,52 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">W czeskim i słowackim istnieje ta sama istota ludowa.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lady Midday</t>
+          <t xml:space="preserve">the Thing in the Thicket</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Mittagsfrau</t>
+          <t xml:space="preserve">das Wesen aus dem Dickicht</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Dama del Mediodía</t>
+          <t xml:space="preserve">la Criatura de la maleza</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Dama do Meio-Dia</t>
+          <t xml:space="preserve">a Criatura do matagal</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Dame de Midi</t>
+          <t xml:space="preserve">la Créature des fourrés</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Signora del Mezzogiorno</t>
+          <t xml:space="preserve">la Creatura della boscaglia</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">polednice</t>
+          <t xml:space="preserve">stvůra z houští</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poludnica</t>
+          <t xml:space="preserve">stvora z húštiny</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">真昼の女</t>
+          <t xml:space="preserve">藪の怪物</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3058,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Północnica</t>
+          <t xml:space="preserve">Zielarka znad jeziora</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3067,52 +3068,52 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Para do Południcy — tłumaczona tak samo.</t>
+          <t xml:space="preserve">Wiedźma, od której zaczęła się klątwa.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lady Midnight</t>
+          <t xml:space="preserve">the Herbwoman from the Lake</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Mitternachtsfrau</t>
+          <t xml:space="preserve">die Kräuterfrau vom See</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Dama de la Medianoche</t>
+          <t xml:space="preserve">la Herbolaria del lago</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Dama da Meia-Noite</t>
+          <t xml:space="preserve">a Erveira do lago</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Dame de Minuit</t>
+          <t xml:space="preserve">l’Herboriste du lac</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Signora della Mezzanotte</t>
+          <t xml:space="preserve">l’Erborista del lago</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">půlnočnice</t>
+          <t xml:space="preserve">bylinkářka od jezera</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">polnočnica</t>
+          <t xml:space="preserve">bylinkárka od jazera</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">真夜中の女</t>
+          <t xml:space="preserve">湖畔の薬草女</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3125,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rusałki</t>
+          <t xml:space="preserve">Południca</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3134,52 +3135,52 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Słowo znane w większości języków.</t>
+          <t xml:space="preserve">W czeskim i słowackim istnieje ta sama istota ludowa.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalki</t>
+          <t xml:space="preserve">Lady Midday</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rusalken</t>
+          <t xml:space="preserve">die Mittagsfrau</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalkas</t>
+          <t xml:space="preserve">la Dama del Mediodía</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalcas</t>
+          <t xml:space="preserve">a Dama do Meio-Dia</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">roussalkas</t>
+          <t xml:space="preserve">la Dame de Midi</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalke</t>
+          <t xml:space="preserve">la Signora del Mezzogiorno</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalky</t>
+          <t xml:space="preserve">polednice</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalky</t>
+          <t xml:space="preserve">poludnica</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ルサルカたち</t>
+          <t xml:space="preserve">真昼の女</t>
         </is>
       </c>
     </row>
@@ -3191,62 +3192,62 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mamuny</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">Północnica</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brak odpowiedników — polska nazwa, wyjaśnia karta w zapiskach.</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamunas</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mamunen</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamunas</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamunas</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamounes</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamune</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamuny</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamuny</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">マムナたち</t>
+          <t xml:space="preserve">Para do Południcy — tłumaczona tak samo.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lady Midnight</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die Mitternachtsfrau</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la Dama de la Medianoche</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Dama da Meia-Noite</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la Dame de Minuit</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la Signora della Mezzanotte</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">půlnočnice</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">polnočnica</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">真夜中の女</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3259,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odmieniec</t>
+          <t xml:space="preserve">Rusałki</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3268,52 +3269,52 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dziecko podrzucone przez mamuny.</t>
+          <t xml:space="preserve">Słowo znane w większości języków.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the changeling</t>
+          <t xml:space="preserve">rusalki</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Wechselbalg</t>
+          <t xml:space="preserve">Rusalken</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el niño cambiado</t>
+          <t xml:space="preserve">rusalkas</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a criança trocada</t>
+          <t xml:space="preserve">rusalkas</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le changelin</t>
+          <t xml:space="preserve">roussalkas</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il bambino scambiato</t>
+          <t xml:space="preserve">rusalke</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">podvrženec</t>
+          <t xml:space="preserve">rusalky</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">podhodenec</t>
+          <t xml:space="preserve">rusalky</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">取り替え子</t>
+          <t xml:space="preserve">ルサルカたち</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3326,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strzyga</t>
+          <t xml:space="preserve">Mamuny</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3335,52 +3336,52 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polska nazwa (znana graczom m.in. z Wiedźmina).</t>
+          <t xml:space="preserve">Brak odpowiedników — polska nazwa, wyjaśnia karta w zapiskach.</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">strzyga</t>
+          <t xml:space="preserve">mamunas</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strzyga</t>
+          <t xml:space="preserve">Mamunen</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">strzyga</t>
+          <t xml:space="preserve">mamunas</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">strzyga</t>
+          <t xml:space="preserve">mamunas</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">strzyga</t>
+          <t xml:space="preserve">mamounes</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">strzyga</t>
+          <t xml:space="preserve">mamune</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">strzyga</t>
+          <t xml:space="preserve">mamuny</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">strzyga</t>
+          <t xml:space="preserve">mamuny</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ストシガ</t>
+          <t xml:space="preserve">マムナたち</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3393,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zmarły, który nie stygnie</t>
+          <t xml:space="preserve">Odmieniec</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3402,52 +3403,52 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuł karty przed odkryciem, że to strzyga.</t>
+          <t xml:space="preserve">Dziecko podrzucone przez mamuny. sk „podhodenec” = podrzutek, dziecko podrzucone komuś, coś podrzuconego, obcego (potwierdzone przez autora).</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Dead Man Who Won’t Go Cold</t>
+          <t xml:space="preserve">the changeling</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Der Tote, der nicht erkaltet</t>
+          <t xml:space="preserve">der Wechselbalg</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El muerto que no se enfría</t>
+          <t xml:space="preserve">el niño cambiado</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">O morto que não esfria</t>
+          <t xml:space="preserve">a criança trocada</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le mort qui ne refroidit pas</t>
+          <t xml:space="preserve">le changelin</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il morto che non si raffredda</t>
+          <t xml:space="preserve">il bambino scambiato</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mrtvý, který nechladne</t>
+          <t xml:space="preserve">podvrženec</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mŕtvy, ktorý nechladne</t>
+          <t xml:space="preserve">podhodenec</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">冷えない死者</t>
+          <t xml:space="preserve">取り替え子</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3460,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licho</t>
+          <t xml:space="preserve">Strzyga</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3469,52 +3470,52 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polska nazwa; w czeskim „licho” też oznacza zło i nieszczęście.</t>
+          <t xml:space="preserve">Polska nazwa (znana graczom m.in. z Wiedźmina). Rzeczownik żeński (de „die Strzyga”, es/pt/fr/it rodzajnik żeński), ale w tej opowieści strzygą jest zmarły stary Wójcik — zaimki osobowe męskie, gdy mowa o nim. L.mn. en „strzygas”, de „Strzygen”, cs/sk „strzygy”.</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">the licho</t>
+          <t xml:space="preserve">strzyga</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">das Licho</t>
+          <t xml:space="preserve">Strzyga</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">el licho</t>
+          <t xml:space="preserve">strzyga</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o licho</t>
+          <t xml:space="preserve">strzyga</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">le licho</t>
+          <t xml:space="preserve">strzyga</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">il licho</t>
+          <t xml:space="preserve">strzyga</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">licho</t>
+          <t xml:space="preserve">strzyga</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">licho</t>
+          <t xml:space="preserve">strzyga</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リホ</t>
+          <t xml:space="preserve">ストシガ</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3527,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jednooka żebraczka</t>
+          <t xml:space="preserve">Zmarły, który nie stygnie</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3536,52 +3537,52 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postać licha.</t>
+          <t xml:space="preserve">Tytuł karty przed odkryciem, że to strzyga.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the One-Eyed Beggar Woman</t>
+          <t xml:space="preserve">The Dead Man Who Won’t Go Cold</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die einäugige Bettlerin</t>
+          <t xml:space="preserve">Der Tote, der nicht erkaltet</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la mendiga tuerta</t>
+          <t xml:space="preserve">El muerto que no se enfría</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a mendiga caolha</t>
+          <t xml:space="preserve">O morto que não esfria</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la mendiante borgne</t>
+          <t xml:space="preserve">Le mort qui ne refroidit pas</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la mendicante orba</t>
+          <t xml:space="preserve">Il morto che non si raffredda</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">jednooká žebračka</t>
+          <t xml:space="preserve">Mrtvý, který nechladne</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">jednooká žobráčka</t>
+          <t xml:space="preserve">Mŕtvy, ktorý nechladne</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">片目の物乞い女</t>
+          <t xml:space="preserve">冷えない死者</t>
         </is>
       </c>
     </row>
@@ -3593,62 +3594,62 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Żytnia baba</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Licho</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">W niemieckim tradycyjny odpowiednik.</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the Rye Mother</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">die Roggenmuhme</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la Vieja del Centeno</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Velha do Centeio</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la Vieille du Seigle</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la Vecchia della Segale</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Žitná bába</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Žitná baba</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ライ麦の婆</t>
+          <t xml:space="preserve">Polska nazwa; rodzaj nijaki (w tekście „ono/je”): en „it”, de „das Licho”, cs/sk nijaki. Wielką literą, gdy jest nazwane („Licho, co nie śpi”), małą w ogólnym „na każde licho”. Uwaga: we współczesnym czeskim i słowackim „lichý” znaczy głównie „nieparzysty, marny”; znaczenie „nieszczęście” (jak ros. лихо) do potwierdzenia przez natywnego.</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the licho</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">das Licho</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el licho</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o licho</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le licho</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">il licho</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">licho</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">licho</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">リホ</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3661,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobieta w życie</t>
+          <t xml:space="preserve">Jednooka żebraczka</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3670,52 +3671,52 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuł karty przed rozpoznaniem żytniej baby.</t>
+          <t xml:space="preserve">Postać licha.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Woman in the Rye</t>
+          <t xml:space="preserve">the One-Eyed Beggar Woman</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Frau im Roggen</t>
+          <t xml:space="preserve">die einäugige Bettlerin</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la mujer del centeno</t>
+          <t xml:space="preserve">la mendiga tuerta</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a mulher do centeio</t>
+          <t xml:space="preserve">a mendiga caolha</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la femme dans le seigle</t>
+          <t xml:space="preserve">la mendiante borgne</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la donna nella segale</t>
+          <t xml:space="preserve">la mendicante orba</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">žena v žitě</t>
+          <t xml:space="preserve">jednooká žebračka</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">žena v raži</t>
+          <t xml:space="preserve">jednooká žobráčka</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ライ麦畑の女</t>
+          <t xml:space="preserve">片目の物乞い女</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3728,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Błędne ogniki</t>
+          <t xml:space="preserve">Żytnia baba</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3737,52 +3738,52 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">W niemieckim tradycyjny odpowiednik.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">will-o’-the-wisps</t>
+          <t xml:space="preserve">the Rye Mother</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Irrlichter</t>
+          <t xml:space="preserve">die Roggenmuhme</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuegos fatuos</t>
+          <t xml:space="preserve">la Vieja del Centeno</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fogos-fátuos</t>
+          <t xml:space="preserve">a Velha do Centeio</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">feux follets</t>
+          <t xml:space="preserve">la Vieille du Seigle</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuochi fatui</t>
+          <t xml:space="preserve">la Vecchia della Segale</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bludičky</t>
+          <t xml:space="preserve">žitná bába</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bludičky</t>
+          <t xml:space="preserve">žitná baba</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">鬼火</t>
+          <t xml:space="preserve">ライ麦の婆</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3795,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Błędnice</t>
+          <t xml:space="preserve">Kobieta w życie</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3804,52 +3805,52 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duchy-światła z orszaku Pana Lasu. Propozycja do sprawdzenia — w innych językach brak utartej nazwy.</t>
+          <t xml:space="preserve">Tytuł karty przed rozpoznaniem żytniej baby.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wisp maidens</t>
+          <t xml:space="preserve">the Woman in the Rye</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Irrlichtjungfern</t>
+          <t xml:space="preserve">die Frau im Roggen</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">doncellas fatuas</t>
+          <t xml:space="preserve">la mujer del centeno</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">donzelas-fátuas</t>
+          <t xml:space="preserve">a mulher do centeio</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">demoiselles follettes</t>
+          <t xml:space="preserve">la femme dans le seigle</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fanciulle fatue</t>
+          <t xml:space="preserve">la donna nella segale</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bludné panny</t>
+          <t xml:space="preserve">žena v žitě</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bludné panny</t>
+          <t xml:space="preserve">žena v raži</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">迷い火の娘たち</t>
+          <t xml:space="preserve">ライ麦畑の女</t>
         </is>
       </c>
     </row>
@@ -3861,62 +3862,62 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Płanetnik</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">Błędne ogniki</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duch chmur i gradu; polska nazwa, wyjaśnia karta.</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetnik</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planetnik</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetnik</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetnik</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetnik</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetnik</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetník</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetník</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">プワネトニク</t>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">will-o’-the-wisps</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Irrlichter</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuegos fatuos</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fogos-fátuos</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feux follets</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuochi fatui</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bludičky</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bludičky</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鬼火</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3929,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ubożę</t>
+          <t xml:space="preserve">Błędnice</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3938,52 +3939,52 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duszek domowy za piecem.</t>
+          <t xml:space="preserve">Kule światła nad bagnem w głębi boru, w każdej skulona mała postać, popiskują jak pisklęta; ze świty Pana Lasu. Nie ma utartej nazwy — wybrano słowa (a) inne niż dla błędnych ogników, (b) sugerujące małe istotki, (c) bez „panien/dziewic” (karta ich nie opisuje). cs/sk „světýlka/svetielka” to poświadczone ludowe nazwy błądzących świateł.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the hearth sprite</t>
+          <t xml:space="preserve">wisplings</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Hausgeist</t>
+          <t xml:space="preserve">Irrwische</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el duende del hogar</t>
+          <t xml:space="preserve">candelillas</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o duende da casa</t>
+          <t xml:space="preserve">luzinhas errantes</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le lutin du foyer</t>
+          <t xml:space="preserve">follettes</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lo spiritello del focolare</t>
+          <t xml:space="preserve">fiammelle erranti</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hospodáříček</t>
+          <t xml:space="preserve">světýlka</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">škriatok</t>
+          <t xml:space="preserve">svetielka</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">かまどの精</t>
+          <t xml:space="preserve">迷い火</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3996,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dziad z lirą</t>
+          <t xml:space="preserve">świta (Pana Lasu)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4005,52 +4006,52 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wędrowny śpiewak z liry korbowej (nie lutnia).</t>
+          <t xml:space="preserve">Orszak istot Pana Lasu (rusałki, mamuny, błędnice). Małą literą. ja 眷属 = orszak bóstwa.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Old Man with the Hurdy-Gurdy</t>
+          <t xml:space="preserve">the retinue</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Alte mit der Drehleier</t>
+          <t xml:space="preserve">das Gefolge</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el viejo de la zanfoña</t>
+          <t xml:space="preserve">el séquito</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o velho da viela de roda</t>
+          <t xml:space="preserve">o séquito</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le vieillard à la vielle</t>
+          <t xml:space="preserve">le cortège</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il vecchio con la ghironda</t>
+          <t xml:space="preserve">il corteo</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dědek s niněrou</t>
+          <t xml:space="preserve">družina</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">starec s ninerou</t>
+          <t xml:space="preserve">družina</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ハーディ・ガーディの老人</t>
+          <t xml:space="preserve">眷属</t>
         </is>
       </c>
     </row>
@@ -4062,62 +4063,62 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biały wilk</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Płanetnik</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the White Wolf</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">der Weiße Wolf</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el Lobo Blanco</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o Lobo Branco</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">le Loup blanc</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">il Lupo Bianco</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bílý vlk</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biely vlk</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白い狼</t>
+          <t xml:space="preserve">Duch chmur i gradu; polska nazwa, wyjaśnia karta.</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetnik</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planetnik</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetnik</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetnik</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetnik</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetnik</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetník</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetník</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">プワネトニク</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4130,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dzieci spod dębu</t>
+          <t xml:space="preserve">Ubożę</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4139,52 +4140,52 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Duszek domowy za piecem; rodzaj nijaki („je”), w tekście wielką literą jak imię („Kto Ubożę karmi”). Bogactwo, które przynosi, ubywa sąsiadom (jak niemiecki Kobold).</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Children under the Oak</t>
+          <t xml:space="preserve">the hearth sprite</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Kinder unter der Eiche</t>
+          <t xml:space="preserve">der Hausgeist</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">los niños bajo el roble</t>
+          <t xml:space="preserve">el duende del hogar</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">as crianças sob o carvalho</t>
+          <t xml:space="preserve">o duende da casa</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">les enfants sous le chêne</t>
+          <t xml:space="preserve">le lutin du foyer</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">i bambini sotto la quercia</t>
+          <t xml:space="preserve">lo spiritello del focolare</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">děti pod dubem</t>
+          <t xml:space="preserve">hospodáříček</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">deti spod duba</t>
+          <t xml:space="preserve">škriatok</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">樫の下の子どもたち</t>
+          <t xml:space="preserve">かまどの精</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4197,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pod oknem (karta)</t>
+          <t xml:space="preserve">Dziad z lirą</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4206,64 +4207,64 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Wędrowny śpiewak z liry korbowej (nie lutnia).</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under the Window</t>
+          <t xml:space="preserve">the Old Man with the Hurdy-Gurdy</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unter dem Fenster</t>
+          <t xml:space="preserve">der Alte mit der Drehleier</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bajo la ventana</t>
+          <t xml:space="preserve">el viejo de la zanfoña</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sob a janela</t>
+          <t xml:space="preserve">o velho da viela de roda</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sous la fenêtre</t>
+          <t xml:space="preserve">le vieillard à la vielle</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sotto la finestra</t>
+          <t xml:space="preserve">il vecchio con la ghironda</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pod oknem</t>
+          <t xml:space="preserve">dědek s niněrou</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pod oknom</t>
+          <t xml:space="preserve">starec s ninerou</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">窓の下</t>
+          <t xml:space="preserve">ハーディ・ガーディ弾きの老人</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Przedmioty</t>
+          <t xml:space="preserve">Istoty</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siekiera dziadka Maćka</t>
+          <t xml:space="preserve">Biały wilk</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4278,59 +4279,59 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grandfather Maciek’s axe</t>
+          <t xml:space="preserve">the white wolf</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Großvater Macieks Axt</t>
+          <t xml:space="preserve">der weiße Wolf</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El hacha del abuelo Maciek</t>
+          <t xml:space="preserve">el lobo blanco</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">O machado do avô Maciek</t>
+          <t xml:space="preserve">o lobo branco</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La hache de grand-père Maciek</t>
+          <t xml:space="preserve">le loup blanc</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">L’ascia di nonno Maciek</t>
+          <t xml:space="preserve">il lupo bianco</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sekera dědečka Maćka</t>
+          <t xml:space="preserve">bílý vlk</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sekera dedka Maćka</t>
+          <t xml:space="preserve">biely vlk</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">マチェクじいさんの斧</t>
+          <t xml:space="preserve">白い狼</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Przedmioty</t>
+          <t xml:space="preserve">Istoty</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nadpalona figurka (lalka)</t>
+          <t xml:space="preserve">Dzieci spod dębu</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4340,64 +4341,64 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">„Lalka” zielarki — w snach dzieci: „Gdzie moja lalka?”.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charred figurine (the doll)</t>
+          <t xml:space="preserve">the Children under the Oak</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Angekohlte Figur (die Puppe)</t>
+          <t xml:space="preserve">die Kinder unter der Eiche</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Figurilla chamuscada (la muñeca)</t>
+          <t xml:space="preserve">los niños bajo el roble</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estatueta chamuscada (a boneca)</t>
+          <t xml:space="preserve">as crianças sob o carvalho</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Figurine calcinée (la poupée)</t>
+          <t xml:space="preserve">les enfants sous le chêne</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statuina bruciacchiata (la bambola)</t>
+          <t xml:space="preserve">i bambini sotto la quercia</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ohořelá figurka (panenka)</t>
+          <t xml:space="preserve">děti pod dubem</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ohorená figúrka (bábika)</t>
+          <t xml:space="preserve">deti spod duba</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">焦げた人形</t>
+          <t xml:space="preserve">樫の下の子どもたち</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Przedmioty</t>
+          <t xml:space="preserve">Istoty</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krzesiwo</t>
+          <t xml:space="preserve">Pod oknem (karta)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4412,47 +4413,47 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flint and steel</t>
+          <t xml:space="preserve">Under the Window</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feuerstahl</t>
+          <t xml:space="preserve">Unter dem Fenster</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eslabón</t>
+          <t xml:space="preserve">Bajo la ventana</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuzil</t>
+          <t xml:space="preserve">Sob a janela</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Briquet à silex</t>
+          <t xml:space="preserve">Sous la fenêtre</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acciarino</t>
+          <t xml:space="preserve">Sotto la finestra</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Křesadlo</t>
+          <t xml:space="preserve">Pod oknem</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kresadlo</t>
+          <t xml:space="preserve">Pod oknom</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">火打ち金</t>
+          <t xml:space="preserve">窓の下</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4465,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Księga opowiadań (pana Ignacego)</t>
+          <t xml:space="preserve">Siekiera dziadka Maćka</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4474,52 +4475,52 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rękopis nauczyciela z podaniami.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book of tales</t>
+          <t xml:space="preserve">Grandfather Maciek’s axe</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buch der Erzählungen</t>
+          <t xml:space="preserve">Großvater Macieks Axt</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libro de relatos</t>
+          <t xml:space="preserve">El hacha del abuelo Maciek</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Livro de contos</t>
+          <t xml:space="preserve">O machado do avô Maciek</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Livre de contes</t>
+          <t xml:space="preserve">La hache de grand-père Maciek</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libro di racconti</t>
+          <t xml:space="preserve">L’ascia di nonno Maciek</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kniha vyprávění</t>
+          <t xml:space="preserve">Sekera dědečka Maćka</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kniha rozprávok</t>
+          <t xml:space="preserve">Sekera dedka Maćka</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">昔話の帳面</t>
+          <t xml:space="preserve">マチェクじいさんの斧</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4532,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Żołądź ze Starego Dębu</t>
+          <t xml:space="preserve">Nadpalona figurka (lalka)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4541,52 +4542,52 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">„Lalka” zielarki — w snach dzieci: „Gdzie moja lalka?”.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acorn from the Old Oak</t>
+          <t xml:space="preserve">Charred figurine (the doll)</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eichel der Alten Eiche</t>
+          <t xml:space="preserve">Angekohlte Figur (die Puppe)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bellota del Viejo Roble</t>
+          <t xml:space="preserve">Figurilla chamuscada (la muñeca)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolota do Velho Carvalho</t>
+          <t xml:space="preserve">Estatueta chamuscada (a boneca)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gland du Vieux Chêne</t>
+          <t xml:space="preserve">Figurine calcinée (la poupée)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ghianda della Vecchia Quercia</t>
+          <t xml:space="preserve">Statuina bruciacchiata (la bambola)</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Žalud ze Starého dubu</t>
+          <t xml:space="preserve">Ohořelá figurka (panenka)</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Žaluď zo Starého duba</t>
+          <t xml:space="preserve">Ohorená figúrka (bábika)</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">老樫のどんぐり</t>
+          <t xml:space="preserve">焦げた人形</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4599,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piołun</t>
+          <t xml:space="preserve">Krzesiwo</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4613,47 +4614,47 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wormwood</t>
+          <t xml:space="preserve">Flint and steel</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wermut</t>
+          <t xml:space="preserve">Feuerstahl</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajenjo</t>
+          <t xml:space="preserve">Eslabón</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Losna</t>
+          <t xml:space="preserve">Pederneira</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absinthe (armoise)</t>
+          <t xml:space="preserve">Briquet à silex</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assenzio</t>
+          <t xml:space="preserve">Acciarino</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pelyněk</t>
+          <t xml:space="preserve">Křesadlo</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palina</t>
+          <t xml:space="preserve">Kresadlo</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ニガヨモギ</t>
+          <t xml:space="preserve">火打ち金</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4666,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korale z jarzębiny</t>
+          <t xml:space="preserve">Księga opowiadań (pana Ignacego)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4675,52 +4676,52 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rękopis nauczyciela z podaniami.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rowan-berry beads</t>
+          <t xml:space="preserve">Book of legends</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vogelbeerkette</t>
+          <t xml:space="preserve">Sagenbuch</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collar de serbal</t>
+          <t xml:space="preserve">Libro de relatos</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colar de sorveira</t>
+          <t xml:space="preserve">Livro de contos</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collier de sorbier</t>
+          <t xml:space="preserve">Livre de contes</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collana di sorbo</t>
+          <t xml:space="preserve">Quaderno delle leggende</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korále z jeřabin</t>
+          <t xml:space="preserve">Kniha vyprávění</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korálky z jarabiny</t>
+          <t xml:space="preserve">Kniha rozprávok</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ナナカマドの数珠</t>
+          <t xml:space="preserve">昔話の帳面</t>
         </is>
       </c>
     </row>
@@ -4732,7 +4733,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Świątek z kapliczki</t>
+          <t xml:space="preserve">Żołądź ze Starego Dębu</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4742,52 +4743,52 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drewniana figurka świętego z przydrożnej kapliczki.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wayside saint figure</t>
+          <t xml:space="preserve">Acorn from the Old Oak</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heiligenfigur aus dem Bildstock</t>
+          <t xml:space="preserve">Eichel der Alten Eiche</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santito de la capilla</t>
+          <t xml:space="preserve">Bellota del Viejo Roble</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santinho do oratório</t>
+          <t xml:space="preserve">Bolota do Velho Carvalho</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statuette de calvaire</t>
+          <t xml:space="preserve">Gland du Vieux Chêne</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santino dell’edicola</t>
+          <t xml:space="preserve">Ghianda della Vecchia Quercia</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svatý ze kapličky</t>
+          <t xml:space="preserve">Žalud ze Starého dubu</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svätý z kaplnky</t>
+          <t xml:space="preserve">Žaluď zo Starého duba</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">祠の聖像</t>
+          <t xml:space="preserve">老樫のどんぐり</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4800,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Podkowa kowala</t>
+          <t xml:space="preserve">Piołun</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4814,47 +4815,47 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The smith’s horseshoe</t>
+          <t xml:space="preserve">Wormwood</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hufeisen des Schmieds</t>
+          <t xml:space="preserve">Wermut</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La herradura del herrero</t>
+          <t xml:space="preserve">Ajenjo</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A ferradura do ferreiro</t>
+          <t xml:space="preserve">Losna</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le fer à cheval du forgeron</t>
+          <t xml:space="preserve">Absinthe (armoise)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il ferro di cavallo del fabbro</t>
+          <t xml:space="preserve">Assenzio</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kovářova podkova</t>
+          <t xml:space="preserve">Pelyněk</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kováčova podkova</t>
+          <t xml:space="preserve">Palina</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">鍛冶屋の蹄鉄</t>
+          <t xml:space="preserve">ニガヨモギ</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4867,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krzyżyk kowala</t>
+          <t xml:space="preserve">Korale z jarzębiny</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4881,47 +4882,47 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The smith’s cross</t>
+          <t xml:space="preserve">Rowan-berry beads</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kreuz des Schmieds</t>
+          <t xml:space="preserve">Vogelbeerkette</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La crucecita del herrero</t>
+          <t xml:space="preserve">Collar de serbal</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A cruzinha do ferreiro</t>
+          <t xml:space="preserve">Colar de sorveira</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La croix du forgeron</t>
+          <t xml:space="preserve">Collier de sorbier</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La crocetta del fabbro</t>
+          <t xml:space="preserve">Collana di sorbo</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kovářův křížek</t>
+          <t xml:space="preserve">Korále z jeřabin</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kováčov krížik</t>
+          <t xml:space="preserve">Korálky z jarabiny</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">鍛冶屋の十字架</t>
+          <t xml:space="preserve">ナナカマドの数珠</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4934,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gromnica</t>
+          <t xml:space="preserve">Świątek z kapliczki</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4943,52 +4944,52 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Świeca święcona na Matki Bożej Gromnicznej.</t>
+          <t xml:space="preserve">Drewniana figurka świętego z przydrożnej kapliczki.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candlemas candle</t>
+          <t xml:space="preserve">Wayside saint figure</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lichtmesskerze</t>
+          <t xml:space="preserve">Heiligenfigur aus dem Bildstock</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vela de la Candelaria</t>
+          <t xml:space="preserve">Santito del humilladero</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vela da Candelária</t>
+          <t xml:space="preserve">Santinho do oratório</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cierge de la Chandeleur</t>
+          <t xml:space="preserve">Statuette de l’oratoire</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candela della Candelora</t>
+          <t xml:space="preserve">Santino dell’edicola</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hromnička</t>
+          <t xml:space="preserve">Soška z kapličky</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hromničná svieca</t>
+          <t xml:space="preserve">Soška z kaplnky</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖燭祭の蝋燭</t>
+          <t xml:space="preserve">祠の聖像</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5001,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drewniaki Marysi</t>
+          <t xml:space="preserve">Podkowa kowala</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5010,52 +5011,52 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Małe czerwone chodaki.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysia’s clogs</t>
+          <t xml:space="preserve">The smith’s horseshoe</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysias Holzschuhe</t>
+          <t xml:space="preserve">Hufeisen des Schmieds</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los zuecos de Marysia</t>
+          <t xml:space="preserve">La herradura del herrero</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os tamancos de Marysia</t>
+          <t xml:space="preserve">A ferradura do ferreiro</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les sabots de Marysia</t>
+          <t xml:space="preserve">Le fer à cheval du forgeron</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gli zoccoli di Marysia</t>
+          <t xml:space="preserve">Il ferro di cavallo del fabbro</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysiny dřeváky</t>
+          <t xml:space="preserve">Kovářova podkova</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysine dreváky</t>
+          <t xml:space="preserve">Kováčova podkova</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">マリシャの木靴</t>
+          <t xml:space="preserve">鍛冶屋の蹄鉄</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5068,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wstążka Marysi</t>
+          <t xml:space="preserve">Krzyżyk kowala</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5082,47 +5083,47 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysia’s ribbon</t>
+          <t xml:space="preserve">The smith’s cross</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysias Band</t>
+          <t xml:space="preserve">Kreuz des Schmieds</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La cinta de Marysia</t>
+          <t xml:space="preserve">La crucecita del herrero</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A fita de Marysia</t>
+          <t xml:space="preserve">A cruzinha do ferreiro</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le ruban de Marysia</t>
+          <t xml:space="preserve">La croix du forgeron</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il nastro di Marysia</t>
+          <t xml:space="preserve">La crocetta del fabbro</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysina stužka</t>
+          <t xml:space="preserve">Kovářův křížek</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysina stužka</t>
+          <t xml:space="preserve">Kováčov krížik</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">マリシャのリボン</t>
+          <t xml:space="preserve">鍛冶屋の十字架</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5135,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garść maku</t>
+          <t xml:space="preserve">Gromnica</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5144,52 +5145,52 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Świeca święcona na Matki Bożej Gromnicznej.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A handful of poppy seeds</t>
+          <t xml:space="preserve">Candlemas candle</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eine Handvoll Mohn</t>
+          <t xml:space="preserve">Lichtmesskerze</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un puñado de amapola</t>
+          <t xml:space="preserve">Vela de la Candelaria</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um punhado de papoula</t>
+          <t xml:space="preserve">Vela da Candelária</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Une poignée de pavot</t>
+          <t xml:space="preserve">Cierge de la Chandeleur</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Una manciata di papavero</t>
+          <t xml:space="preserve">Candela della Candelora</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrst máku</t>
+          <t xml:space="preserve">Hromnička</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrsť maku</t>
+          <t xml:space="preserve">Hromničná svieca</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ひと握りのケシの実</t>
+          <t xml:space="preserve">聖燭祭の蝋燭</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5202,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kora ze znakiem</t>
+          <t xml:space="preserve">Drewniaki Marysi</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5211,52 +5212,52 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Małe czerwone chodaki.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bark with a sign</t>
+          <t xml:space="preserve">Marysia’s clogs</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rinde mit Zeichen</t>
+          <t xml:space="preserve">Marysias Holzschuhe</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corteza con un signo</t>
+          <t xml:space="preserve">Los zuecos de Marysia</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casca com um sinal</t>
+          <t xml:space="preserve">Os tamancos de Marysia</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Écorce marquée</t>
+          <t xml:space="preserve">Les sabots de Marysia</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corteccia col segno</t>
+          <t xml:space="preserve">Gli zoccoli di Marysia</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kůra se znamením</t>
+          <t xml:space="preserve">Marysiny dřeváky</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kôra so znamením</t>
+          <t xml:space="preserve">Marysine dreváky</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">印のある樹皮</t>
+          <t xml:space="preserve">マリシャの木靴</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5269,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poświęcony różaniec</t>
+          <t xml:space="preserve">Wstążka Marysi</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5283,47 +5284,47 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blessed rosary</t>
+          <t xml:space="preserve">Marysia’s ribbon</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geweihter Rosenkranz</t>
+          <t xml:space="preserve">Marysias Band</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosario bendito</t>
+          <t xml:space="preserve">La cinta de Marysia</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terço bento</t>
+          <t xml:space="preserve">A fita de Marysia</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chapelet béni</t>
+          <t xml:space="preserve">Le ruban de Marysia</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosario benedetto</t>
+          <t xml:space="preserve">Il nastro di Marysia</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Posvěcený růženec</t>
+          <t xml:space="preserve">Marysina stužka</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Posvätený ruženec</t>
+          <t xml:space="preserve">Marysina stužka</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖別されたロザリオ</t>
+          <t xml:space="preserve">マリシャのリボン</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5336,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">całun (mamun)</t>
+          <t xml:space="preserve">Garść maku</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5345,52 +5346,52 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Małe płótno prane przez mamuny.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shroud</t>
+          <t xml:space="preserve">A handful of poppy seeds</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leichentuch</t>
+          <t xml:space="preserve">Eine Handvoll Mohn</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mortaja</t>
+          <t xml:space="preserve">Un puñado de semillas de amapola</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mortalha</t>
+          <t xml:space="preserve">Um punhado de sementes de papoula</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">linceul</t>
+          <t xml:space="preserve">Une poignée de graines de pavot</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sudario</t>
+          <t xml:space="preserve">Una manciata di semi di papavero</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rubáš</t>
+          <t xml:space="preserve">Hrst máku</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rubáš</t>
+          <t xml:space="preserve">Hrsť maku</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">経帷子</t>
+          <t xml:space="preserve">ひと握りのケシの実</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5403,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kijanka</t>
+          <t xml:space="preserve">Kora ze znakiem</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5412,64 +5413,64 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drewniana pałka do prania; jej klaskanie zwiastuje mamuny.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">washing paddle</t>
+          <t xml:space="preserve">Bark with a sign</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waschbleuel</t>
+          <t xml:space="preserve">Rinde mit Zeichen</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pala de lavar</t>
+          <t xml:space="preserve">Corteza con un signo</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">batedor de roupa</t>
+          <t xml:space="preserve">Casca com um sinal</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">battoir</t>
+          <t xml:space="preserve">Écorce marquée</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">battipanni</t>
+          <t xml:space="preserve">Corteccia col segno</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prací palička</t>
+          <t xml:space="preserve">Kůra se znamením</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pracia palica</t>
+          <t xml:space="preserve">Kôra so znamením</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">洗濯棒</t>
+          <t xml:space="preserve">印のある樹皮</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Święta i obrzędy</t>
+          <t xml:space="preserve">Przedmioty</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wigilia</t>
+          <t xml:space="preserve">Poświęcony różaniec</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5484,59 +5485,59 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christmas Eve</t>
+          <t xml:space="preserve">Blessed rosary</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heiligabend</t>
+          <t xml:space="preserve">Geweihter Rosenkranz</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nochebuena</t>
+          <t xml:space="preserve">Rosario bendito</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Véspera de Natal</t>
+          <t xml:space="preserve">Terço bento</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le réveillon de Noël</t>
+          <t xml:space="preserve">Chapelet béni</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Vigilia di Natale</t>
+          <t xml:space="preserve">Rosario benedetto</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Štědrý večer</t>
+          <t xml:space="preserve">Posvěcený růženec</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Štedrý večer</t>
+          <t xml:space="preserve">Posvätený ruženec</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">クリスマス・イブ</t>
+          <t xml:space="preserve">聖別されたロザリオ</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Święta i obrzędy</t>
+          <t xml:space="preserve">Przedmioty</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pasterka</t>
+          <t xml:space="preserve">całun (mamun)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5546,64 +5547,64 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Małe płótno prane przez mamuny.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midnight Mass</t>
+          <t xml:space="preserve">shroud</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christmette</t>
+          <t xml:space="preserve">Leichentuch</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misa del Gallo</t>
+          <t xml:space="preserve">mortaja</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Missa do Galo</t>
+          <t xml:space="preserve">mortalha</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">messe de minuit</t>
+          <t xml:space="preserve">linceul</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">messa di mezzanotte</t>
+          <t xml:space="preserve">sudario</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">půlnoční mše</t>
+          <t xml:space="preserve">rubáš</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">polnočná omša</t>
+          <t xml:space="preserve">rubáš</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">真夜中のミサ</t>
+          <t xml:space="preserve">経帷子</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Święta i obrzędy</t>
+          <t xml:space="preserve">Przedmioty</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zaduszki</t>
+          <t xml:space="preserve">kijanka</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5613,52 +5614,52 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Drewniana pałka do prania; jej klaskanie zwiastuje mamuny.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Souls’ Day</t>
+          <t xml:space="preserve">washing paddle</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allerseelen</t>
+          <t xml:space="preserve">Waschbleuel</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Día de los Difuntos</t>
+          <t xml:space="preserve">pala de lavar</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia de Finados</t>
+          <t xml:space="preserve">batedor de roupa</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le jour des Morts</t>
+          <t xml:space="preserve">battoir</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il giorno dei Morti</t>
+          <t xml:space="preserve">battipanni</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dušičky</t>
+          <t xml:space="preserve">prací palička</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dušičky</t>
+          <t xml:space="preserve">pracia palica</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">死者の日</t>
+          <t xml:space="preserve">洗濯棒</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5671,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zielone Świątki</t>
+          <t xml:space="preserve">Wigilia</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5685,47 +5686,47 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pentecost</t>
+          <t xml:space="preserve">Christmas Eve</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pfingsten</t>
+          <t xml:space="preserve">Heiligabend</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pentecostés</t>
+          <t xml:space="preserve">Nochebuena</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pentecostes</t>
+          <t xml:space="preserve">Véspera de Natal</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Pentecôte</t>
+          <t xml:space="preserve">la veillée de Noël</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Pentecoste</t>
+          <t xml:space="preserve">la Vigilia di Natale</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Letnice</t>
+          <t xml:space="preserve">Štědrý večer</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turíce</t>
+          <t xml:space="preserve">Štedrý večer</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖霊降臨祭</t>
+          <t xml:space="preserve">聖夜</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5738,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noc Kupały / noc świętojańska</t>
+          <t xml:space="preserve">opłatek</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5747,52 +5748,52 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Cienki biały wafel łamany w Wigilię; kładziony na talerzu dla wędrowca. W tekście też porównanie „cienki jak opłatek” (lód) — oddać naturalnym porównaniem (en „wafer-thin”, de „hauchdünn wie eine Oblate”).</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kupala Night / Midsummer Night</t>
+          <t xml:space="preserve">the Christmas wafer</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kupalanacht / Johannisnacht</t>
+          <t xml:space="preserve">die Weihnachtsoblate</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noche de Kupala / Noche de San Juan</t>
+          <t xml:space="preserve">la oblea de Navidad</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noite de Kupala / Noite de São João</t>
+          <t xml:space="preserve">a hóstia de Natal</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nuit de Kupala / nuit de la Saint-Jean</t>
+          <t xml:space="preserve">l’hostie de Noël</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">notte di Kupala / notte di San Giovanni</t>
+          <t xml:space="preserve">l’ostia di Natale</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kupalská noc / svatojánská noc</t>
+          <t xml:space="preserve">oplatka</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kupadelná noc / jánska noc</t>
+          <t xml:space="preserve">oblátka</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">クパーラの夜 / 夏至の夜</t>
+          <t xml:space="preserve">クリスマスの聖餅</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5805,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sobótki</t>
+          <t xml:space="preserve">Pasterka</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5814,52 +5815,52 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ogniska w noc świętojańską.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midsummer bonfires</t>
+          <t xml:space="preserve">Midnight Mass</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannisfeuer</t>
+          <t xml:space="preserve">Christmette</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hogueras de San Juan</t>
+          <t xml:space="preserve">Misa del Gallo</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fogueiras de São João</t>
+          <t xml:space="preserve">Missa do Galo</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">feux de la Saint-Jean</t>
+          <t xml:space="preserve">messe de minuit</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">falò di San Giovanni</t>
+          <t xml:space="preserve">messa di mezzanotte</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">svatojánské ohně</t>
+          <t xml:space="preserve">půlnoční mše</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">jánske ohne</t>
+          <t xml:space="preserve">polnočná omša</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">夏至の焚き火</t>
+          <t xml:space="preserve">真夜中のミサ</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5872,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gromniczna</t>
+          <t xml:space="preserve">Zaduszki</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5881,52 +5882,52 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 lutego.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candlemas</t>
+          <t xml:space="preserve">All Souls’ Day</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lichtmess</t>
+          <t xml:space="preserve">Allerseelen</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Candelaria</t>
+          <t xml:space="preserve">Día de los Difuntos</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Candelária</t>
+          <t xml:space="preserve">Dia de Finados</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Chandeleur</t>
+          <t xml:space="preserve">le jour des Morts</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Candelora</t>
+          <t xml:space="preserve">il giorno dei Morti</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hromnice</t>
+          <t xml:space="preserve">Dušičky</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hromnice</t>
+          <t xml:space="preserve">Dušičky</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖燭祭</t>
+          <t xml:space="preserve">死者の日</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5939,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wielkanoc / Wielki Czwartek</t>
+          <t xml:space="preserve">Zielone Świątki</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5953,47 +5954,47 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Easter / Maundy Thursday</t>
+          <t xml:space="preserve">Whitsun</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ostern / Gründonnerstag</t>
+          <t xml:space="preserve">Pfingsten</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pascua / Jueves Santo</t>
+          <t xml:space="preserve">Pentecostés</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Páscoa / Quinta-feira Santa</t>
+          <t xml:space="preserve">Pentecostes</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pâques / Jeudi saint</t>
+          <t xml:space="preserve">la Pentecôte</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pasqua / Giovedì santo</t>
+          <t xml:space="preserve">la Pentecoste</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velikonoce / Zelený čtvrtek</t>
+          <t xml:space="preserve">Letnice</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veľká noc / Zelený štvrtok</t>
+          <t xml:space="preserve">Turíce</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">復活祭 / 聖木曜日</t>
+          <t xml:space="preserve">聖霊降臨祭</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6006,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrzejki</t>
+          <t xml:space="preserve">Noc Kupały / noc świętojańska</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6015,52 +6016,52 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wieczór wróżb 29 listopada.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">St Andrew’s Eve</t>
+          <t xml:space="preserve">Kupala Night / Midsummer Night</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andreasnacht</t>
+          <t xml:space="preserve">Kupalanacht / Johannisnacht</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">víspera de San Andrés</t>
+          <t xml:space="preserve">Noche de Kupala / Noche de San Juan</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">véspera de Santo André</t>
+          <t xml:space="preserve">Noite de Kupala / Noite de São João</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la veille de la Saint-André</t>
+          <t xml:space="preserve">nuit de Kupala / nuit de la Saint-Jean</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la vigilia di Sant’Andrea</t>
+          <t xml:space="preserve">notte di Kupala / notte di San Giovanni</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondřejská noc</t>
+          <t xml:space="preserve">Kupalská noc / svatojánská noc</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrejská noc</t>
+          <t xml:space="preserve">Kupalova noc / svätojánska noc</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖アンデレの前夜</t>
+          <t xml:space="preserve">クパーラの夜 / 夏至の夜</t>
         </is>
       </c>
     </row>
@@ -6072,62 +6073,62 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marzanna</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">sobótki</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polska nazwa + przy pierwszym wystąpieniu: słomiana kukła topiona na wiosnę. W czeskim i słowackim ten sam zwyczaj ma własną nazwę (Morana, Morena).</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (the straw effigy of winter)</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (die Strohpuppe des Winters)</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (la muñeca de paja del invierno)</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (a boneca de palha do inverno)</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (l’effigie de paille de l’hiver)</t>
-        </is>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (il fantoccio di paglia dell’inverno)</t>
-        </is>
-      </c>
-      <c r="K90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Morana (Mařena)</t>
-        </is>
-      </c>
-      <c r="L90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Morena</t>
-        </is>
-      </c>
-      <c r="M90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">マルザンナ（冬の藁人形）</t>
+          <t xml:space="preserve">Ogniska w noc świętojańską.</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Midsummer bonfires</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Johannisfeuer</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hogueras de San Juan</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fogueiras de São João</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feux de la Saint-Jean</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">falò di San Giovanni</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">svatojánské ohně</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jánske ohne</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夏至の焚き火</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6140,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">oczepiny / swaty / zrękowiny</t>
+          <t xml:space="preserve">kołacz</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6149,52 +6150,52 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obrzędy weselne — opisowo, bez szukania egzotycznych słów.</t>
+          <t xml:space="preserve">Weselny placek drożdżowy (Hanka piecze je z miodem); poczęstunek dla starca w noc oczepin.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unveiling of the bride / matchmaking / betrothal</t>
+          <t xml:space="preserve">wedding loaf</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haubung / Brautwerbung / Verlobung</t>
+          <t xml:space="preserve">Hochzeitskuchen</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tocado de la novia / petición de mano / esponsales</t>
+          <t xml:space="preserve">rosca de boda</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">touca da noiva / pedido / noivado</t>
+          <t xml:space="preserve">rosca de casamento</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">coiffure de la mariée / demande / fiançailles</t>
+          <t xml:space="preserve">brioche de noces</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">velo della sposa / combinazione / fidanzamento</t>
+          <t xml:space="preserve">focaccia nuziale</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">čepení / námluvy / zásnuby</t>
+          <t xml:space="preserve">svatební koláč</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">čepčenie / pytačky / zásnuby</t>
+          <t xml:space="preserve">svadobný koláč</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">花嫁の頭巾の儀 / 縁談 / 婚約</t>
+          <t xml:space="preserve">婚礼のパン</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6207,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">przednówek</t>
+          <t xml:space="preserve">Gromniczna</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6216,52 +6217,52 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Głodny czas przed pierwszymi plonami.</t>
+          <t xml:space="preserve">2 lutego.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the hungry gap</t>
+          <t xml:space="preserve">Candlemas</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Notzeit vor der Ernte</t>
+          <t xml:space="preserve">Lichtmess</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la escasez de primavera</t>
+          <t xml:space="preserve">la Candelaria</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a fome antes da colheita</t>
+          <t xml:space="preserve">a Candelária</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la soudure</t>
+          <t xml:space="preserve">la Chandeleur</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il periodo di magra</t>
+          <t xml:space="preserve">la Candelora</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hladové jaro</t>
+          <t xml:space="preserve">Hromnice</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hladná jar</t>
+          <t xml:space="preserve">Hromnice</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">端境期</t>
+          <t xml:space="preserve">聖燭祭</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6274,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kapliczka</t>
+          <t xml:space="preserve">Wielkanoc / Wielki Czwartek</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6283,198 +6284,198 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Przydrożna kapliczka — ważny motyw, zawsze ten sam wyraz.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wayside shrine</t>
+          <t xml:space="preserve">Easter / Maundy Thursday</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bildstock</t>
+          <t xml:space="preserve">Ostern / Gründonnerstag</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">capilla</t>
+          <t xml:space="preserve">Pascua / Jueves Santo</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">oratório</t>
+          <t xml:space="preserve">Páscoa / Quinta-feira Santa</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">calvaire</t>
+          <t xml:space="preserve">Pâques / Jeudi saint</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">edicola votiva</t>
+          <t xml:space="preserve">Pasqua / Giovedì santo</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kaplička</t>
+          <t xml:space="preserve">Velikonoce / Zelený čtvrtek</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kaplnka</t>
+          <t xml:space="preserve">Veľká noc / Zelený štvrtok</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">道端の祠</t>
+          <t xml:space="preserve">復活祭 / 聖木曜日</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuły rozdziałów</t>
+          <t xml:space="preserve">Święta i obrzędy</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prolog: Zapadlina</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">Andrzejki</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Części prologu: Zapadlina, Chata, Dach, Zgliszcza, Miasto, Rodzina, Powrót, Jedna świeca, Lata spokoju.</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="M94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ザパドリナ</t>
+          <t xml:space="preserve">Wieczór wróżb 29 listopada.</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">St Andrew’s Eve</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andreasnacht</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">víspera de San Andrés</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">véspera de Santo André</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la veille de la Saint-André</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la vigilia di Sant’Andrea</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ondřejská noc</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ondrejská noc</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖アンデレの前夜</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuły rozdziałów</t>
+          <t xml:space="preserve">Święta i obrzędy</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chata / Dach / Zgliszcza</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Marzanna</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Hut / The Roof / The Ashes</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Die Hütte / Das Dach / Die Brandstätte</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La cabaña / El tejado / Las cenizas</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A cabana / O telhado / As cinzas</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La cabane / Le toit / Les cendres</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La capanna / Il tetto / Le macerie</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chata / Střecha / Spáleniště</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chata / Strecha / Spálenisko</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">小屋 / 屋根 / 焼け跡</t>
+          <t xml:space="preserve">Polska nazwa + przy pierwszym wystąpieniu: słomiana kukła topiona na wiosnę. W czeskim i słowackim ten sam zwyczaj ma własną nazwę (Morana, Morena).</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marzanna (the straw effigy of winter)</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marzanna (die Strohpuppe des Winters)</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marzanna (la muñeca de paja del invierno)</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marzanna (a boneca de palha do inverno)</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marzanna (l’effigie de paille de l’hiver)</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marzanna (il fantoccio di paglia dell’inverno)</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morana (Mařena)</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morena</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">マジャンナ（冬の藁人形）</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuły rozdziałów</t>
+          <t xml:space="preserve">Święta i obrzędy</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miasto / Rodzina / Powrót</t>
+          <t xml:space="preserve">oczepiny / swaty / zrękowiny</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6484,64 +6485,64 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Obrzędy weselne — opisowo, bez szukania egzotycznych słów.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Town / The Family / The Return</t>
+          <t xml:space="preserve">capping of the bride / matchmaking / betrothal</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Die Stadt / Die Familie / Die Heimkehr</t>
+          <t xml:space="preserve">Haubung / Brautwerbung / Verlobung</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La ciudad / La familia / El regreso</t>
+          <t xml:space="preserve">tocado de la novia / petición de mano / esponsales</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A cidade / A família / O regresso</t>
+          <t xml:space="preserve">touca da noiva / pedido de casamento / noivado</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La ville / La famille / Le retour</t>
+          <t xml:space="preserve">coiffe de la mariée / demande en mariage / fiançailles</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La città / La famiglia / Il ritorno</t>
+          <t xml:space="preserve">cuffia della sposa / richiesta di matrimonio / fidanzamento</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Město / Rodina / Návrat</t>
+          <t xml:space="preserve">čepení / námluvy / zásnuby</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mesto / Rodina / Návrat</t>
+          <t xml:space="preserve">čepčenie / pytačky / zásnuby</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">町 / 家族 / 帰還</t>
+          <t xml:space="preserve">花嫁の頭巾の儀 / 縁談 / 婚約</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuły rozdziałów</t>
+          <t xml:space="preserve">Święta i obrzędy</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedna świeca / Lata spokoju</t>
+          <t xml:space="preserve">przednówek</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6551,64 +6552,64 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Głodny czas przed pierwszymi plonami.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">One Candle / Quiet Years</t>
+          <t xml:space="preserve">the hungry gap</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eine Kerze / Ruhige Jahre</t>
+          <t xml:space="preserve">die Notzeit vor der Ernte</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Una vela / Años de calma</t>
+          <t xml:space="preserve">la escasez de primavera</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma vela / Anos de paz</t>
+          <t xml:space="preserve">a fome antes da colheita</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Une seule bougie / Les années paisibles</t>
+          <t xml:space="preserve">la soudure</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Una candela / Anni di pace</t>
+          <t xml:space="preserve">il periodo di magra</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedna svíce / Léta klidu</t>
+          <t xml:space="preserve">hladové jaro</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedna sviečka / Roky pokoja</t>
+          <t xml:space="preserve">hladná jar</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">一本の蝋燭 / 平穏な年月</t>
+          <t xml:space="preserve">端境期</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuły rozdziałów</t>
+          <t xml:space="preserve">Święta i obrzędy</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Lato · 2 Szkoła · 3 Wigilia · 4 Marzanna</t>
+          <t xml:space="preserve">kapliczka</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6618,52 +6619,52 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Przydrożna kapliczka — ważny motyw, zawsze ten sam wyraz. es „humilladero” (decyzja autora; „capilla” to budynek).</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Summer · School · Christmas Eve · Marzanna</t>
+          <t xml:space="preserve">wayside shrine</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sommer · Schule · Heiligabend · Marzanna</t>
+          <t xml:space="preserve">Bildstock</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verano · La escuela · Nochebuena · Marzanna</t>
+          <t xml:space="preserve">humilladero</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verão · A escola · Véspera de Natal · Marzanna</t>
+          <t xml:space="preserve">oratório</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">L’été · L’école · Le réveillon · Marzanna</t>
+          <t xml:space="preserve">oratoire</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estate · La scuola · La Vigilia · Marzanna</t>
+          <t xml:space="preserve">edicola votiva</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Léto · Škola · Štědrý večer · Morana</t>
+          <t xml:space="preserve">kaplička</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leto · Škola · Štedrý večer · Morena</t>
+          <t xml:space="preserve">kaplnka</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">夏・学校・クリスマス・イブ・マルザンナ</t>
+          <t xml:space="preserve">道端の祠</t>
         </is>
       </c>
     </row>
@@ -6675,62 +6676,62 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 Tartak · 6 Samo południe · 7 Zielone Świątki · 8 Chude lato</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Prolog: Zapadlina</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Sawmill · High Noon · Pentecost · The Lean Summer</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Das Sägewerk · Hoher Mittag · Pfingsten · Der magere Sommer</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El aserradero · Mediodía · Pentecostés · El verano flaco</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A serraria · Meio-dia em ponto · Pentecostes · O verão magro</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La scierie · En plein midi · La Pentecôte · L’été maigre</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La segheria · Mezzogiorno in punto · Pentecoste · L’estate magra</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pila · Pravé poledne · Letnice · Hubené léto</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Píla · Pravé poludnie · Turíce · Chudobné leto</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">製材所・真昼・聖霊降臨祭・痩せた夏</t>
+          <t xml:space="preserve">Części prologu: Zapadlina, Chata, Dach, Zgliszcza, Miasto, Rodzina, Powrót, Jedna świeca, Lata spokoju.</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ザパドリナ</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6743,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 Wesele · 10 Narodziny · 11 Obława · 12 Czuwanie przy zmarłym</t>
+          <t xml:space="preserve">Chata / Dach / Zgliszcza</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6757,47 +6758,47 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Wedding · The Birth · The Hunt · The Wake</t>
+          <t xml:space="preserve">The Hut / The Roof / The Ashes</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Die Hochzeit · Die Geburt · Die Treibjagd · Die Totenwache</t>
+          <t xml:space="preserve">Die Hütte / Das Dach / Die Brandstätte</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La boda · El nacimiento · La batida · El velatorio</t>
+          <t xml:space="preserve">La cabaña / El tejado / Las cenizas</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">O casamento · O nascimento · A batida · O velório</t>
+          <t xml:space="preserve">A cabana / O telhado / As cinzas</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les noces · La naissance · La battue · La veillée funèbre</t>
+          <t xml:space="preserve">La cabane / Le toit / Les cendres</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le nozze · La nascita · La battuta · La veglia funebre</t>
+          <t xml:space="preserve">La capanna / Il tetto / Le macerie</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svatba · Narození · Hon · Bdění u mrtvého</t>
+          <t xml:space="preserve">Chata / Střecha / Spáleniště</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svadba · Narodenie · Poľovačka · Bdenie pri mŕtvom</t>
+          <t xml:space="preserve">Chata / Strecha / Spálenisko</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">婚礼・誕生・山狩り・通夜</t>
+          <t xml:space="preserve">小屋 / 屋根 / 焼け跡</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6810,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 Wspólny sen · 14 Kapliczki płoną · 15 Noc Kupały · 16 W głąb boru</t>
+          <t xml:space="preserve">Miasto / Rodzina / Powrót</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6824,47 +6825,47 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Shared Dream · The Shrines Burn · Kupala Night · Into the Forest</t>
+          <t xml:space="preserve">The Town / The Family / The Return</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Der gemeinsame Traum · Die Bildstöcke brennen · Kupalanacht · Tief in den Wald</t>
+          <t xml:space="preserve">Die Stadt / Die Familie / Die Heimkehr</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El sueño compartido · Arden las capillas · La noche de Kupala · Bosque adentro</t>
+          <t xml:space="preserve">La ciudad / La familia / El regreso</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">O sonho partilhado · Os oratórios ardem · A noite de Kupala · Floresta adentro</t>
+          <t xml:space="preserve">A cidade / A família / O regresso</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le rêve partagé · Les calvaires brûlent · La nuit de Kupala · Au cœur de la forêt</t>
+          <t xml:space="preserve">La ville / La famille / Le retour</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il sogno condiviso · Bruciano le edicole · La notte di Kupala · Nel cuore del bosco</t>
+          <t xml:space="preserve">La città / La famiglia / Il ritorno</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Společný sen · Kapličky hoří · Kupalská noc · Do hloubi boru</t>
+          <t xml:space="preserve">Město / Rodina / Návrat</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spoločný sen · Kaplnky horia · Kupadelná noc · Do hĺbky boru</t>
+          <t xml:space="preserve">Mesto / Rodina / Návrat</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">共に見る夢・燃える祠・クパーラの夜・森の奥へ</t>
+          <t xml:space="preserve">町 / 家族 / 帰還</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6877,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 Rozmowa w borze · 18 Wybór · 19 Świt · 20 Ostatnia noc</t>
+          <t xml:space="preserve">Jedna świeca / Lata spokoju</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6891,59 +6892,59 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Talk in the Forest · The Choice · Dawn · The Last Night</t>
+          <t xml:space="preserve">One Candle / Quiet Years</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ein Gespräch im Wald · Die Wahl · Morgengrauen · Die letzte Nacht</t>
+          <t xml:space="preserve">Eine Kerze / Ruhige Jahre</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conversación en el bosque · La elección · El alba · La última noche</t>
+          <t xml:space="preserve">Una vela / Años de calma</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conversa na floresta · A escolha · A aurora · A última noite</t>
+          <t xml:space="preserve">Uma vela / Anos de paz</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Une conversation dans la forêt · Le choix · L’aube · La dernière nuit</t>
+          <t xml:space="preserve">Une seule bougie / Les années paisibles</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colloquio nel bosco · La scelta · L’alba · L’ultima notte</t>
+          <t xml:space="preserve">Una candela / Anni di pace</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rozhovor v boru · Volba · Svítání · Poslední noc</t>
+          <t xml:space="preserve">Jedna svíce / Léta klidu</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rozhovor v bore · Voľba · Úsvit · Posledná noc</t>
+          <t xml:space="preserve">Jedna sviečka / Roky pokoja</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">森での対話・選択・夜明け・最後の夜</t>
+          <t xml:space="preserve">一本の蝋燭 / 平穏な年月</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zakończenia</t>
+          <t xml:space="preserve">Tytuły rozdziałów</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Młody dąb</t>
+          <t xml:space="preserve">1 Lato · 2 Szkoła · 3 Wigilia · 4 Marzanna</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6953,64 +6954,64 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granica, żołądź zasadzony, Marysia wróciła.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Young Oak</t>
+          <t xml:space="preserve">Summer · School · Christmas Eve · Marzanna</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Die junge Eiche</t>
+          <t xml:space="preserve">Sommer · Schule · Heiligabend · Marzanna</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El roble joven</t>
+          <t xml:space="preserve">Verano · La escuela · Nochebuena · Marzanna</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">O carvalho jovem</t>
+          <t xml:space="preserve">Verão · A escola · Véspera de Natal · Marzanna</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le jeune chêne</t>
+          <t xml:space="preserve">L’été · L’école · La veillée de Noël · Marzanna</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La giovane quercia</t>
+          <t xml:space="preserve">Estate · La scuola · La Vigilia · Marzanna</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mladý dub</t>
+          <t xml:space="preserve">Léto · Škola · Štědrý večer · Morana</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mladý dub</t>
+          <t xml:space="preserve">Leto · Škola · Štedrý večer · Morena</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">若い樫</t>
+          <t xml:space="preserve">夏・学校・聖夜・マジャンナ</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zakończenia</t>
+          <t xml:space="preserve">Tytuły rozdziałów</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z dziadkiem Maćkiem</t>
+          <t xml:space="preserve">5 Tartak · 6 Samo południe · 7 Zielone Świątki · 8 Chude lato</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -7020,64 +7021,64 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granica, żołądź, Marysia odchodzi z umarłymi.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">With Grandfather Maciek</t>
+          <t xml:space="preserve">The Sawmill · High Noon · Whitsun · The Lean Summer</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mit Großvater Maciek</t>
+          <t xml:space="preserve">Das Sägewerk · Mittagsstunde · Pfingsten · Der magere Sommer</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Con el abuelo Maciek</t>
+          <t xml:space="preserve">El aserradero · Mediodía · Pentecostés · El verano magro</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Com o avô Maciek</t>
+          <t xml:space="preserve">A serraria · Meio-dia em ponto · Pentecostes · O verão magro</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avec grand-père Maciek</t>
+          <t xml:space="preserve">La scierie · En plein midi · La Pentecôte · L’été maigre</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Con nonno Maciek</t>
+          <t xml:space="preserve">La segheria · Mezzogiorno in punto · Pentecoste · L’estate magra</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S dědečkem Maćkem</t>
+          <t xml:space="preserve">Pila · Pravé poledne · Letnice · Hubené léto</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S dedkom Maćkom</t>
+          <t xml:space="preserve">Píla · Pravé poludnie · Turíce · Chudobné leto</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">マチェクじいさんと共に</t>
+          <t xml:space="preserve">製材所・真昼・聖霊降臨祭・不作の夏</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zakończenia</t>
+          <t xml:space="preserve">Tytuły rozdziałów</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Słowo za słowo</t>
+          <t xml:space="preserve">9 Wesele · 10 Narodziny · 11 Obława · 12 Czuwanie przy zmarłym</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -7087,64 +7088,64 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granica bez żołędzia, Marysia wróciła.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Word for Word</t>
+          <t xml:space="preserve">The Wedding · The Birth · The Hunt · The Wake</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wort um Wort</t>
+          <t xml:space="preserve">Die Hochzeit · Die Geburt · Die Treibjagd · Die Totenwache</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palabra por palabra</t>
+          <t xml:space="preserve">La boda · El nacimiento · La batida · El velatorio</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palavra por palavra</t>
+          <t xml:space="preserve">O casamento · O nascimento · A caçada · O velório</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parole contre parole</t>
+          <t xml:space="preserve">Les noces · La naissance · La battue · La veillée funèbre</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parola per parola</t>
+          <t xml:space="preserve">Le nozze · La nascita · La battuta · La veglia funebre</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slovo za slovo</t>
+          <t xml:space="preserve">Svatba · Narození · Hon · Bdění u mrtvého</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slovo za slovo</t>
+          <t xml:space="preserve">Svadba · Narodenie · Poľovačka · Bdenie pri mŕtvom</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">言葉には言葉を</t>
+          <t xml:space="preserve">婚礼・誕生・山狩り・通夜</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zakończenia</t>
+          <t xml:space="preserve">Tytuły rozdziałów</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedno dziecko na pokolenie</t>
+          <t xml:space="preserve">13 Wspólny sen · 14 Kapliczki płoną · 15 Noc Kupały · 16 W głąb boru</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -7154,64 +7155,64 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granica bez żołędzia, bez Marysi.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">One Child a Generation</t>
+          <t xml:space="preserve">The Shared Dream · The Shrines Burn · Kupala Night · Into the Forest</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ein Kind pro Generation</t>
+          <t xml:space="preserve">Der gemeinsame Traum · Die Bildstöcke brennen · Kupalanacht · Tief in den Wald</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un niño por generación</t>
+          <t xml:space="preserve">El sueño compartido · Arden las capillas · La noche de Kupala · Bosque adentro</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma criança por geração</t>
+          <t xml:space="preserve">O sonho compartilhado · Os oratórios ardem · A noite de Kupala · Floresta adentro</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un enfant par génération</t>
+          <t xml:space="preserve">Le rêve partagé · Les oratoires brûlent · La nuit de Kupala · Au cœur de la forêt</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un bambino per generazione</t>
+          <t xml:space="preserve">Il sogno condiviso · Bruciano le edicole · La notte di Kupala · Nel cuore del bosco</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedno dítě za pokolení</t>
+          <t xml:space="preserve">Společný sen · Kapličky hoří · Kupalská noc · Do hloubi boru</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedno dieťa za pokolenie</t>
+          <t xml:space="preserve">Spoločný sen · Kaplnky horia · Kupalova noc · Do hĺbky boru</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">一世代に一人の子</t>
+          <t xml:space="preserve">共に見る夢・燃える祠・クパーラの夜・森の奥へ</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zakończenia</t>
+          <t xml:space="preserve">Tytuły rozdziałów</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Za płotem</t>
+          <t xml:space="preserve">17 Rozmowa w borze · 18 Wybór · 19 Świt · 20 Ostatnia noc</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -7221,52 +7222,52 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromir zostaje Panem Lasu, Marysia wróciła.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyond the Fence</t>
+          <t xml:space="preserve">A Talk in the Forest · The Choice · Dawn · The Last Night</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hinter dem Zaun</t>
+          <t xml:space="preserve">Ein Gespräch im Wald · Die Wahl · Morgengrauen · Die letzte Nacht</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tras la cerca</t>
+          <t xml:space="preserve">Conversación en el bosque · La elección · El alba · La última noche</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Além da cerca</t>
+          <t xml:space="preserve">Conversa na floresta · A escolha · A aurora · A última noite</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derrière la clôture</t>
+          <t xml:space="preserve">Une conversation dans la forêt · Le choix · L’aube · La dernière nuit</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oltre lo steccato</t>
+          <t xml:space="preserve">Colloquio nel bosco · La scelta · L’alba · L’ultima notte</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Za plotem</t>
+          <t xml:space="preserve">Rozhovor v boru · Volba · Svítání · Poslední noc</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Za plotom</t>
+          <t xml:space="preserve">Rozhovor v bore · Voľba · Úsvit · Posledná noc</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">垣根の向こう</t>
+          <t xml:space="preserve">森での対話・選択・夜明け・最後の夜</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7279,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idziemy do domu, tato</t>
+          <t xml:space="preserve">Młody dąb</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -7288,52 +7289,52 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromir odchodzi w bór z Marysią.</t>
+          <t xml:space="preserve">Granica, żołądź zasadzony, Marysia wróciła.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Let’s Go Home, Papa</t>
+          <t xml:space="preserve">The Young Oak</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wir gehen nach Hause, Papa</t>
+          <t xml:space="preserve">Die junge Eiche</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vamos a casa, papá</t>
+          <t xml:space="preserve">El roble joven</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vamos para casa, papai</t>
+          <t xml:space="preserve">O carvalho jovem</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">On rentre à la maison, papa</t>
+          <t xml:space="preserve">Le jeune chêne</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andiamo a casa, papà</t>
+          <t xml:space="preserve">La giovane quercia</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jdeme domů, tati</t>
+          <t xml:space="preserve">Mladý dub</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ideme domov, ocko</t>
+          <t xml:space="preserve">Mladý dub</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">おうちに帰ろう、とうさん</t>
+          <t xml:space="preserve">若い樫</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7346,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las, którego nie ma</t>
+          <t xml:space="preserve">Z dziadkiem Maćkiem</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7355,52 +7356,52 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pożar boru, Marysia wróciła.</t>
+          <t xml:space="preserve">Granica, żołądź, Marysia odchodzi z umarłymi.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Forest That Is No More</t>
+          <t xml:space="preserve">With Grandfather Maciek</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Der Wald, den es nicht mehr gibt</t>
+          <t xml:space="preserve">Mit Großvater Maciek</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El bosque que ya no existe</t>
+          <t xml:space="preserve">Con el abuelo Maciek</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A floresta que já não existe</t>
+          <t xml:space="preserve">Com o avô Maciek</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La forêt qui n’est plus</t>
+          <t xml:space="preserve">Avec grand-père Maciek</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il bosco che non c’è più</t>
+          <t xml:space="preserve">Con nonno Maciek</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les, který už není</t>
+          <t xml:space="preserve">S dědečkem Maćkem</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les, ktorý už nie je</t>
+          <t xml:space="preserve">S dedkom Maćkom</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">もうない森</t>
+          <t xml:space="preserve">マチェクじいさんと共に</t>
         </is>
       </c>
     </row>
@@ -7412,67 +7413,402 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Słowo za słowo</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granica bez żołędzia, Marysia wróciła.</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Word for a Word</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wort um Wort</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Palabra por palabra</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Palavra por palavra</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parole contre parole</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parola per parola</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slovo za slovo</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slovo za slovo</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">言葉には言葉を</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakończenia</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jedno dziecko na pokolenie</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granica bez żołędzia, bez Marysi.</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One Child a Generation</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ein Kind pro Generation</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un niño por generación</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uma criança por geração</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un enfant par génération</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un bambino per generazione</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jedno dítě za pokolení</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jedno dieťa za pokolenie</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一世代に一人の子</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakończenia</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Za płotem</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaromir zostaje Panem Lasu, Marysia wróciła.</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyond the Fence</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hinter dem Zaun</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tras la cerca</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Além da cerca</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Derrière la clôture</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oltre lo steccato</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Za plotem</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Za plotom</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">垣根の向こう</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakończenia</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idziemy do domu, tato</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaromir odchodzi w bór z Marysią.</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Let’s Go Home, Papa</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wir gehen nach Hause, Papa</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vamos a casa, papá</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vamos para casa, papai</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On rentre à la maison, papa</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andiamo a casa, papà</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jdeme domů, tati</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ideme domov, ocko</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">おうちに帰ろう、とうさん</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakończenia</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las, którego nie ma</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pożar boru, Marysia wróciła.</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Forest That Is No More</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Wald, den es nicht mehr gibt</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El bosque que ya no existe</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A floresta que já não existe</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La forêt qui n’est plus</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Il bosco che non c’è più</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les, který už není</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les, ktorý už nie je</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">もうない森</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakończenia</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ciepły popiół</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Pożar boru, bez Marysi.</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Warm Ashes</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Warme Asche</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ceniza tibia</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cinza morna</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cendres tièdes</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="J115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cenere tiepida</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="K115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teplý popel</t>
         </is>
       </c>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="L115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teplý popol</t>
         </is>
       </c>
-      <c r="M110" s="2" t="inlineStr">
+      <c r="M115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">温かい灰</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M110"/>
+  <autoFilter ref="A1:M115"/>
 </worksheet>
 </file>
 
@@ -7569,6 +7905,441 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zasady</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jak nazwy zachowują się w zdaniu (odmiana, rodzajniki, wołacz, polskie znaki) — arkusz „Zasady językowe”.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="140" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zasady językowe dla tłumaczy „Mała wioska” / „Little village”</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arkusz uzupełnia słowniczek. Rejestr: literacki, lekko archaiczny, wiejski, XIX wiek. Bez słownictwa z gier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zasady wspólne</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Imiona zostają polskie (w ja: katakana). Wyrazy pokrewieństwa i tytuły się tłumaczy (dziadek, babka, stary, pan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Znaki diakrytyczne: w językach łacińskich zachować wszystkie polskie litery (ś, ł, ó, ż, ć, ę): Staś, Kaśka, Józek, Wójcik, Dobrosław, Maćka. Font obsługuje Latin Extended-A, a tak robią wydawcy przekładów literatury polskiej (Tokarczuk, Sienkiewicz). Nie upraszczać (Stas, Kaska), bo raz uproszczonego imienia nie da się już ujednolicić. Jedyny wyjątek: w cs/sk „Staš” (decyzja autora). Ewentualną wskazówkę wymowy dać raz, w Zapiskach lub w „O grze”, nie w tekście.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Wielkie litery idą za polskim tekstem prozy, nie za tytułem karty. Wielką literą piszemy: Pan Lasu, Borowy, Stary Dąb, Bukowy Grzbiet, Południca, Ubożę oraz Licho, gdy jest nazwane. Małą: topielec, starzec w kapeluszu z mchu, zielarka, żytnia baba, biały wilk, mamuny, rusałki, strzyga, odmieniec, błędnice, ogniki. W tabeli angielskie i francuskie formy mają wielkie litery, bo to tytuły kart. W prozie te same wyrazy piszemy małą literą (en „the old man in the moss hat stood…”).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Wołacz: polskie formy (Marysiu!, Jaromirze!, dziadku!, Antku!, babko!, tato!) w językach bez wołacza zamieniamy na mianownik. Wołacz mają tylko cs i (szczątkowo) ja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Rodzaje do pilnowania: licho i ubożę są nijakie (en „it”, de „das”). Strzyga jest gramatycznie żeńska, ale tu chodzi o zmarłego starego Wójcika, więc zaimki osobowe męskie. Starzec, Pan Lasu i Borowy to ta sama istota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Angielski (en)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Tytuł przed imieniem wielką literą: Grandfather Maciek, Grandmother Marianna, Mr Ignacy, Mr Urbaniak. „Old” małą: old Staś, old Wójcik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• W zwrocie: „Grandfather!” (także do obcego starca), „Papa!” (Marysia do ojca).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Dzierżawczy: Staś’s, Maciek’s, Marysia’s. „U Stasiowych” to „at Staś’s”. Rodzina z nazwiska: the Kowalczyks, the Wójciks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Bez rodzajnika przy imionach. Z rodzajnikiem przy istotach: the Lord of the Forest, the licho, the white wolf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Niemiecki (de)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Dopełniacz na -s: Jaromirs, Hankas, Marysias, Macieks, Anteks, Józeks. Imiona na ś/s/sz/z biorą apostrof albo konstrukcję z rodzajnikiem: Staś’ Hof, der Hund des alten Staś. Nigdy „Staśs”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Liczba mnoga rodzin tylko od nazwisk: die Kowalczyks, die Wójciks. Domownicy Stasia to „die Familie des alten Staś” albo „bei Staś’ Leuten”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• „Die Wójcikowa” (polska forma żeńska z rodzajnikiem) jest dopuszczalna, ale trzeba jej używać konsekwentnie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• W zwrocie: „Großvater!”, „Herr Ignacy!”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hiszpański (es), portugalski BR (pt), francuski (fr), włoski (it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Narracja z rodzajnikiem, zwrot bez: es „el abuelo Maciek” / „¡abuelo!”; pt „o avô Maciek” / „vovô!”; fr „grand-père Maciek” (bez rodzajnika, jak po francusku) / „grand-père !”; it „nonno Maciek” (narracja i zwrot). Tytuły małą literą: el señor Urbaniak, don Ignacy, monsieur Urbaniak, il maestro Ignacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• pt-BR: w narracji literackiej bez rodzajnika przed samym imieniem (Jaromir disse), wyjątek to frazy potoczne w dialogu. Formy brazylijskie: compartilhado, não partilhado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Rodziny z nazwiska: los Kowalczyk, os Kowalczyk, les Kowalczyk, i Kowalczyk (nazwisko nieodmienne). Od imienia: los de Staś / en casa de Staś, a família de Staś, ceux de chez Staś, quelli di Staś.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• fr: przed imieniem zaczynającym się samogłoską stawiamy elizję („l’histoire d’Antek”, „d’Andrzej”), ale nie przed „h” w Hanka („de Hanka”).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Tytuły kart w es/pt/it: wielka litera tylko na początku (El viejo del sombrero de musgo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Czeski (cs) i słowacki (sk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Imiona odmieniamy, zachowując polską pisownię tematu (temat jak w polskich przypadkach zależnych: Maćka, Antka, Stasia):</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      – -ek z ruchomym e: Antek – Antka – Antkovi – Antkem, wołacz cs „Antku!”. Tak samo Franek, Józek, Bartek. Maciek – Maćka – Maćkovi – Maćkem (sk Maćkom).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      – Jaromir – Jaromira – Jaromirovi – Jaromirem (sk -om), wołacz cs „Jaromire!”. Dobrosław – Dobrosława. Ignacy (odmiana przymiotnikowa): Ignacyho, Ignacymu, Ignacym.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      – Żeńskie na -a: Hanka – Hanky – Hance – Hanku – Hankou, wołacz cs „Hanko!”. Kaśka – Kaśky – Kaśce (sk Kaśke). Jagna – Jagny – Jagně (sk Jagne).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      – Staś zapisujemy „Staš” (decyzja autora): cs Staše – Stašovi – Stašem, wołacz „Staši!”, „u Stašových”; sk Staša – Stašovi – Stašom, „u Stašovcov”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Nazwiska żeńskie: -ová / -ová: Wójciková (żona i córka). Rodziny: cs Wójcikovi, Kowalczykovi; sk Wójcikovci, Kowalczykovci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Nazwy wsi: cs v Zapadlině, z Bukowce, v Bukowci; sk v Zapadline, z Bukowca, v Bukowci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• sk nie ma wołacza: „Jaromir!”, „Hanka!”, „dedko!”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Istoty z rodzimym odpowiednikiem piszemy rodzimą formą i małą literą: polednice/poludnica, půlnočnice/polnočnica, cs utopec / sk utopenec, rusalky, bludičky, světýlka/svetielka, planetník.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japoński (ja)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Katakana wg wymowy, nie pisowni: ś, si, sz → シ; cz, ć → チ; rz, ż → ジ (Andrzej アンジェイ, Marzanna マジャンナ); ł → ワ-row (Dobrosław ドブロスワフ, Płanetnik プワネトニク); w → ヴ (ヤドヴィシャ, ブコヴィエツ); ó, u → ウ; ę/ą przed spółgłoską → エン/オン.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Nazwy istot pozostawione po polsku (strzyga, licho, mamuny) zapisujemy katakaną bez tłumaczenia, a wyjaśnia je karta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Sufiksy: starcy dostają 〜じいさん (マチェクじいさん, スタシじいさん, ヴイチクじいさん), staruszki 〜ばあさん (マリアンナばあさん), nauczyciel 〜先生 (イグナツィ先生), kupiec 〜の旦那 (ウルバニャクの旦那), żona 〜のおかみさん. Nie mieszać kanji 爺 z hiraganą. Dzieci i rówieśników zostawiamy bez sufiksu (ヤロミル, ハンカ, アンテク), a dziecięce czułe formy tylko w dialogu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Rodzina: 〜家 (スタシ家, コヴァルチク家).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Zwroty: 「おじいさん！」, 「とうさん」 (Marysia do ojca), 「マリシャ！」.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Święta: Wigilia 聖夜 (nie クリスマス・イブ), rozdziały 第一章 itd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Otwarte pytania do natywnych tłumaczy</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. cs/sk, odmiana Marysia/Jadwisia (-sia): wzór -ia (Marysie, Marysii, wołacz „Marysio!”) czy inny? Przymiotnik dzierżawczy „Marysiin” czy omówienie dopełniaczem? W słowniczku na razie stoi „Marysiny/Marysine”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Hasła do dopisania później (są w tekście, rzadziej): błędne ognie/ogniki z prologu, dziedzic, kożuch/kapota, drużba, szarwark, ruble srebrem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rozstrzygnięte przez autora</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• en „Mr Ignacy” (nie „Master”).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• cs/sk „Staš” zamiast „Staś”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• cs topielec = „utopec”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• es kapliczka = „humilladero”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• sk „podhodenec” zostaje: podrzutek, dziecko podrzucone komuś, coś podrzuconego, obcego.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Dopisane hasła: Borowy, świta, gajowy, opłatek, kołacz.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/tools/Translations/slowniczek.xlsx
+++ b/tools/Translations/slowniczek.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Zasady językowe" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Słowniczek'!$A$1:$M$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Słowniczek'!$A$1:$M$120</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -924,7 +924,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zdrobnienie od Maria — wyjaśnić raz przy chrzcie, potem tylko „Marysia”. Wołacz „Marysiu!” → „Marysia!” (en, de, es, pt, fr, it, sk), ja „マリシャ！”. cs: wołacz i odmiana do decyzji natywnego tłumacza (propozycja: Marysie – Marysii – Marysii – Marysio!); dzierżawcze cs/sk („Marysiny/Marysine”) do sprawdzenia — wzór od imion na -ia daje „Marysiin/Marysiina”, bezpieczniej użyć dopełniacza („dřeváky Marysie”).</t>
+          <t xml:space="preserve">Zdrobnienie od Maria — wyjaśnić raz przy chrzcie, potem tylko „Marysia”. Wołacz „Marysiu!” → „Marysia!” (en, de, es, pt, fr, it, sk), ja „マリシャ！”. cs/sk: pisownia polska, odmiana jak imiona na -ia (Maria, Julia). cs: Marysia – Marysie – Marysii – Marysii – wołacz „Marysio!” – o Marysii – s Marysií; lm. Marysie, dop. lm. Marysií (r18: „tucet Marysií”). sk: Marysia – Marysie – Marysii – Marysiu – o Marysii – s Marysiou; wołacz = mianownik „Marysia!”; lm. Marysie, dop. lm. Marysií. Przymiotnik dzierżawczy (cs/sk „Marysiin”) jest poprawny, ale nieczytelny (podwójne i) — zawsze dopełniacz: cs „dřeváky Marysie”, sk „dreváky Marysie”. Nigdy „Marysin(a)/Marysiny/Marysine” (to od imienia „Marysa”) ani polskich form „Marysi/Marysię/Marysią”.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Żona Antka.</t>
+          <t xml:space="preserve">Żona Antka. cs/sk odmiana jak Marysia (wzór -ia): cs Jadwisia – Jadwisie – Jadwisii – Jadwisii – wołacz „Jadwisio!” – o Jadwisii – s Jadwisií; sk Jadwisia – Jadwisie – Jadwisii – Jadwisiu – o Jadwisii – s Jadwisiou (wołacz = mianownik). Dzierżawczość dopełniaczem: cs „korále Jadwisie”, sk „korálky Jadwisie”; nie „Jadwisin(a)”.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leśniczy z dubeltówką przy obławie na wilka. Imię zostaje, „gajowy” tłumaczyć.</t>
+          <t xml:space="preserve">Gajowy z dworu (strażnik lasu i zwierzyny w służbie dziedzica, niższy rangą od leśniczego), z dubeltówką; prowadzi obławę na wilka (r11), potem pilnuje roboty Urbaniaka (r14). Imię zostaje, „gajowy” tłumaczyć słowem na dworskiego strażnika łowiska, nie na wykształconego leśnika.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Förster Pawlik</t>
+          <t xml:space="preserve">der Heger Pawlik</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">le garde-forestier Pawlik</t>
+          <t xml:space="preserve">le garde-chasse Pawlik</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2249,67 +2249,67 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miejsca</t>
+          <t xml:space="preserve">Postacie</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">dziedzic</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wieś bohaterów. Brzmi jak prawdziwa miejscowość — nie tłumaczyć.</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zapadlina</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ザパドリナ</t>
+          <t xml:space="preserve">Właściciel majątku i wsi (szlachcic z dworu); w tekście nie pojawia się osobiście. Prolog: oddaje pustki pod karczunek za niski czynsz; r4: sprzedał Urbaniakowi wyrąb; r11: „Jaśnie pan dziedzic zarządza obławę”, płaci za skórę wilka. „Jaśnie pan” = uniżona formuła chłopa lub sługi: en „His Lordship the squire”, de „der gnädige Herr”, cs/sk „milostpán”, ja 地主様. „Dwór” (strzelcy z dworu, dworska stodoła): en the manor, de der Gutshof, cs panský dvůr, sk kaštieľ. Bez współczesnych słów typu „właściciel ziemski”.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the squire</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">der Gutsherr</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el terrateniente</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o senhor das terras</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le seigneur</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">il padrone</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">statkář</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zemepán</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地主</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2331,52 +2331,52 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wieś z kościołem i targiem.</t>
+          <t xml:space="preserve">Wieś bohaterów. Brzmi jak prawdziwa miejscowość — nie tłumaczyć.</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowiec</t>
+          <t xml:space="preserve">Zapadlina</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ブコヴィエツ</t>
+          <t xml:space="preserve">ザパドリナ</t>
         </is>
       </c>
     </row>
@@ -2388,62 +2388,62 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukowy Grzbiet</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nazwa opisowa — tłumaczyć.</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Beech Ridge</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Buchenkamm</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la Cresta de las Hayas</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Serra das Faias</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la Crête des Hêtres</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la Cresta dei Faggi</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bukový hřbet</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bukový hrebeň</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ブナの尾根</t>
+          <t xml:space="preserve">Wieś z kościołem i targiem.</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukowiec</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ブコヴィエツ</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stary Dąb</t>
+          <t xml:space="preserve">Bukowy Grzbiet</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2465,52 +2465,52 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konkretne drzewo — wielkimi literami.</t>
+          <t xml:space="preserve">Nazwa opisowa — tłumaczyć.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Old Oak</t>
+          <t xml:space="preserve">Beech Ridge</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Alte Eiche</t>
+          <t xml:space="preserve">Buchenkamm</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el Viejo Roble</t>
+          <t xml:space="preserve">la Cresta de las Hayas</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o Velho Carvalho</t>
+          <t xml:space="preserve">a Serra das Faias</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le Vieux Chêne</t>
+          <t xml:space="preserve">la Crête des Hêtres</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Vecchia Quercia</t>
+          <t xml:space="preserve">la Cresta dei Faggi</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starý dub</t>
+          <t xml:space="preserve">Bukový hřbet</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starý dub</t>
+          <t xml:space="preserve">Bukový hrebeň</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">老樫</t>
+          <t xml:space="preserve">ブナの尾根</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bór</t>
+          <t xml:space="preserve">Stary Dąb</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2532,52 +2532,52 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stary, ciemny las iglasty — zawsze ten sam wyraz w całej grze.</t>
+          <t xml:space="preserve">Konkretne drzewo — wielkimi literami.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the forest</t>
+          <t xml:space="preserve">the Old Oak</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Wald</t>
+          <t xml:space="preserve">die Alte Eiche</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el bosque</t>
+          <t xml:space="preserve">el Viejo Roble</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a floresta</t>
+          <t xml:space="preserve">o Velho Carvalho</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la forêt</t>
+          <t xml:space="preserve">le Vieux Chêne</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il bosco</t>
+          <t xml:space="preserve">la Vecchia Quercia</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bor</t>
+          <t xml:space="preserve">Starý dub</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bór</t>
+          <t xml:space="preserve">Starý dub</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">森</t>
+          <t xml:space="preserve">老樫</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">baza na starym bzie</t>
+          <t xml:space="preserve">bór</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2599,52 +2599,52 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kryjówka chłopców w dziupli starego bzu.</t>
+          <t xml:space="preserve">Stary, ciemny las iglasty — zawsze ten sam wyraz w całej grze.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the den in the old elder</t>
+          <t xml:space="preserve">the forest</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">das Versteck im alten Holunder</t>
+          <t xml:space="preserve">der Wald</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la guarida del viejo saúco</t>
+          <t xml:space="preserve">el bosque</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o esconderijo no velho sabugueiro</t>
+          <t xml:space="preserve">a floresta</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la cabane du vieux sureau</t>
+          <t xml:space="preserve">la forêt</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il rifugio nel vecchio sambuco</t>
+          <t xml:space="preserve">il bosco</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">skrýš ve starém bezu</t>
+          <t xml:space="preserve">bor</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">skrýša v starom baze</t>
+          <t xml:space="preserve">bór</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">古いニワトコの隠れ家</t>
+          <t xml:space="preserve">森</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">młodnik</t>
+          <t xml:space="preserve">baza na starym bzie</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2666,64 +2666,64 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Młody las pod borem.</t>
+          <t xml:space="preserve">Kryjówka chłopców w dziupli starego bzu.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the young wood</t>
+          <t xml:space="preserve">the den in the old elder</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">das Jungholz</t>
+          <t xml:space="preserve">das Versteck im alten Holunder</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el monte joven</t>
+          <t xml:space="preserve">la guarida del viejo saúco</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o mato novo</t>
+          <t xml:space="preserve">o esconderijo no velho sabugueiro</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le jeune bois</t>
+          <t xml:space="preserve">la cabane du vieux sureau</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il bosco giovane</t>
+          <t xml:space="preserve">il rifugio nel vecchio sambuco</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mlází</t>
+          <t xml:space="preserve">skrýš ve starém bezu</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mladina</t>
+          <t xml:space="preserve">skrýša v starom baze</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">若木の林</t>
+          <t xml:space="preserve">古いニワトコの隠れ家</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Istoty</t>
+          <t xml:space="preserve">Miejsca</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan Lasu</t>
+          <t xml:space="preserve">młodnik</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2733,52 +2733,52 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leszy. Zawsze wielkimi literami.</t>
+          <t xml:space="preserve">Młody las pod borem.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Lord of the Forest</t>
+          <t xml:space="preserve">the young wood</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Herr des Waldes</t>
+          <t xml:space="preserve">das Jungholz</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el Señor del Bosque</t>
+          <t xml:space="preserve">el monte joven</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o Senhor da Floresta</t>
+          <t xml:space="preserve">o mato novo</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le Seigneur de la Forêt</t>
+          <t xml:space="preserve">le jeune bois</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il Signore del Bosco</t>
+          <t xml:space="preserve">il bosco giovane</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pán lesa</t>
+          <t xml:space="preserve">mlází</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pán lesa</t>
+          <t xml:space="preserve">mladina</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">森の主</t>
+          <t xml:space="preserve">若木の林</t>
         </is>
       </c>
     </row>
@@ -2790,62 +2790,62 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borowy</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">Pan Lasu</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drugie, ludowe imię Pana Lasu (od „bór”), w tekście 7×, zawsze obok „Pan Lasu” jako ta sama istota. Wielką literą. cs/sk rodzimy przymiotnik „Borový” (odmiana: Borového, Borovému).</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Borowy</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Borowy</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Borowy</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Borowy</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Borowy</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Borowy</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Borový</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Borový</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ボロヴィ</t>
+          <t xml:space="preserve">Leszy. Zawsze wielkimi literami.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Lord of the Forest</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">der Herr des Waldes</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el Señor del Bosque</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o Senhor da Floresta</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le Seigneur de la Forêt</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">il Signore del Bosco</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pán lesa</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pán lesa</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">森の主</t>
         </is>
       </c>
     </row>
@@ -2857,62 +2857,62 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starzec w kapeluszu z mchu</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ludzka postać Pana Lasu.</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the Old Man in the Moss Hat</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">der Alte mit dem Moosshut</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el viejo del sombrero de musgo</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o velho do chapéu de musgo</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">le Vieillard au chapeau de mousse</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">il vecchio dal cappello di muschio</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stařec v klobouku z mechu</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Starec v klobúku z machu</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">苔の帽子の老人</t>
+          <t xml:space="preserve">Drugie, ludowe imię Pana Lasu (od „bór”), w tekście 7×, zawsze obok „Pan Lasu” jako ta sama istota. Wielką literą. cs/sk rodzimy przymiotnik „Borový” (odmiana: Borového, Borovému).</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borowy</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borový</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borový</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ボロヴィ</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topielec</t>
+          <t xml:space="preserve">Starzec w kapeluszu z mchu</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2934,52 +2934,52 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stwór z bagna, dusza utopionego bez księdza; we śnie przewraca gliniane garnki (motyw wodnika). W niemieckim tradycyjny odpowiednik (Wassermann — on też trzyma dusze pod garnkami); w czeskim ludowy śląsko-morawski „utopec” (decyzja autora). Uwaga: w prologu „topielce uwięzione pod mułem” to ogólnie utopieni — tam de „die Ertrunkenen”, en „the drowned”, cs „utopenci”. W prozie małą literą.</t>
+          <t xml:space="preserve">Ludzka postać Pana Lasu.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Drowned One</t>
+          <t xml:space="preserve">the Old Man in the Moss Hat</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Wassermann</t>
+          <t xml:space="preserve">der Alte mit dem Moosshut</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el Ahogado</t>
+          <t xml:space="preserve">el viejo del sombrero de musgo</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o Afogado</t>
+          <t xml:space="preserve">o velho do chapéu de musgo</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le Noyé</t>
+          <t xml:space="preserve">le Vieillard au chapeau de mousse</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">l’Annegato</t>
+          <t xml:space="preserve">il vecchio dal cappello di muschio</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">utopec</t>
+          <t xml:space="preserve">Stařec v klobouku z mechu</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">utopenec</t>
+          <t xml:space="preserve">Starec v klobúku z machu</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">水死霊</t>
+          <t xml:space="preserve">苔の帽子の老人</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stwór z zarośli</t>
+          <t xml:space="preserve">Topielec</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3001,52 +3001,52 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Stwór z bagna, dusza utopionego bez księdza; we śnie przewraca gliniane garnki (motyw wodnika). W niemieckim tradycyjny odpowiednik (Wassermann — on też trzyma dusze pod garnkami); w czeskim ludowy śląsko-morawski „utopec” (decyzja autora). Uwaga: w prologu „topielce uwięzione pod mułem” to ogólnie utopieni — tam de „die Ertrunkenen”, en „the drowned”, cs „utopenci”. W prozie małą literą.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Thing in the Thicket</t>
+          <t xml:space="preserve">the Drowned One</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">das Wesen aus dem Dickicht</t>
+          <t xml:space="preserve">der Wassermann</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Criatura de la maleza</t>
+          <t xml:space="preserve">el Ahogado</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Criatura do matagal</t>
+          <t xml:space="preserve">o Afogado</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Créature des fourrés</t>
+          <t xml:space="preserve">le Noyé</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Creatura della boscaglia</t>
+          <t xml:space="preserve">l’Annegato</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stvůra z houští</t>
+          <t xml:space="preserve">utopec</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stvora z húštiny</t>
+          <t xml:space="preserve">utopenec</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">藪の怪物</t>
+          <t xml:space="preserve">水死霊</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zielarka znad jeziora</t>
+          <t xml:space="preserve">Stwór z zarośli</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3068,52 +3068,52 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wiedźma, od której zaczęła się klątwa.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Herbwoman from the Lake</t>
+          <t xml:space="preserve">the Thing in the Thicket</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Kräuterfrau vom See</t>
+          <t xml:space="preserve">das Wesen aus dem Dickicht</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Herbolaria del lago</t>
+          <t xml:space="preserve">la Criatura de la maleza</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Erveira do lago</t>
+          <t xml:space="preserve">a Criatura do matagal</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">l’Herboriste du lac</t>
+          <t xml:space="preserve">la Créature des fourrés</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">l’Erborista del lago</t>
+          <t xml:space="preserve">la Creatura della boscaglia</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bylinkářka od jezera</t>
+          <t xml:space="preserve">stvůra z houští</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bylinkárka od jazera</t>
+          <t xml:space="preserve">stvora z húštiny</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">湖畔の薬草女</t>
+          <t xml:space="preserve">藪の怪物</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Południca</t>
+          <t xml:space="preserve">Zielarka znad jeziora</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3135,52 +3135,52 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">W czeskim i słowackim istnieje ta sama istota ludowa.</t>
+          <t xml:space="preserve">Wiedźma, od której zaczęła się klątwa.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lady Midday</t>
+          <t xml:space="preserve">the Herbwoman from the Lake</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Mittagsfrau</t>
+          <t xml:space="preserve">die Kräuterfrau vom See</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Dama del Mediodía</t>
+          <t xml:space="preserve">la Herbolaria del lago</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Dama do Meio-Dia</t>
+          <t xml:space="preserve">a Erveira do lago</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Dame de Midi</t>
+          <t xml:space="preserve">l’Herboriste du lac</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Signora del Mezzogiorno</t>
+          <t xml:space="preserve">l’Erborista del lago</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">polednice</t>
+          <t xml:space="preserve">bylinkářka od jezera</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poludnica</t>
+          <t xml:space="preserve">bylinkárka od jazera</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">真昼の女</t>
+          <t xml:space="preserve">湖畔の薬草女</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Północnica</t>
+          <t xml:space="preserve">Południca</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3202,52 +3202,52 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Para do Południcy — tłumaczona tak samo.</t>
+          <t xml:space="preserve">W czeskim i słowackim istnieje ta sama istota ludowa.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lady Midnight</t>
+          <t xml:space="preserve">Lady Midday</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Mitternachtsfrau</t>
+          <t xml:space="preserve">die Mittagsfrau</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Dama de la Medianoche</t>
+          <t xml:space="preserve">la Dama del Mediodía</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Dama da Meia-Noite</t>
+          <t xml:space="preserve">a Dama do Meio-Dia</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Dame de Minuit</t>
+          <t xml:space="preserve">la Dame de Midi</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Signora della Mezzanotte</t>
+          <t xml:space="preserve">la Signora del Mezzogiorno</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">půlnočnice</t>
+          <t xml:space="preserve">polednice</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">polnočnica</t>
+          <t xml:space="preserve">poludnica</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">真夜中の女</t>
+          <t xml:space="preserve">真昼の女</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rusałki</t>
+          <t xml:space="preserve">Północnica</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3269,52 +3269,52 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Słowo znane w większości języków.</t>
+          <t xml:space="preserve">Para do Południcy — tłumaczona tak samo.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalki</t>
+          <t xml:space="preserve">Lady Midnight</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rusalken</t>
+          <t xml:space="preserve">die Mitternachtsfrau</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalkas</t>
+          <t xml:space="preserve">la Dama de la Medianoche</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalkas</t>
+          <t xml:space="preserve">a Dama da Meia-Noite</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">roussalkas</t>
+          <t xml:space="preserve">la Dame de Minuit</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalke</t>
+          <t xml:space="preserve">la Signora della Mezzanotte</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalky</t>
+          <t xml:space="preserve">půlnočnice</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rusalky</t>
+          <t xml:space="preserve">polnočnica</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ルサルカたち</t>
+          <t xml:space="preserve">真夜中の女</t>
         </is>
       </c>
     </row>
@@ -3326,62 +3326,62 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mamuny</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">Rusałki</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brak odpowiedników — polska nazwa, wyjaśnia karta w zapiskach.</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamunas</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mamunen</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamunas</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamunas</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamounes</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamune</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamuny</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mamuny</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">マムナたち</t>
+          <t xml:space="preserve">Słowo znane w większości języków.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rusalki</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rusalken</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rusalkas</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rusalkas</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roussalkas</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rusalke</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rusalky</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rusalky</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ルサルカたち</t>
         </is>
       </c>
     </row>
@@ -3393,62 +3393,62 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odmieniec</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Mamuny</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dziecko podrzucone przez mamuny. sk „podhodenec” = podrzutek, dziecko podrzucone komuś, coś podrzuconego, obcego (potwierdzone przez autora).</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the changeling</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">der Wechselbalg</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el niño cambiado</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a criança trocada</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">le changelin</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">il bambino scambiato</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">podvrženec</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">podhodenec</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">取り替え子</t>
+          <t xml:space="preserve">Brak odpowiedników — polska nazwa, wyjaśnia karta w zapiskach.</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mamunas</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mamunen</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mamunas</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mamunas</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mamounes</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mamune</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mamuny</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mamuny</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">マムナたち</t>
         </is>
       </c>
     </row>
@@ -3460,62 +3460,62 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strzyga</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">Odmieniec</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polska nazwa (znana graczom m.in. z Wiedźmina). Rzeczownik żeński (de „die Strzyga”, es/pt/fr/it rodzajnik żeński), ale w tej opowieści strzygą jest zmarły stary Wójcik — zaimki osobowe męskie, gdy mowa o nim. L.mn. en „strzygas”, de „Strzygen”, cs/sk „strzygy”.</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">strzyga</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Strzyga</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">strzyga</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">strzyga</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">strzyga</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">strzyga</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">strzyga</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">strzyga</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ストシガ</t>
+          <t xml:space="preserve">Dziecko podrzucone przez mamuny. sk „podhodenec” = podrzutek, dziecko podrzucone komuś, coś podrzuconego, obcego (potwierdzone przez autora).</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the changeling</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">der Wechselbalg</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el niño cambiado</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a criança trocada</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le changelin</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">il bambino scambiato</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">podvrženec</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">podhodenec</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取り替え子</t>
         </is>
       </c>
     </row>
@@ -3527,62 +3527,62 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zmarły, który nie stygnie</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Strzyga</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuł karty przed odkryciem, że to strzyga.</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Dead Man Who Won’t Go Cold</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Der Tote, der nicht erkaltet</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El muerto que no se enfría</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O morto que não esfria</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le mort qui ne refroidit pas</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Il morto che non si raffredda</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mrtvý, který nechladne</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mŕtvy, ktorý nechladne</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冷えない死者</t>
+          <t xml:space="preserve">Polska nazwa (znana graczom m.in. z Wiedźmina). Rzeczownik żeński (de „die Strzyga”, es/pt/fr/it rodzajnik żeński), ale w tej opowieści strzygą jest zmarły stary Wójcik — zaimki osobowe męskie, gdy mowa o nim. L.mn. en „strzygas”, de „Strzygen”, cs/sk „strzygy”.</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strzyga</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strzyga</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strzyga</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strzyga</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strzyga</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strzyga</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strzyga</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strzyga</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ストシガ</t>
         </is>
       </c>
     </row>
@@ -3594,62 +3594,62 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licho</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">Zmarły, który nie stygnie</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polska nazwa; rodzaj nijaki (w tekście „ono/je”): en „it”, de „das Licho”, cs/sk nijaki. Wielką literą, gdy jest nazwane („Licho, co nie śpi”), małą w ogólnym „na każde licho”. Uwaga: we współczesnym czeskim i słowackim „lichý” znaczy głównie „nieparzysty, marny”; znaczenie „nieszczęście” (jak ros. лихо) do potwierdzenia przez natywnego.</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the licho</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">das Licho</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el licho</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o licho</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">le licho</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">il licho</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">licho</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">licho</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リホ</t>
+          <t xml:space="preserve">Tytuł karty przed odkryciem, że to strzyga.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Dead Man Who Won’t Go Cold</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Tote, der nicht erkaltet</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El muerto que no se enfría</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O morto que não esfria</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le mort qui ne refroidit pas</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Il morto che non si raffredda</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mrtvý, který nechladne</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mŕtvy, ktorý nechladne</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷えない死者</t>
         </is>
       </c>
     </row>
@@ -3661,62 +3661,62 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jednooka żebraczka</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Licho</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postać licha.</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the One-Eyed Beggar Woman</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">die einäugige Bettlerin</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la mendiga tuerta</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a mendiga caolha</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la mendiante borgne</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la mendicante orba</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jednooká žebračka</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jednooká žobráčka</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">片目の物乞い女</t>
+          <t xml:space="preserve">Polska nazwa; rodzaj nijaki (w tekście „ono/je”): en „it”, de „das Licho”, cs/sk nijaki. Wielką literą, gdy jest nazwane („Licho, co nie śpi”), małą w ogólnym „na każde licho”. Uwaga: we współczesnym czeskim i słowackim „lichý” znaczy głównie „nieparzysty, marny”; znaczenie „nieszczęście” (jak ros. лихо) do potwierdzenia przez natywnego.</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the licho</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">das Licho</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el licho</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o licho</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le licho</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">il licho</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">licho</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">licho</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">リホ</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Żytnia baba</t>
+          <t xml:space="preserve">Jednooka żebraczka</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3738,52 +3738,52 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">W niemieckim tradycyjny odpowiednik.</t>
+          <t xml:space="preserve">Postać licha.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Rye Mother</t>
+          <t xml:space="preserve">the One-Eyed Beggar Woman</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Roggenmuhme</t>
+          <t xml:space="preserve">die einäugige Bettlerin</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Vieja del Centeno</t>
+          <t xml:space="preserve">la mendiga tuerta</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Velha do Centeio</t>
+          <t xml:space="preserve">a mendiga caolha</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Vieille du Seigle</t>
+          <t xml:space="preserve">la mendiante borgne</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Vecchia della Segale</t>
+          <t xml:space="preserve">la mendicante orba</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">žitná bába</t>
+          <t xml:space="preserve">jednooká žebračka</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">žitná baba</t>
+          <t xml:space="preserve">jednooká žobráčka</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ライ麦の婆</t>
+          <t xml:space="preserve">片目の物乞い女</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobieta w życie</t>
+          <t xml:space="preserve">Żytnia baba</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3805,52 +3805,52 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuł karty przed rozpoznaniem żytniej baby.</t>
+          <t xml:space="preserve">W niemieckim tradycyjny odpowiednik.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Woman in the Rye</t>
+          <t xml:space="preserve">the Rye Mother</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Frau im Roggen</t>
+          <t xml:space="preserve">die Roggenmuhme</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la mujer del centeno</t>
+          <t xml:space="preserve">la Vieja del Centeno</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a mulher do centeio</t>
+          <t xml:space="preserve">a Velha do Centeio</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la femme dans le seigle</t>
+          <t xml:space="preserve">la Vieille du Seigle</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la donna nella segale</t>
+          <t xml:space="preserve">la Vecchia della Segale</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">žena v žitě</t>
+          <t xml:space="preserve">žitná bába</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">žena v raži</t>
+          <t xml:space="preserve">žitná baba</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ライ麦畑の女</t>
+          <t xml:space="preserve">ライ麦の婆</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Błędne ogniki</t>
+          <t xml:space="preserve">Kobieta w życie</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3872,52 +3872,52 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tytuł karty przed rozpoznaniem żytniej baby.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">will-o’-the-wisps</t>
+          <t xml:space="preserve">the Woman in the Rye</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Irrlichter</t>
+          <t xml:space="preserve">die Frau im Roggen</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuegos fatuos</t>
+          <t xml:space="preserve">la mujer del centeno</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fogos-fátuos</t>
+          <t xml:space="preserve">a mulher do centeio</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">feux follets</t>
+          <t xml:space="preserve">la femme dans le seigle</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuochi fatui</t>
+          <t xml:space="preserve">la donna nella segale</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bludičky</t>
+          <t xml:space="preserve">žena v žitě</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bludičky</t>
+          <t xml:space="preserve">žena v raži</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">鬼火</t>
+          <t xml:space="preserve">ライ麦畑の女</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Błędnice</t>
+          <t xml:space="preserve">Błędne ogniki</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3939,52 +3939,52 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kule światła nad bagnem w głębi boru, w każdej skulona mała postać, popiskują jak pisklęta; ze świty Pana Lasu. Nie ma utartej nazwy — wybrano słowa (a) inne niż dla błędnych ogników, (b) sugerujące małe istotki, (c) bez „panien/dziewic” (karta ich nie opisuje). cs/sk „světýlka/svetielka” to poświadczone ludowe nazwy błądzących świateł.</t>
+          <t xml:space="preserve">Światełka nad mokradłami pod wsią — dusze tych, co spalili zielarkę (karty ogniki_1, ogniki_2; r4, r12, r13, r16). W prozie małą literą, zwykle samo „ogniki”; w r13 skrótem „ognie” („Jak ognie dojdą do progu”) — te same światła, oddać tym samym wyrazem albo zwykłym „światła”. Nie mylić z błędnicami (r16: „Światła nie przypominały ogników znad mokradeł”) ani z ogólnym „błędne ognie” z prologu i r3 (osobne hasło).</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wisplings</t>
+          <t xml:space="preserve">will-o’-the-wisps</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Irrwische</t>
+          <t xml:space="preserve">Irrlichter</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">candelillas</t>
+          <t xml:space="preserve">fuegos fatuos</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">luzinhas errantes</t>
+          <t xml:space="preserve">fogos-fátuos</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">follettes</t>
+          <t xml:space="preserve">feux follets</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fiammelle erranti</t>
+          <t xml:space="preserve">fuochi fatui</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">světýlka</t>
+          <t xml:space="preserve">bludičky</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">svetielka</t>
+          <t xml:space="preserve">bludičky</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">迷い火</t>
+          <t xml:space="preserve">鬼火</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">świta (Pana Lasu)</t>
+          <t xml:space="preserve">błędne ognie (prolog, r3)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4006,52 +4006,52 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orszak istot Pana Lasu (rusałki, mamuny, błędnice). Małą literą. ja 眷属 = orszak bóstwa.</t>
+          <t xml:space="preserve">Ogólna nazwa zjawiska (ignis fatuus), nie istota. Prolog: Andrzej mówi „Nie żadne błędne ognie” i odrzuca zwykłe, przyrodnicze wyjaśnienie (Maciek myślał, że to gnijące drewno albo bagienne wyziewy). r3: porównanie lampionów („kołysały się jak błędne ognie”). Brać najzwyklejszą nazwę zjawiska w danym języku. Gdzie się da, inną niż tytuł karty „Błędne ogniki” (en marsh lights ≠ will-o’-the-wisps, cs/sk bludné ohně ≠ bludičky). W de/es/pt/fr/it/ja język ma jedną nazwę, więc może być ta sama co na karcie — po polsku też brzmi podobnie (ognie/ogniki). Nigdy wyrazów błędnic (wisplings, Irrwische, candelillas, luzinhas errantes, follettes, fiammelle erranti, světýlka, svetielka, 迷い火).</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the retinue</t>
+          <t xml:space="preserve">marsh lights</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">das Gefolge</t>
+          <t xml:space="preserve">Irrlichter</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el séquito</t>
+          <t xml:space="preserve">fuegos fatuos</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o séquito</t>
+          <t xml:space="preserve">fogos-fátuos</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le cortège</t>
+          <t xml:space="preserve">feux follets</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il corteo</t>
+          <t xml:space="preserve">fuochi fatui</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">družina</t>
+          <t xml:space="preserve">bludné ohně</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">družina</t>
+          <t xml:space="preserve">bludné ohne</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">眷属</t>
+          <t xml:space="preserve">鬼火</t>
         </is>
       </c>
     </row>
@@ -4063,62 +4063,62 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Płanetnik</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">Błędnice</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duch chmur i gradu; polska nazwa, wyjaśnia karta.</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetnik</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planetnik</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetnik</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetnik</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetnik</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetnik</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetník</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">planetník</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">プワネトニク</t>
+          <t xml:space="preserve">Kule światła nad bagnem w głębi boru, w każdej skulona mała postać, popiskują jak pisklęta; ze świty Pana Lasu. Nie ma utartej nazwy — wybrano słowa (a) inne niż dla błędnych ogników, (b) sugerujące małe istotki, (c) bez „panien/dziewic” (karta ich nie opisuje). cs/sk „světýlka/svetielka” to poświadczone ludowe nazwy błądzących świateł.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wisplings</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Irrwische</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">candelillas</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">luzinhas errantes</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">follettes</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fiammelle erranti</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">světýlka</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">svetielka</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">迷い火</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ubożę</t>
+          <t xml:space="preserve">świta (Pana Lasu)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4140,52 +4140,52 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duszek domowy za piecem; rodzaj nijaki („je”), w tekście wielką literą jak imię („Kto Ubożę karmi”). Bogactwo, które przynosi, ubywa sąsiadom (jak niemiecki Kobold).</t>
+          <t xml:space="preserve">Orszak istot Pana Lasu (rusałki, mamuny, błędnice). Małą literą. ja 眷属 = orszak bóstwa.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the hearth sprite</t>
+          <t xml:space="preserve">the retinue</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der Hausgeist</t>
+          <t xml:space="preserve">das Gefolge</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el duende del hogar</t>
+          <t xml:space="preserve">el séquito</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o duende da casa</t>
+          <t xml:space="preserve">o séquito</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le lutin du foyer</t>
+          <t xml:space="preserve">le cortège</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lo spiritello del focolare</t>
+          <t xml:space="preserve">il corteo</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hospodáříček</t>
+          <t xml:space="preserve">družina</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">škriatok</t>
+          <t xml:space="preserve">družina</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">かまどの精</t>
+          <t xml:space="preserve">眷属</t>
         </is>
       </c>
     </row>
@@ -4197,62 +4197,62 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dziad z lirą</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Płanetnik</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wędrowny śpiewak z liry korbowej (nie lutnia).</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the Old Man with the Hurdy-Gurdy</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">der Alte mit der Drehleier</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el viejo de la zanfoña</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o velho da viela de roda</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">le vieillard à la vielle</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">il vecchio con la ghironda</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dědek s niněrou</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">starec s ninerou</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ハーディ・ガーディ弾きの老人</t>
+          <t xml:space="preserve">Duch chmur i gradu; polska nazwa, wyjaśnia karta.</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetnik</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planetnik</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetnik</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetnik</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetnik</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetnik</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetník</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">planetník</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">プワネトニク</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biały wilk</t>
+          <t xml:space="preserve">Ubożę</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4274,52 +4274,52 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Duszek domowy za piecem; rodzaj nijaki („je”), w tekście wielką literą jak imię („Kto Ubożę karmi”). Bogactwo, które przynosi, ubywa sąsiadom (jak niemiecki Kobold).</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the white wolf</t>
+          <t xml:space="preserve">the hearth sprite</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">der weiße Wolf</t>
+          <t xml:space="preserve">der Hausgeist</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el lobo blanco</t>
+          <t xml:space="preserve">el duende del hogar</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o lobo branco</t>
+          <t xml:space="preserve">o duende da casa</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le loup blanc</t>
+          <t xml:space="preserve">le lutin du foyer</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il lupo bianco</t>
+          <t xml:space="preserve">lo spiritello del focolare</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bílý vlk</t>
+          <t xml:space="preserve">hospodáříček</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">biely vlk</t>
+          <t xml:space="preserve">škriatok</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">白い狼</t>
+          <t xml:space="preserve">かまどの精</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dzieci spod dębu</t>
+          <t xml:space="preserve">Dziad z lirą</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4341,52 +4341,52 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Wędrowny śpiewak z liry korbowej (nie lutnia).</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Children under the Oak</t>
+          <t xml:space="preserve">the Old Man with the Hurdy-Gurdy</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Kinder unter der Eiche</t>
+          <t xml:space="preserve">der Alte mit der Drehleier</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">los niños bajo el roble</t>
+          <t xml:space="preserve">el viejo de la zanfoña</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">as crianças sob o carvalho</t>
+          <t xml:space="preserve">o velho da viela de roda</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">les enfants sous le chêne</t>
+          <t xml:space="preserve">le vieillard à la vielle</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">i bambini sotto la quercia</t>
+          <t xml:space="preserve">il vecchio con la ghironda</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">děti pod dubem</t>
+          <t xml:space="preserve">dědek s niněrou</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">deti spod duba</t>
+          <t xml:space="preserve">starec s ninerou</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">樫の下の子どもたち</t>
+          <t xml:space="preserve">ハーディ・ガーディ弾きの老人</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pod oknem (karta)</t>
+          <t xml:space="preserve">Biały wilk</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4413,59 +4413,59 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under the Window</t>
+          <t xml:space="preserve">the white wolf</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unter dem Fenster</t>
+          <t xml:space="preserve">der weiße Wolf</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bajo la ventana</t>
+          <t xml:space="preserve">el lobo blanco</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sob a janela</t>
+          <t xml:space="preserve">o lobo branco</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sous la fenêtre</t>
+          <t xml:space="preserve">le loup blanc</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sotto la finestra</t>
+          <t xml:space="preserve">il lupo bianco</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pod oknem</t>
+          <t xml:space="preserve">bílý vlk</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pod oknom</t>
+          <t xml:space="preserve">biely vlk</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">窓の下</t>
+          <t xml:space="preserve">白い狼</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Przedmioty</t>
+          <t xml:space="preserve">Istoty</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siekiera dziadka Maćka</t>
+          <t xml:space="preserve">Dzieci spod dębu</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4480,59 +4480,59 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grandfather Maciek’s axe</t>
+          <t xml:space="preserve">the Children under the Oak</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Großvater Macieks Axt</t>
+          <t xml:space="preserve">die Kinder unter der Eiche</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El hacha del abuelo Maciek</t>
+          <t xml:space="preserve">los niños bajo el roble</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">O machado do avô Maciek</t>
+          <t xml:space="preserve">as crianças sob o carvalho</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La hache de grand-père Maciek</t>
+          <t xml:space="preserve">les enfants sous le chêne</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">L’ascia di nonno Maciek</t>
+          <t xml:space="preserve">i bambini sotto la quercia</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sekera dědečka Maćka</t>
+          <t xml:space="preserve">děti pod dubem</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sekera dedka Maćka</t>
+          <t xml:space="preserve">deti spod duba</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">マチェクじいさんの斧</t>
+          <t xml:space="preserve">樫の下の子どもたち</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Przedmioty</t>
+          <t xml:space="preserve">Istoty</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nadpalona figurka (lalka)</t>
+          <t xml:space="preserve">Pod oknem (karta)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4542,52 +4542,52 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">„Lalka” zielarki — w snach dzieci: „Gdzie moja lalka?”.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charred figurine (the doll)</t>
+          <t xml:space="preserve">Under the Window</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Angekohlte Figur (die Puppe)</t>
+          <t xml:space="preserve">Unter dem Fenster</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Figurilla chamuscada (la muñeca)</t>
+          <t xml:space="preserve">Bajo la ventana</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estatueta chamuscada (a boneca)</t>
+          <t xml:space="preserve">Sob a janela</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Figurine calcinée (la poupée)</t>
+          <t xml:space="preserve">Sous la fenêtre</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statuina bruciacchiata (la bambola)</t>
+          <t xml:space="preserve">Sotto la finestra</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ohořelá figurka (panenka)</t>
+          <t xml:space="preserve">Pod oknem</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ohorená figúrka (bábika)</t>
+          <t xml:space="preserve">Pod oknom</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">焦げた人形</t>
+          <t xml:space="preserve">窓の下</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krzesiwo</t>
+          <t xml:space="preserve">Siekiera dziadka Maćka</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4614,47 +4614,47 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flint and steel</t>
+          <t xml:space="preserve">Grandfather Maciek’s axe</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feuerstahl</t>
+          <t xml:space="preserve">Großvater Macieks Axt</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eslabón</t>
+          <t xml:space="preserve">El hacha del abuelo Maciek</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pederneira</t>
+          <t xml:space="preserve">O machado do avô Maciek</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Briquet à silex</t>
+          <t xml:space="preserve">La hache de grand-père Maciek</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acciarino</t>
+          <t xml:space="preserve">L’ascia di nonno Maciek</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Křesadlo</t>
+          <t xml:space="preserve">Sekera dědečka Maćka</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kresadlo</t>
+          <t xml:space="preserve">Sekera dedka Maćka</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">火打ち金</t>
+          <t xml:space="preserve">マチェクじいさんの斧</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Księga opowiadań (pana Ignacego)</t>
+          <t xml:space="preserve">Nadpalona figurka (lalka)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4676,52 +4676,52 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rękopis nauczyciela z podaniami.</t>
+          <t xml:space="preserve">„Lalka” zielarki — w snach dzieci: „Gdzie moja lalka?”.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book of legends</t>
+          <t xml:space="preserve">Charred figurine (the doll)</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sagenbuch</t>
+          <t xml:space="preserve">Angekohlte Figur (die Puppe)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libro de relatos</t>
+          <t xml:space="preserve">Figurilla chamuscada (la muñeca)</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Livro de contos</t>
+          <t xml:space="preserve">Estatueta chamuscada (a boneca)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Livre de contes</t>
+          <t xml:space="preserve">Figurine calcinée (la poupée)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quaderno delle leggende</t>
+          <t xml:space="preserve">Statuina bruciacchiata (la bambola)</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kniha vyprávění</t>
+          <t xml:space="preserve">Ohořelá figurka (panenka)</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kniha rozprávok</t>
+          <t xml:space="preserve">Ohorená figúrka (bábika)</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">昔話の帳面</t>
+          <t xml:space="preserve">焦げた人形</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Żołądź ze Starego Dębu</t>
+          <t xml:space="preserve">Krzesiwo</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4748,47 +4748,47 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acorn from the Old Oak</t>
+          <t xml:space="preserve">Flint and steel</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eichel der Alten Eiche</t>
+          <t xml:space="preserve">Feuerstahl</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bellota del Viejo Roble</t>
+          <t xml:space="preserve">Eslabón</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolota do Velho Carvalho</t>
+          <t xml:space="preserve">Pederneira</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gland du Vieux Chêne</t>
+          <t xml:space="preserve">Briquet à silex</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ghianda della Vecchia Quercia</t>
+          <t xml:space="preserve">Acciarino</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Žalud ze Starého dubu</t>
+          <t xml:space="preserve">Křesadlo</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Žaluď zo Starého duba</t>
+          <t xml:space="preserve">Kresadlo</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">老樫のどんぐり</t>
+          <t xml:space="preserve">火打ち金</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piołun</t>
+          <t xml:space="preserve">Księga opowiadań (pana Ignacego)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4810,52 +4810,52 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rękopis nauczyciela z podaniami.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wormwood</t>
+          <t xml:space="preserve">Book of legends</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wermut</t>
+          <t xml:space="preserve">Sagenbuch</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajenjo</t>
+          <t xml:space="preserve">Libro de relatos</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Losna</t>
+          <t xml:space="preserve">Livro de contos</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absinthe (armoise)</t>
+          <t xml:space="preserve">Livre de contes</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assenzio</t>
+          <t xml:space="preserve">Quaderno delle leggende</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pelyněk</t>
+          <t xml:space="preserve">Kniha vyprávění</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palina</t>
+          <t xml:space="preserve">Kniha rozprávok</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ニガヨモギ</t>
+          <t xml:space="preserve">昔話の帳面</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korale z jarzębiny</t>
+          <t xml:space="preserve">Żołądź ze Starego Dębu</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4882,47 +4882,47 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rowan-berry beads</t>
+          <t xml:space="preserve">Acorn from the Old Oak</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vogelbeerkette</t>
+          <t xml:space="preserve">Eichel der Alten Eiche</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collar de serbal</t>
+          <t xml:space="preserve">Bellota del Viejo Roble</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colar de sorveira</t>
+          <t xml:space="preserve">Bolota do Velho Carvalho</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collier de sorbier</t>
+          <t xml:space="preserve">Gland du Vieux Chêne</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collana di sorbo</t>
+          <t xml:space="preserve">Ghianda della Vecchia Quercia</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korále z jeřabin</t>
+          <t xml:space="preserve">Žalud ze Starého dubu</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korálky z jarabiny</t>
+          <t xml:space="preserve">Žaluď zo Starého duba</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ナナカマドの数珠</t>
+          <t xml:space="preserve">老樫のどんぐり</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Świątek z kapliczki</t>
+          <t xml:space="preserve">Piołun</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4944,52 +4944,52 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drewniana figurka świętego z przydrożnej kapliczki.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wayside saint figure</t>
+          <t xml:space="preserve">Wormwood</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heiligenfigur aus dem Bildstock</t>
+          <t xml:space="preserve">Wermut</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santito del humilladero</t>
+          <t xml:space="preserve">Ajenjo</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santinho do oratório</t>
+          <t xml:space="preserve">Losna</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statuette de l’oratoire</t>
+          <t xml:space="preserve">Absinthe (armoise)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santino dell’edicola</t>
+          <t xml:space="preserve">Assenzio</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soška z kapličky</t>
+          <t xml:space="preserve">Pelyněk</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soška z kaplnky</t>
+          <t xml:space="preserve">Palina</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">祠の聖像</t>
+          <t xml:space="preserve">ニガヨモギ</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Podkowa kowala</t>
+          <t xml:space="preserve">Korale z jarzębiny</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5016,47 +5016,47 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The smith’s horseshoe</t>
+          <t xml:space="preserve">Rowan-berry beads</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hufeisen des Schmieds</t>
+          <t xml:space="preserve">Vogelbeerkette</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La herradura del herrero</t>
+          <t xml:space="preserve">Collar de serbal</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A ferradura do ferreiro</t>
+          <t xml:space="preserve">Colar de sorveira</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le fer à cheval du forgeron</t>
+          <t xml:space="preserve">Collier de sorbier</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il ferro di cavallo del fabbro</t>
+          <t xml:space="preserve">Collana di sorbo</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kovářova podkova</t>
+          <t xml:space="preserve">Korále z jeřabin</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kováčova podkova</t>
+          <t xml:space="preserve">Korálky z jarabiny</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">鍛冶屋の蹄鉄</t>
+          <t xml:space="preserve">ナナカマドの数珠</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krzyżyk kowala</t>
+          <t xml:space="preserve">Świątek z kapliczki</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5078,52 +5078,52 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Drewniana figurka świętego z przydrożnej kapliczki.</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The smith’s cross</t>
+          <t xml:space="preserve">Wayside saint figure</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kreuz des Schmieds</t>
+          <t xml:space="preserve">Heiligenfigur aus dem Bildstock</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La crucecita del herrero</t>
+          <t xml:space="preserve">Santito del humilladero</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A cruzinha do ferreiro</t>
+          <t xml:space="preserve">Santinho do oratório</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La croix du forgeron</t>
+          <t xml:space="preserve">Statuette de l’oratoire</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La crocetta del fabbro</t>
+          <t xml:space="preserve">Santino dell’edicola</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kovářův křížek</t>
+          <t xml:space="preserve">Soška z kapličky</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kováčov krížik</t>
+          <t xml:space="preserve">Soška z kaplnky</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">鍛冶屋の十字架</t>
+          <t xml:space="preserve">祠の聖像</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gromnica</t>
+          <t xml:space="preserve">Podkowa kowala</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5145,52 +5145,52 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Świeca święcona na Matki Bożej Gromnicznej.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candlemas candle</t>
+          <t xml:space="preserve">The smith’s horseshoe</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lichtmesskerze</t>
+          <t xml:space="preserve">Hufeisen des Schmieds</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vela de la Candelaria</t>
+          <t xml:space="preserve">La herradura del herrero</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vela da Candelária</t>
+          <t xml:space="preserve">A ferradura do ferreiro</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cierge de la Chandeleur</t>
+          <t xml:space="preserve">Le fer à cheval du forgeron</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candela della Candelora</t>
+          <t xml:space="preserve">Il ferro di cavallo del fabbro</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hromnička</t>
+          <t xml:space="preserve">Kovářova podkova</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hromničná svieca</t>
+          <t xml:space="preserve">Kováčova podkova</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖燭祭の蝋燭</t>
+          <t xml:space="preserve">鍛冶屋の蹄鉄</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drewniaki Marysi</t>
+          <t xml:space="preserve">Krzyżyk kowala</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5212,52 +5212,52 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Małe czerwone chodaki.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysia’s clogs</t>
+          <t xml:space="preserve">The smith’s cross</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysias Holzschuhe</t>
+          <t xml:space="preserve">Kreuz des Schmieds</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los zuecos de Marysia</t>
+          <t xml:space="preserve">La crucecita del herrero</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os tamancos de Marysia</t>
+          <t xml:space="preserve">A cruzinha do ferreiro</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les sabots de Marysia</t>
+          <t xml:space="preserve">La croix du forgeron</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gli zoccoli di Marysia</t>
+          <t xml:space="preserve">La crocetta del fabbro</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysiny dřeváky</t>
+          <t xml:space="preserve">Kovářův křížek</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysine dreváky</t>
+          <t xml:space="preserve">Kováčov krížik</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">マリシャの木靴</t>
+          <t xml:space="preserve">鍛冶屋の十字架</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wstążka Marysi</t>
+          <t xml:space="preserve">Gromnica</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5279,52 +5279,52 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Świeca święcona na Matki Bożej Gromnicznej.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysia’s ribbon</t>
+          <t xml:space="preserve">Candlemas candle</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysias Band</t>
+          <t xml:space="preserve">Lichtmesskerze</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La cinta de Marysia</t>
+          <t xml:space="preserve">Vela de la Candelaria</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A fita de Marysia</t>
+          <t xml:space="preserve">Vela da Candelária</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le ruban de Marysia</t>
+          <t xml:space="preserve">Cierge de la Chandeleur</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il nastro di Marysia</t>
+          <t xml:space="preserve">Candela della Candelora</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysina stužka</t>
+          <t xml:space="preserve">Hromnička</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marysina stužka</t>
+          <t xml:space="preserve">Hromničná svieca</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">マリシャのリボン</t>
+          <t xml:space="preserve">聖燭祭の蝋燭</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garść maku</t>
+          <t xml:space="preserve">Drewniaki Marysi</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5346,52 +5346,52 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Małe czerwone chodaki.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A handful of poppy seeds</t>
+          <t xml:space="preserve">Marysia’s clogs</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eine Handvoll Mohn</t>
+          <t xml:space="preserve">Marysias Holzschuhe</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un puñado de semillas de amapola</t>
+          <t xml:space="preserve">Los zuecos de Marysia</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um punhado de sementes de papoula</t>
+          <t xml:space="preserve">Os tamancos de Marysia</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Une poignée de graines de pavot</t>
+          <t xml:space="preserve">Les sabots de Marysia</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Una manciata di semi di papavero</t>
+          <t xml:space="preserve">Gli zoccoli di Marysia</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrst máku</t>
+          <t xml:space="preserve">Dřeváky Marysie</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrsť maku</t>
+          <t xml:space="preserve">Dreváky Marysie</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ひと握りのケシの実</t>
+          <t xml:space="preserve">マリシャの木靴</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kora ze znakiem</t>
+          <t xml:space="preserve">Wstążka Marysi</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5418,47 +5418,47 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bark with a sign</t>
+          <t xml:space="preserve">Marysia’s ribbon</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rinde mit Zeichen</t>
+          <t xml:space="preserve">Marysias Band</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corteza con un signo</t>
+          <t xml:space="preserve">La cinta de Marysia</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casca com um sinal</t>
+          <t xml:space="preserve">A fita de Marysia</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Écorce marquée</t>
+          <t xml:space="preserve">Le ruban de Marysia</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corteccia col segno</t>
+          <t xml:space="preserve">Il nastro di Marysia</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kůra se znamením</t>
+          <t xml:space="preserve">Stužka Marysie</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kôra so znamením</t>
+          <t xml:space="preserve">Stužka Marysie</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">印のある樹皮</t>
+          <t xml:space="preserve">マリシャのリボン</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poświęcony różaniec</t>
+          <t xml:space="preserve">Garść maku</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5485,47 +5485,47 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blessed rosary</t>
+          <t xml:space="preserve">A handful of poppy seeds</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geweihter Rosenkranz</t>
+          <t xml:space="preserve">Eine Handvoll Mohn</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosario bendito</t>
+          <t xml:space="preserve">Un puñado de semillas de amapola</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terço bento</t>
+          <t xml:space="preserve">Um punhado de sementes de papoula</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chapelet béni</t>
+          <t xml:space="preserve">Une poignée de graines de pavot</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosario benedetto</t>
+          <t xml:space="preserve">Una manciata di semi di papavero</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Posvěcený růženec</t>
+          <t xml:space="preserve">Hrst máku</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Posvätený ruženec</t>
+          <t xml:space="preserve">Hrsť maku</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖別されたロザリオ</t>
+          <t xml:space="preserve">ひと握りのケシの実</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">całun (mamun)</t>
+          <t xml:space="preserve">Kora ze znakiem</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5547,52 +5547,52 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Małe płótno prane przez mamuny.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shroud</t>
+          <t xml:space="preserve">Bark with a sign</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leichentuch</t>
+          <t xml:space="preserve">Rinde mit Zeichen</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mortaja</t>
+          <t xml:space="preserve">Corteza con un signo</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mortalha</t>
+          <t xml:space="preserve">Casca com um sinal</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">linceul</t>
+          <t xml:space="preserve">Écorce marquée</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sudario</t>
+          <t xml:space="preserve">Corteccia col segno</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rubáš</t>
+          <t xml:space="preserve">Kůra se znamením</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rubáš</t>
+          <t xml:space="preserve">Kôra so znamením</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">経帷子</t>
+          <t xml:space="preserve">印のある樹皮</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kijanka</t>
+          <t xml:space="preserve">Poświęcony różaniec</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5614,64 +5614,64 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drewniana pałka do prania; jej klaskanie zwiastuje mamuny.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">washing paddle</t>
+          <t xml:space="preserve">Blessed rosary</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waschbleuel</t>
+          <t xml:space="preserve">Geweihter Rosenkranz</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pala de lavar</t>
+          <t xml:space="preserve">Rosario bendito</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">batedor de roupa</t>
+          <t xml:space="preserve">Terço bento</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">battoir</t>
+          <t xml:space="preserve">Chapelet béni</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">battipanni</t>
+          <t xml:space="preserve">Rosario benedetto</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prací palička</t>
+          <t xml:space="preserve">Posvěcený růženec</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pracia palica</t>
+          <t xml:space="preserve">Posvätený ruženec</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">洗濯棒</t>
+          <t xml:space="preserve">聖別されたロザリオ</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Święta i obrzędy</t>
+          <t xml:space="preserve">Przedmioty</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wigilia</t>
+          <t xml:space="preserve">całun (mamun)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5681,64 +5681,64 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Małe płótno prane przez mamuny.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christmas Eve</t>
+          <t xml:space="preserve">shroud</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heiligabend</t>
+          <t xml:space="preserve">Leichentuch</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nochebuena</t>
+          <t xml:space="preserve">mortaja</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Véspera de Natal</t>
+          <t xml:space="preserve">mortalha</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la veillée de Noël</t>
+          <t xml:space="preserve">linceul</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Vigilia di Natale</t>
+          <t xml:space="preserve">sudario</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Štědrý večer</t>
+          <t xml:space="preserve">rubáš</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Štedrý večer</t>
+          <t xml:space="preserve">rubáš</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖夜</t>
+          <t xml:space="preserve">経帷子</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Święta i obrzędy</t>
+          <t xml:space="preserve">Przedmioty</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">opłatek</t>
+          <t xml:space="preserve">kożuch / kapota</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5748,64 +5748,64 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cienki biały wafel łamany w Wigilię; kładziony na talerzu dla wędrowca. W tekście też porównanie „cienki jak opłatek” (lód) — oddać naturalnym porównaniem (en „wafer-thin”, de „hauchdünn wie eine Oblate”).</t>
+          <t xml:space="preserve">Kożuch: okrycie z owczej skóry, wełną do środka. Motyw „kożuch wywrócony włosiem na wierzch” (starzec / Pan Lasu r2, r9, r16, r20; Jaromir r3) oddać dosłownie: en „a sheepskin turned fleece-out”, de „mit dem Fell nach außen”, cs „kožich obrácený srstí ven”, sk „kožuch obrátený srsťou von”. Kapota: sukienne okrycie wierzchnie z podszewką (r9 kapota Franka „podszewką na wierzch”, r16 i r18 Jaromira „szwami na wierzch”) — zwykły wyraz na płaszcz lub kurtkę, bez egzotyzmu. To dwie różne rzeczy, nie mieszać. Sukmana (prolog, r3) — tak samo zwykły wyraz na chłopskie okrycie z grubego sukna. Uwaga: „tęczowy kożuch” na wodzie (r16) to warstwa na powierzchni (en film, de Schicht, cs povlak), nie ubranie.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Christmas wafer</t>
+          <t xml:space="preserve">sheepskin coat / coat</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Weihnachtsoblate</t>
+          <t xml:space="preserve">Schafspelz / Joppe</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la oblea de Navidad</t>
+          <t xml:space="preserve">zamarra / chaquetón</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a hóstia de Natal</t>
+          <t xml:space="preserve">samarra / casaco</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">l’hostie de Noël</t>
+          <t xml:space="preserve">peau de mouton / veste</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">l’ostia di Natale</t>
+          <t xml:space="preserve">pelliccia di montone / giubba</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">oplatka</t>
+          <t xml:space="preserve">kožich / kabát</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">oblátka</t>
+          <t xml:space="preserve">kožuch / kabát</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">クリスマスの聖餅</t>
+          <t xml:space="preserve">羊皮の外套 / 上着</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Święta i obrzędy</t>
+          <t xml:space="preserve">Przedmioty</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pasterka</t>
+          <t xml:space="preserve">kijanka</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5815,64 +5815,64 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Drewniana pałka do prania; jej klaskanie zwiastuje mamuny.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midnight Mass</t>
+          <t xml:space="preserve">washing paddle</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christmette</t>
+          <t xml:space="preserve">Waschbleuel</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misa del Gallo</t>
+          <t xml:space="preserve">pala de lavar</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Missa do Galo</t>
+          <t xml:space="preserve">batedor de roupa</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">messe de minuit</t>
+          <t xml:space="preserve">battoir</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">messa di mezzanotte</t>
+          <t xml:space="preserve">battipanni</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">půlnoční mše</t>
+          <t xml:space="preserve">prací palička</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">polnočná omša</t>
+          <t xml:space="preserve">pracia palica</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">真夜中のミサ</t>
+          <t xml:space="preserve">洗濯棒</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Święta i obrzędy</t>
+          <t xml:space="preserve">Przedmioty</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zaduszki</t>
+          <t xml:space="preserve">ruble srebrem</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5882,52 +5882,52 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">r11: dziedzic płaci za skórę białego wilka „dziesięć rubli srebrem”, Urbaniak dokłada drugie tyle; „dwadzieścia rubli” to więcej, niż niejeden gospodarz widział przez całe życie. „Srebrem” = w srebrnej monecie (nie w papierowych asygnatach), XIX-wieczna formuła z zaboru rosyjskiego. Liczby zostają, bez przeliczania i bez przypisów. Tak samo „płaci srebrem” u Urbaniaka (r5, r8, r14) = płaci monetą do ręki: en „pays in silver”, de „zahlt in Silber”, cs „platí stříbrem”, sk „platí striebrom”. en pisownia brytyjska „roubles”; cs „deset rublů ve stříbře”, sk „desať rubľov v striebre”.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Souls’ Day</t>
+          <t xml:space="preserve">silver roubles</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allerseelen</t>
+          <t xml:space="preserve">Silberrubel</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Día de los Difuntos</t>
+          <t xml:space="preserve">rublos de plata</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia de Finados</t>
+          <t xml:space="preserve">rublos de prata</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le jour des Morts</t>
+          <t xml:space="preserve">roubles d’argent</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il giorno dei Morti</t>
+          <t xml:space="preserve">rubli d’argento</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dušičky</t>
+          <t xml:space="preserve">rubly ve stříbře</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dušičky</t>
+          <t xml:space="preserve">ruble v striebre</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">死者の日</t>
+          <t xml:space="preserve">ルーブル銀貨</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zielone Świątki</t>
+          <t xml:space="preserve">Wigilia</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5954,47 +5954,47 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whitsun</t>
+          <t xml:space="preserve">Christmas Eve</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pfingsten</t>
+          <t xml:space="preserve">Heiligabend</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pentecostés</t>
+          <t xml:space="preserve">Nochebuena</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pentecostes</t>
+          <t xml:space="preserve">Véspera de Natal</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Pentecôte</t>
+          <t xml:space="preserve">la veillée de Noël</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Pentecoste</t>
+          <t xml:space="preserve">la Vigilia di Natale</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Letnice</t>
+          <t xml:space="preserve">Štědrý večer</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turíce</t>
+          <t xml:space="preserve">Štedrý večer</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖霊降臨祭</t>
+          <t xml:space="preserve">聖夜</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noc Kupały / noc świętojańska</t>
+          <t xml:space="preserve">opłatek</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6016,52 +6016,52 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Cienki biały wafel łamany w Wigilię; kładziony na talerzu dla wędrowca. W tekście też porównanie „cienki jak opłatek” (lód) — oddać naturalnym porównaniem (en „wafer-thin”, de „hauchdünn wie eine Oblate”).</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kupala Night / Midsummer Night</t>
+          <t xml:space="preserve">the Christmas wafer</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kupalanacht / Johannisnacht</t>
+          <t xml:space="preserve">die Weihnachtsoblate</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noche de Kupala / Noche de San Juan</t>
+          <t xml:space="preserve">la oblea de Navidad</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noite de Kupala / Noite de São João</t>
+          <t xml:space="preserve">a hóstia de Natal</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nuit de Kupala / nuit de la Saint-Jean</t>
+          <t xml:space="preserve">l’hostie de Noël</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">notte di Kupala / notte di San Giovanni</t>
+          <t xml:space="preserve">l’ostia di Natale</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kupalská noc / svatojánská noc</t>
+          <t xml:space="preserve">oplatka</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kupalova noc / svätojánska noc</t>
+          <t xml:space="preserve">oblátka</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">クパーラの夜 / 夏至の夜</t>
+          <t xml:space="preserve">聖餅</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sobótki</t>
+          <t xml:space="preserve">Pasterka</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -6083,52 +6083,52 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ogniska w noc świętojańską.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midsummer bonfires</t>
+          <t xml:space="preserve">Midnight Mass</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannisfeuer</t>
+          <t xml:space="preserve">Christmette</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hogueras de San Juan</t>
+          <t xml:space="preserve">Misa del Gallo</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fogueiras de São João</t>
+          <t xml:space="preserve">Missa do Galo</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">feux de la Saint-Jean</t>
+          <t xml:space="preserve">messe de minuit</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">falò di San Giovanni</t>
+          <t xml:space="preserve">messa di mezzanotte</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">svatojánské ohně</t>
+          <t xml:space="preserve">půlnoční mše</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">jánske ohne</t>
+          <t xml:space="preserve">polnočná omša</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">夏至の焚き火</t>
+          <t xml:space="preserve">真夜中のミサ</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kołacz</t>
+          <t xml:space="preserve">Zaduszki</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6150,52 +6150,52 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weselny placek drożdżowy (Hanka piecze je z miodem); poczęstunek dla starca w noc oczepin.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wedding loaf</t>
+          <t xml:space="preserve">All Souls’ Day</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hochzeitskuchen</t>
+          <t xml:space="preserve">Allerseelen</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rosca de boda</t>
+          <t xml:space="preserve">Día de los Difuntos</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rosca de casamento</t>
+          <t xml:space="preserve">Dia de Finados</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brioche de noces</t>
+          <t xml:space="preserve">le jour des Morts</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">focaccia nuziale</t>
+          <t xml:space="preserve">il giorno dei Morti</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">svatební koláč</t>
+          <t xml:space="preserve">Dušičky</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">svadobný koláč</t>
+          <t xml:space="preserve">Dušičky</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">婚礼のパン</t>
+          <t xml:space="preserve">死者の日</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gromniczna</t>
+          <t xml:space="preserve">Zielone Świątki</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6217,52 +6217,52 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 lutego.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candlemas</t>
+          <t xml:space="preserve">Whitsun</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lichtmess</t>
+          <t xml:space="preserve">Pfingsten</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Candelaria</t>
+          <t xml:space="preserve">Pentecostés</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Candelária</t>
+          <t xml:space="preserve">Pentecostes</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Chandeleur</t>
+          <t xml:space="preserve">la Pentecôte</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la Candelora</t>
+          <t xml:space="preserve">la Pentecoste</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hromnice</t>
+          <t xml:space="preserve">Letnice</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hromnice</t>
+          <t xml:space="preserve">Turíce</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖燭祭</t>
+          <t xml:space="preserve">聖霊降臨祭</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wielkanoc / Wielki Czwartek</t>
+          <t xml:space="preserve">Noc Kupały / noc świętojańska</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6289,47 +6289,47 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Easter / Maundy Thursday</t>
+          <t xml:space="preserve">Kupala Night / Midsummer Night</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ostern / Gründonnerstag</t>
+          <t xml:space="preserve">Kupalanacht / Johannisnacht</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pascua / Jueves Santo</t>
+          <t xml:space="preserve">Noche de Kupala / Noche de San Juan</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Páscoa / Quinta-feira Santa</t>
+          <t xml:space="preserve">Noite de Kupala / Noite de São João</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pâques / Jeudi saint</t>
+          <t xml:space="preserve">nuit de Kupala / nuit de la Saint-Jean</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pasqua / Giovedì santo</t>
+          <t xml:space="preserve">notte di Kupala / notte di San Giovanni</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velikonoce / Zelený čtvrtek</t>
+          <t xml:space="preserve">Kupalská noc / svatojánská noc</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veľká noc / Zelený štvrtok</t>
+          <t xml:space="preserve">Kupalova noc / svätojánska noc</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">復活祭 / 聖木曜日</t>
+          <t xml:space="preserve">クパーラの夜 / 夏至の夜</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrzejki</t>
+          <t xml:space="preserve">sobótki</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6351,52 +6351,52 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wieczór wróżb 29 listopada.</t>
+          <t xml:space="preserve">Ogniska w noc świętojańską.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">St Andrew’s Eve</t>
+          <t xml:space="preserve">Midsummer bonfires</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andreasnacht</t>
+          <t xml:space="preserve">Johannisfeuer</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">víspera de San Andrés</t>
+          <t xml:space="preserve">hogueras de San Juan</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">véspera de Santo André</t>
+          <t xml:space="preserve">fogueiras de São João</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la veille de la Saint-André</t>
+          <t xml:space="preserve">feux de la Saint-Jean</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la vigilia di Sant’Andrea</t>
+          <t xml:space="preserve">falò di San Giovanni</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondřejská noc</t>
+          <t xml:space="preserve">svatojánské ohně</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrejská noc</t>
+          <t xml:space="preserve">jánske ohne</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖アンデレの前夜</t>
+          <t xml:space="preserve">夏至の焚き火</t>
         </is>
       </c>
     </row>
@@ -6408,62 +6408,62 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marzanna</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zostaje</t>
+          <t xml:space="preserve">kołacz</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polska nazwa + przy pierwszym wystąpieniu: słomiana kukła topiona na wiosnę. W czeskim i słowackim ten sam zwyczaj ma własną nazwę (Morana, Morena).</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (the straw effigy of winter)</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (die Strohpuppe des Winters)</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (la muñeca de paja del invierno)</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (a boneca de palha do inverno)</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (l’effigie de paille de l’hiver)</t>
-        </is>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marzanna (il fantoccio di paglia dell’inverno)</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Morana (Mařena)</t>
-        </is>
-      </c>
-      <c r="L95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Morena</t>
-        </is>
-      </c>
-      <c r="M95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">マジャンナ（冬の藁人形）</t>
+          <t xml:space="preserve">Weselny placek drożdżowy (Hanka piecze je z miodem); poczęstunek dla starca w noc oczepin.</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wedding loaf</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hochzeitskuchen</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosca de boda</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosca de casamento</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brioche de noces</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focaccia nuziale</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">svatební koláč</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">svadobný koláč</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">婚礼のパン</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">oczepiny / swaty / zrękowiny</t>
+          <t xml:space="preserve">Gromniczna</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6485,52 +6485,52 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obrzędy weselne — opisowo, bez szukania egzotycznych słów.</t>
+          <t xml:space="preserve">2 lutego.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">capping of the bride / matchmaking / betrothal</t>
+          <t xml:space="preserve">Candlemas</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haubung / Brautwerbung / Verlobung</t>
+          <t xml:space="preserve">Lichtmess</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tocado de la novia / petición de mano / esponsales</t>
+          <t xml:space="preserve">la Candelaria</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">touca da noiva / pedido de casamento / noivado</t>
+          <t xml:space="preserve">a Candelária</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">coiffe de la mariée / demande en mariage / fiançailles</t>
+          <t xml:space="preserve">la Chandeleur</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuffia della sposa / richiesta di matrimonio / fidanzamento</t>
+          <t xml:space="preserve">la Candelora</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">čepení / námluvy / zásnuby</t>
+          <t xml:space="preserve">Hromnice</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">čepčenie / pytačky / zásnuby</t>
+          <t xml:space="preserve">Hromnice</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">花嫁の頭巾の儀 / 縁談 / 婚約</t>
+          <t xml:space="preserve">聖燭祭</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">przednówek</t>
+          <t xml:space="preserve">Wielkanoc / Wielki Czwartek</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6552,52 +6552,52 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Głodny czas przed pierwszymi plonami.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the hungry gap</t>
+          <t xml:space="preserve">Easter / Maundy Thursday</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Notzeit vor der Ernte</t>
+          <t xml:space="preserve">Ostern / Gründonnerstag</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la escasez de primavera</t>
+          <t xml:space="preserve">Pascua / Jueves Santo</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a fome antes da colheita</t>
+          <t xml:space="preserve">Páscoa / Quinta-feira Santa</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">la soudure</t>
+          <t xml:space="preserve">Pâques / Jeudi saint</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">il periodo di magra</t>
+          <t xml:space="preserve">Pasqua / Giovedì santo</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hladové jaro</t>
+          <t xml:space="preserve">Velikonoce / Zelený čtvrtek</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hladná jar</t>
+          <t xml:space="preserve">Veľká noc / Zelený štvrtok</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">端境期</t>
+          <t xml:space="preserve">復活祭 / 聖木曜日</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kapliczka</t>
+          <t xml:space="preserve">Andrzejki</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6619,64 +6619,64 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Przydrożna kapliczka — ważny motyw, zawsze ten sam wyraz. es „humilladero” (decyzja autora; „capilla” to budynek).</t>
+          <t xml:space="preserve">Wieczór wróżb 29 listopada.</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wayside shrine</t>
+          <t xml:space="preserve">St Andrew’s Eve</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bildstock</t>
+          <t xml:space="preserve">Andreasnacht</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">humilladero</t>
+          <t xml:space="preserve">víspera de San Andrés</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">oratório</t>
+          <t xml:space="preserve">véspera de Santo André</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">oratoire</t>
+          <t xml:space="preserve">la veille de la Saint-André</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">edicola votiva</t>
+          <t xml:space="preserve">la vigilia di Sant’Andrea</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kaplička</t>
+          <t xml:space="preserve">Ondřejská noc</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kaplnka</t>
+          <t xml:space="preserve">Ondrejská noc</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">道端の祠</t>
+          <t xml:space="preserve">聖アンデレの前夜</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuły rozdziałów</t>
+          <t xml:space="preserve">Święta i obrzędy</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prolog: Zapadlina</t>
+          <t xml:space="preserve">Marzanna</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -6686,64 +6686,64 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Części prologu: Zapadlina, Chata, Dach, Zgliszcza, Miasto, Rodzina, Powrót, Jedna świeca, Lata spokoju.</t>
+          <t xml:space="preserve">Polska nazwa + przy pierwszym wystąpieniu: słomiana kukła topiona na wiosnę. W czeskim i słowackim ten sam zwyczaj ma własną nazwę (Morana, Morena).</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">Marzanna (the straw effigy of winter)</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">Marzanna (die Strohpuppe des Winters)</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">Marzanna (la muñeca de paja del invierno)</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">Marzanna (a boneca de palha do inverno)</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">Marzanna (l’effigie de paille de l’hiver)</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">Marzanna (il fantoccio di paglia dell’inverno)</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">Morana (Mařena)</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zapadlina</t>
+          <t xml:space="preserve">Morena</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ザパドリナ</t>
+          <t xml:space="preserve">マジャンナ（冬の藁人形）</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuły rozdziałów</t>
+          <t xml:space="preserve">Święta i obrzędy</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chata / Dach / Zgliszcza</t>
+          <t xml:space="preserve">oczepiny / swaty / zrękowiny</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6753,64 +6753,64 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Obrzędy weselne — opisowo, bez szukania egzotycznych słów.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Hut / The Roof / The Ashes</t>
+          <t xml:space="preserve">capping of the bride / matchmaking / betrothal</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Die Hütte / Das Dach / Die Brandstätte</t>
+          <t xml:space="preserve">Haubung / Brautwerbung / Verlobung</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La cabaña / El tejado / Las cenizas</t>
+          <t xml:space="preserve">tocado de la novia / petición de mano / esponsales</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A cabana / O telhado / As cinzas</t>
+          <t xml:space="preserve">touca da noiva / pedido de casamento / noivado</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La cabane / Le toit / Les cendres</t>
+          <t xml:space="preserve">coiffe de la mariée / demande en mariage / fiançailles</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La capanna / Il tetto / Le macerie</t>
+          <t xml:space="preserve">cuffia della sposa / richiesta di matrimonio / fidanzamento</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chata / Střecha / Spáleniště</t>
+          <t xml:space="preserve">čepení / námluvy / zásnuby</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chata / Strecha / Spálenisko</t>
+          <t xml:space="preserve">čepčenie / pytačky / zásnuby</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">小屋 / 屋根 / 焼け跡</t>
+          <t xml:space="preserve">花嫁の頭巾の儀 / 縁談 / 婚約</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuły rozdziałów</t>
+          <t xml:space="preserve">Święta i obrzędy</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miasto / Rodzina / Powrót</t>
+          <t xml:space="preserve">drużba</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6820,64 +6820,64 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">W tekście raz (r12): Antek żeni się z Jadwisią i prosi Jaromira na drużbę. Drużba to weselny towarzysz pana młodego, prowadzi orszak i pilnuje obrzędu. Oddać zwykłym, ludowym słowem weselnym, nie urzędowym „świadkiem” (de lepiej Brautführer niż Trauzeuge). cs/sk „družba” to rodzimy odpowiednik; nie mylić z „družina” (świta Pana Lasu).</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Town / The Family / The Return</t>
+          <t xml:space="preserve">best man</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Die Stadt / Die Familie / Die Heimkehr</t>
+          <t xml:space="preserve">Brautführer</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La ciudad / La familia / El regreso</t>
+          <t xml:space="preserve">padrino de boda</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A cidade / A família / O regresso</t>
+          <t xml:space="preserve">padrinho de casamento</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La ville / La famille / Le retour</t>
+          <t xml:space="preserve">garçon d’honneur</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La città / La famiglia / Il ritorno</t>
+          <t xml:space="preserve">testimone dello sposo</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Město / Rodina / Návrat</t>
+          <t xml:space="preserve">družba</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mesto / Rodina / Návrat</t>
+          <t xml:space="preserve">družba</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">町 / 家族 / 帰還</t>
+          <t xml:space="preserve">花婿の介添人</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuły rozdziałów</t>
+          <t xml:space="preserve">Święta i obrzędy</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedna świeca / Lata spokoju</t>
+          <t xml:space="preserve">przednówek</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6887,64 +6887,64 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Głodny czas przed pierwszymi plonami.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">One Candle / Quiet Years</t>
+          <t xml:space="preserve">the hungry gap</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eine Kerze / Ruhige Jahre</t>
+          <t xml:space="preserve">die Notzeit vor der Ernte</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Una vela / Años de calma</t>
+          <t xml:space="preserve">la escasez de primavera</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma vela / Anos de paz</t>
+          <t xml:space="preserve">a fome antes da colheita</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Une seule bougie / Les années paisibles</t>
+          <t xml:space="preserve">la soudure</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Una candela / Anni di pace</t>
+          <t xml:space="preserve">il periodo di magra</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedna svíce / Léta klidu</t>
+          <t xml:space="preserve">hladové jaro</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedna sviečka / Roky pokoja</t>
+          <t xml:space="preserve">hladná jar</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">一本の蝋燭 / 平穏な年月</t>
+          <t xml:space="preserve">端境期</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tytuły rozdziałów</t>
+          <t xml:space="preserve">Święta i obrzędy</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Lato · 2 Szkoła · 3 Wigilia · 4 Marzanna</t>
+          <t xml:space="preserve">kapliczka</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6954,52 +6954,52 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Przydrożna kapliczka — ważny motyw, zawsze ten sam wyraz. es „humilladero” (decyzja autora; „capilla” to budynek).</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Summer · School · Christmas Eve · Marzanna</t>
+          <t xml:space="preserve">wayside shrine</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sommer · Schule · Heiligabend · Marzanna</t>
+          <t xml:space="preserve">Bildstock</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verano · La escuela · Nochebuena · Marzanna</t>
+          <t xml:space="preserve">humilladero</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verão · A escola · Véspera de Natal · Marzanna</t>
+          <t xml:space="preserve">oratório</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">L’été · L’école · La veillée de Noël · Marzanna</t>
+          <t xml:space="preserve">oratoire</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estate · La scuola · La Vigilia · Marzanna</t>
+          <t xml:space="preserve">edicola votiva</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Léto · Škola · Štědrý večer · Morana</t>
+          <t xml:space="preserve">kaplička</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leto · Škola · Štedrý večer · Morena</t>
+          <t xml:space="preserve">kaplnka</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">夏・学校・聖夜・マジャンナ</t>
+          <t xml:space="preserve">道端の祠</t>
         </is>
       </c>
     </row>
@@ -7011,62 +7011,62 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 Tartak · 6 Samo południe · 7 Zielone Świątki · 8 Chude lato</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tłumaczyć</t>
+          <t xml:space="preserve">Prolog: Zapadlina</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zostaje</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Sawmill · High Noon · Whitsun · The Lean Summer</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Das Sägewerk · Mittagsstunde · Pfingsten · Der magere Sommer</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El aserradero · Mediodía · Pentecostés · El verano magro</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A serraria · Meio-dia em ponto · Pentecostes · O verão magro</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La scierie · En plein midi · La Pentecôte · L’été maigre</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La segheria · Mezzogiorno in punto · Pentecoste · L’estate magra</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pila · Pravé poledne · Letnice · Hubené léto</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Píla · Pravé poludnie · Turíce · Chudobné leto</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">製材所・真昼・聖霊降臨祭・不作の夏</t>
+          <t xml:space="preserve">Części prologu: Zapadlina, Chata, Dach, Zgliszcza, Miasto, Rodzina, Powrót, Jedna świeca, Lata spokoju.</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zapadlina</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ザパドリナ</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 Wesele · 10 Narodziny · 11 Obława · 12 Czuwanie przy zmarłym</t>
+          <t xml:space="preserve">Chata / Dach / Zgliszcza</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -7093,47 +7093,47 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Wedding · The Birth · The Hunt · The Wake</t>
+          <t xml:space="preserve">The Hut / The Roof / The Ashes</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Die Hochzeit · Die Geburt · Die Treibjagd · Die Totenwache</t>
+          <t xml:space="preserve">Die Hütte / Das Dach / Die Brandstätte</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La boda · El nacimiento · La batida · El velatorio</t>
+          <t xml:space="preserve">La cabaña / El tejado / Las cenizas</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">O casamento · O nascimento · A caçada · O velório</t>
+          <t xml:space="preserve">A cabana / O telhado / As cinzas</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les noces · La naissance · La battue · La veillée funèbre</t>
+          <t xml:space="preserve">La cabane / Le toit / Les cendres</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le nozze · La nascita · La battuta · La veglia funebre</t>
+          <t xml:space="preserve">La capanna / Il tetto / Le macerie</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svatba · Narození · Hon · Bdění u mrtvého</t>
+          <t xml:space="preserve">Chata / Střecha / Spáleniště</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svadba · Narodenie · Poľovačka · Bdenie pri mŕtvom</t>
+          <t xml:space="preserve">Chata / Strecha / Spálenisko</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">婚礼・誕生・山狩り・通夜</t>
+          <t xml:space="preserve">小屋 / 屋根 / 焼け跡</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 Wspólny sen · 14 Kapliczki płoną · 15 Noc Kupały · 16 W głąb boru</t>
+          <t xml:space="preserve">Miasto / Rodzina / Powrót</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -7160,47 +7160,47 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Shared Dream · The Shrines Burn · Kupala Night · Into the Forest</t>
+          <t xml:space="preserve">The Town / The Family / The Return</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Der gemeinsame Traum · Die Bildstöcke brennen · Kupalanacht · Tief in den Wald</t>
+          <t xml:space="preserve">Die Stadt / Die Familie / Die Heimkehr</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El sueño compartido · Arden las capillas · La noche de Kupala · Bosque adentro</t>
+          <t xml:space="preserve">La ciudad / La familia / El regreso</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">O sonho compartilhado · Os oratórios ardem · A noite de Kupala · Floresta adentro</t>
+          <t xml:space="preserve">A cidade / A família / O regresso</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le rêve partagé · Les oratoires brûlent · La nuit de Kupala · Au cœur de la forêt</t>
+          <t xml:space="preserve">La ville / La famille / Le retour</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il sogno condiviso · Bruciano le edicole · La notte di Kupala · Nel cuore del bosco</t>
+          <t xml:space="preserve">La città / La famiglia / Il ritorno</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Společný sen · Kapličky hoří · Kupalská noc · Do hloubi boru</t>
+          <t xml:space="preserve">Město / Rodina / Návrat</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spoločný sen · Kaplnky horia · Kupalova noc · Do hĺbky boru</t>
+          <t xml:space="preserve">Mesto / Rodina / Návrat</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">共に見る夢・燃える祠・クパーラの夜・森の奥へ</t>
+          <t xml:space="preserve">町 / 家族 / 帰還</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 Rozmowa w borze · 18 Wybór · 19 Świt · 20 Ostatnia noc</t>
+          <t xml:space="preserve">Jedna świeca / Lata spokoju</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -7227,59 +7227,59 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Talk in the Forest · The Choice · Dawn · The Last Night</t>
+          <t xml:space="preserve">One Candle / Quiet Years</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ein Gespräch im Wald · Die Wahl · Morgengrauen · Die letzte Nacht</t>
+          <t xml:space="preserve">Eine Kerze / Ruhige Jahre</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conversación en el bosque · La elección · El alba · La última noche</t>
+          <t xml:space="preserve">Una vela / Años de calma</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conversa na floresta · A escolha · A aurora · A última noite</t>
+          <t xml:space="preserve">Uma vela / Anos de paz</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Une conversation dans la forêt · Le choix · L’aube · La dernière nuit</t>
+          <t xml:space="preserve">Une seule bougie / Les années paisibles</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colloquio nel bosco · La scelta · L’alba · L’ultima notte</t>
+          <t xml:space="preserve">Una candela / Anni di pace</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rozhovor v boru · Volba · Svítání · Poslední noc</t>
+          <t xml:space="preserve">Jedna svíce / Léta klidu</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rozhovor v bore · Voľba · Úsvit · Posledná noc</t>
+          <t xml:space="preserve">Jedna sviečka / Roky pokoja</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">森での対話・選択・夜明け・最後の夜</t>
+          <t xml:space="preserve">一本の蝋燭 / 平穏な年月</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zakończenia</t>
+          <t xml:space="preserve">Tytuły rozdziałów</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Młody dąb</t>
+          <t xml:space="preserve">1 Lato · 2 Szkoła · 3 Wigilia · 4 Marzanna</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -7289,64 +7289,64 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granica, żołądź zasadzony, Marysia wróciła.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Young Oak</t>
+          <t xml:space="preserve">Summer · School · Christmas Eve · Marzanna</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Die junge Eiche</t>
+          <t xml:space="preserve">Sommer · Schule · Heiligabend · Marzanna</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El roble joven</t>
+          <t xml:space="preserve">Verano · La escuela · Nochebuena · Marzanna</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">O carvalho jovem</t>
+          <t xml:space="preserve">Verão · A escola · Véspera de Natal · Marzanna</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le jeune chêne</t>
+          <t xml:space="preserve">L’été · L’école · La veillée de Noël · Marzanna</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La giovane quercia</t>
+          <t xml:space="preserve">Estate · La scuola · La Vigilia · Marzanna</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mladý dub</t>
+          <t xml:space="preserve">Léto · Škola · Štědrý večer · Morana</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mladý dub</t>
+          <t xml:space="preserve">Leto · Škola · Štedrý večer · Morena</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">若い樫</t>
+          <t xml:space="preserve">夏・学校・聖夜・マジャンナ</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zakończenia</t>
+          <t xml:space="preserve">Tytuły rozdziałów</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z dziadkiem Maćkiem</t>
+          <t xml:space="preserve">5 Tartak · 6 Samo południe · 7 Zielone Świątki · 8 Chude lato</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7356,64 +7356,64 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granica, żołądź, Marysia odchodzi z umarłymi.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">With Grandfather Maciek</t>
+          <t xml:space="preserve">The Sawmill · High Noon · Whitsun · The Lean Summer</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mit Großvater Maciek</t>
+          <t xml:space="preserve">Das Sägewerk · Mittagsstunde · Pfingsten · Der magere Sommer</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Con el abuelo Maciek</t>
+          <t xml:space="preserve">El aserradero · Mediodía · Pentecostés · El verano magro</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Com o avô Maciek</t>
+          <t xml:space="preserve">A serraria · Meio-dia em ponto · Pentecostes · O verão magro</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avec grand-père Maciek</t>
+          <t xml:space="preserve">La scierie · En plein midi · La Pentecôte · L’été maigre</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Con nonno Maciek</t>
+          <t xml:space="preserve">La segheria · Mezzogiorno in punto · Pentecoste · L’estate magra</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S dědečkem Maćkem</t>
+          <t xml:space="preserve">Pila · Pravé poledne · Letnice · Hubené léto</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S dedkom Maćkom</t>
+          <t xml:space="preserve">Píla · Pravé poludnie · Turíce · Chudobné leto</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">マチェクじいさんと共に</t>
+          <t xml:space="preserve">製材所・真昼・聖霊降臨祭・不作の夏</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zakończenia</t>
+          <t xml:space="preserve">Tytuły rozdziałów</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Słowo za słowo</t>
+          <t xml:space="preserve">9 Wesele · 10 Narodziny · 11 Obława · 12 Czuwanie przy zmarłym</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -7423,64 +7423,64 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granica bez żołędzia, Marysia wróciła.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Word for a Word</t>
+          <t xml:space="preserve">The Wedding · The Birth · The Hunt · The Wake</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wort um Wort</t>
+          <t xml:space="preserve">Die Hochzeit · Die Geburt · Die Treibjagd · Die Totenwache</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palabra por palabra</t>
+          <t xml:space="preserve">La boda · El nacimiento · La batida · El velatorio</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palavra por palavra</t>
+          <t xml:space="preserve">O casamento · O nascimento · A caçada · O velório</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parole contre parole</t>
+          <t xml:space="preserve">Les noces · La naissance · La battue · La veillée funèbre</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parola per parola</t>
+          <t xml:space="preserve">Le nozze · La nascita · La battuta · La veglia funebre</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slovo za slovo</t>
+          <t xml:space="preserve">Svatba · Narození · Hon · Bdění u mrtvého</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slovo za slovo</t>
+          <t xml:space="preserve">Svadba · Narodenie · Poľovačka · Bdenie pri mŕtvom</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">言葉には言葉を</t>
+          <t xml:space="preserve">婚礼・誕生・山狩り・通夜</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zakończenia</t>
+          <t xml:space="preserve">Tytuły rozdziałów</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedno dziecko na pokolenie</t>
+          <t xml:space="preserve">13 Wspólny sen · 14 Kapliczki płoną · 15 Noc Kupały · 16 W głąb boru</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -7490,64 +7490,64 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granica bez żołędzia, bez Marysi.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">One Child a Generation</t>
+          <t xml:space="preserve">The Shared Dream · The Shrines Burn · Kupala Night · Into the Forest</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ein Kind pro Generation</t>
+          <t xml:space="preserve">Der gemeinsame Traum · Die Bildstöcke brennen · Kupalanacht · Tief in den Wald</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un niño por generación</t>
+          <t xml:space="preserve">El sueño compartido · Arden las capillas · La noche de Kupala · Bosque adentro</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma criança por geração</t>
+          <t xml:space="preserve">O sonho compartilhado · Os oratórios ardem · A noite de Kupala · Floresta adentro</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un enfant par génération</t>
+          <t xml:space="preserve">Le rêve partagé · Les oratoires brûlent · La nuit de Kupala · Au cœur de la forêt</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un bambino per generazione</t>
+          <t xml:space="preserve">Il sogno condiviso · Bruciano le edicole · La notte di Kupala · Nel cuore del bosco</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedno dítě za pokolení</t>
+          <t xml:space="preserve">Společný sen · Kapličky hoří · Kupalská noc · Do hloubi boru</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jedno dieťa za pokolenie</t>
+          <t xml:space="preserve">Spoločný sen · Kaplnky horia · Kupalova noc · Do hĺbky boru</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">一世代に一人の子</t>
+          <t xml:space="preserve">共に見る夢・燃える祠・クパーラの夜・森の奥へ</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zakończenia</t>
+          <t xml:space="preserve">Tytuły rozdziałów</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Za płotem</t>
+          <t xml:space="preserve">17 Rozmowa w borze · 18 Wybór · 19 Świt · 20 Ostatnia noc</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -7557,52 +7557,52 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromir zostaje Panem Lasu, Marysia wróciła.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyond the Fence</t>
+          <t xml:space="preserve">A Talk in the Forest · The Choice · Dawn · The Last Night</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hinter dem Zaun</t>
+          <t xml:space="preserve">Ein Gespräch im Wald · Die Wahl · Morgengrauen · Die letzte Nacht</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tras la cerca</t>
+          <t xml:space="preserve">Conversación en el bosque · La elección · El alba · La última noche</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Além da cerca</t>
+          <t xml:space="preserve">Conversa na floresta · A escolha · A aurora · A última noite</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derrière la clôture</t>
+          <t xml:space="preserve">Une conversation dans la forêt · Le choix · L’aube · La dernière nuit</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oltre lo steccato</t>
+          <t xml:space="preserve">Colloquio nel bosco · La scelta · L’alba · L’ultima notte</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Za plotem</t>
+          <t xml:space="preserve">Rozhovor v boru · Volba · Svítání · Poslední noc</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Za plotom</t>
+          <t xml:space="preserve">Rozhovor v bore · Voľba · Úsvit · Posledná noc</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">垣根の向こう</t>
+          <t xml:space="preserve">森での対話・選択・夜明け・最後の夜</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idziemy do domu, tato</t>
+          <t xml:space="preserve">Młody dąb</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -7624,52 +7624,52 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromir odchodzi w bór z Marysią.</t>
+          <t xml:space="preserve">Granica, żołądź zasadzony, Marysia wróciła.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Let’s Go Home, Papa</t>
+          <t xml:space="preserve">The Young Oak</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wir gehen nach Hause, Papa</t>
+          <t xml:space="preserve">Die junge Eiche</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vamos a casa, papá</t>
+          <t xml:space="preserve">El roble joven</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vamos para casa, papai</t>
+          <t xml:space="preserve">O carvalho jovem</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">On rentre à la maison, papa</t>
+          <t xml:space="preserve">Le jeune chêne</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andiamo a casa, papà</t>
+          <t xml:space="preserve">La giovane quercia</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jdeme domů, tati</t>
+          <t xml:space="preserve">Mladý dub</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ideme domov, ocko</t>
+          <t xml:space="preserve">Mladý dub</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">おうちに帰ろう、とうさん</t>
+          <t xml:space="preserve">若い樫</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las, którego nie ma</t>
+          <t xml:space="preserve">Z dziadkiem Maćkiem</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -7691,52 +7691,52 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pożar boru, Marysia wróciła.</t>
+          <t xml:space="preserve">Granica, żołądź, Marysia odchodzi z umarłymi.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Forest That Is No More</t>
+          <t xml:space="preserve">With Grandfather Maciek</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Der Wald, den es nicht mehr gibt</t>
+          <t xml:space="preserve">Mit Großvater Maciek</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El bosque que ya no existe</t>
+          <t xml:space="preserve">Con el abuelo Maciek</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A floresta que já não existe</t>
+          <t xml:space="preserve">Com o avô Maciek</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La forêt qui n’est plus</t>
+          <t xml:space="preserve">Avec grand-père Maciek</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il bosco che non c’è più</t>
+          <t xml:space="preserve">Con nonno Maciek</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les, který už není</t>
+          <t xml:space="preserve">S dědečkem Maćkem</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les, ktorý už nie je</t>
+          <t xml:space="preserve">S dedkom Maćkom</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">もうない森</t>
+          <t xml:space="preserve">マチェクじいさんと共に</t>
         </is>
       </c>
     </row>
@@ -7748,67 +7748,402 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Słowo za słowo</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granica bez żołędzia, Marysia wróciła.</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Word for a Word</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wort um Wort</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Palabra por palabra</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Palavra por palavra</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parole contre parole</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parola per parola</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slovo za slovo</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slovo za slovo</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">言葉には言葉を</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakończenia</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jedno dziecko na pokolenie</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granica bez żołędzia, bez Marysi.</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One Child a Generation</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ein Kind pro Generation</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un niño por generación</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uma criança por geração</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un enfant par génération</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un bambino per generazione</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jedno dítě za pokolení</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jedno dieťa za pokolenie</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一世代に一人の子</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakończenia</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Za płotem</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaromir zostaje Panem Lasu, Marysia wróciła.</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyond the Fence</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hinter dem Zaun</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tras la cerca</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Além da cerca</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Derrière la clôture</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oltre lo steccato</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Za plotem</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Za plotom</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">垣根の向こう</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakończenia</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idziemy do domu, tato</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaromir odchodzi w bór z Marysią.</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Let’s Go Home, Papa</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wir gehen nach Hause, Papa</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vamos a casa, papá</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vamos para casa, papai</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On rentre à la maison, papa</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andiamo a casa, papà</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jdeme domů, tati</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ideme domov, ocko</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">おうちに帰ろう、とうさん</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakończenia</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las, którego nie ma</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tłumaczyć</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pożar boru, Marysia wróciła.</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Forest That Is No More</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Wald, den es nicht mehr gibt</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El bosque que ya no existe</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A floresta que já não existe</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La forêt qui n’est plus</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Il bosco che non c’è più</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les, který už není</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les, ktorý už nie je</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">もうない森</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakończenia</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ciepły popiół</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">tłumaczyć</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Pożar boru, bez Marysi.</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Warm Ashes</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Warme Asche</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ceniza tibia</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cinza morna</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cendres tièdes</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="J120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cenere tiepida</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teplý popel</t>
         </is>
       </c>
-      <c r="L115" s="2" t="inlineStr">
+      <c r="L120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Teplý popol</t>
         </is>
       </c>
-      <c r="M115" s="2" t="inlineStr">
+      <c r="M120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">温かい灰</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M115"/>
+  <autoFilter ref="A1:M120"/>
 </worksheet>
 </file>
 
@@ -8210,133 +8545,210 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japoński (ja)</t>
+          <t xml:space="preserve">Imiona na -sia (Marysia, Jadwisia) w cs i sk</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Katakana wg wymowy, nie pisowni: ś, si, sz → シ; cz, ć → チ; rz, ż → ジ (Andrzej アンジェイ, Marzanna マジャンナ); ł → ワ-row (Dobrosław ドブロスワフ, Płanetnik プワネトニク); w → ヴ (ヤドヴィシャ, ブコヴィエツ); ó, u → ウ; ę/ą przed spółgłoską → エン/オン.</t>
+          <t xml:space="preserve">• Pisownia zostaje polska (Marysia, Jadwisia), inaczej niż przy „Staš”. Czeski i słowacki czytelnik widzi imię na -ia, więc odmieniamy je jak Maria, Julia (cs wzór růže, sk jak Mária).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Nazwy istot pozostawione po polsku (strzyga, licho, mamuny) zapisujemy katakaną bez tłumaczenia, a wyjaśnia je karta.</t>
+          <t xml:space="preserve">• cs: Marysia – Marysie – Marysii – Marysii – wołacz Marysio! – o Marysii – s Marysií. Lm.: Marysie, dop. Marysií (r18 „kilkanaście Marysi” → „tucet Marysií”). Jadwisia – Jadwisie – Jadwisii – Jadwisii – Jadwisio! – o Jadwisii – s Jadwisií.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Sufiksy: starcy dostają 〜じいさん (マチェクじいさん, スタシじいさん, ヴイチクじいさん), staruszki 〜ばあさん (マリアンナばあさん), nauczyciel 〜先生 (イグナツィ先生), kupiec 〜の旦那 (ウルバニャクの旦那), żona 〜のおかみさん. Nie mieszać kanji 爺 z hiraganą. Dzieci i rówieśników zostawiamy bez sufiksu (ヤロミル, ハンカ, アンテク), a dziecięce czułe formy tylko w dialogu.</t>
+          <t xml:space="preserve">• sk: Marysia – Marysie – Marysii – Marysiu – o Marysii – s Marysiou. Wołacz = mianownik („Marysia, poď!”). Lm.: Marysie, dop. Marysií. Jadwisia – Jadwisie – Jadwisii – Jadwisiu – o Jadwisii – s Jadwisiou.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Rodzina: 〜家 (スタシ家, コヴァルチク家).</t>
+          <t xml:space="preserve">• Dzierżawczość tylko dopełniaczem: cs „dřeváky Marysie”, „stužka Marysie”, „korále Jadwisie”; sk „dreváky Marysie”, „stužka Marysie”, „korálky Jadwisie”. Przymiotnik „Marysiin/Marysiina” jest gramatycznie poprawny, ale podwójne „ii” męczy oko, więc go nie używamy. Przy powtórzeniach lepiej „její/jej dřeváky/dreváky”.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Zwroty: 「おじいさん！」, 「とうさん」 (Marysia do ojca), 「マリシャ！」.</t>
+          <t xml:space="preserve">• Błędy do wyłapania: „Marysina/Marysiny/Marysine” (to przymiotnik od imienia „Marysa”), polskie końcówki „Marysi, Marysię, Marysią” w tekście cs/sk, czeski wołacz w sk („Marysio!” po słowacku nie istnieje).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Święta: Wigilia 聖夜 (nie クリスマス・イブ), rozdziały 第一章 itd.</t>
+          <t xml:space="preserve">• Zdanie wzorcowe cs: Hanka podala Marysii hrnek mléka. „Marysio, pij,“ řekla, a když dopila, posadila se s Marysií na práh. Dřeváky Marysie zůstaly v síni. Antek koupil Jadwisii korále; o Jadwisii se v Bukowci mluvilo jen dobře.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="0" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Zdanie wzorcowe sk: Hanka podala Marysii hrnček mlieka. „Marysia, pi,“ povedala, a keď dopila, sadla si s Marysiou na prah. Dreváky Marysie ostali v pitvore. Antek kúpil Jadwisii korálky; o Jadwisii sa v Bukowci hovorilo len dobre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Otwarte pytania do natywnych tłumaczy</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. cs/sk, odmiana Marysia/Jadwisia (-sia): wzór -ia (Marysie, Marysii, wołacz „Marysio!”) czy inny? Przymiotnik dzierżawczy „Marysiin” czy omówienie dopełniaczem? W słowniczku na razie stoi „Marysiny/Marysine”.</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japoński (ja)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Hasła do dopisania później (są w tekście, rzadziej): błędne ognie/ogniki z prologu, dziedzic, kożuch/kapota, drużba, szarwark, ruble srebrem.</t>
+          <t xml:space="preserve">• Katakana wg wymowy, nie pisowni: ś, si, sz → シ; cz, ć → チ; rz, ż → ジ (Andrzej アンジェイ, Marzanna マジャンナ); ł → ワ-row (Dobrosław ドブロスワフ, Płanetnik プワネトニク); w → ヴ (ヤドヴィシャ, ブコヴィエツ); ó, u → ウ; ę/ą przed spółgłoską → エン/オン.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Nazwy istot pozostawione po polsku (strzyga, licho, mamuny) zapisujemy katakaną bez tłumaczenia, a wyjaśnia je karta.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rozstrzygnięte przez autora</t>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Sufiksy: starcy dostają 〜じいさん (マチェクじいさん, スタシじいさん, ヴイチクじいさん), staruszki 〜ばあさん (マリアンナばあさん), nauczyciel 〜先生 (イグナツィ先生), kupiec 〜の旦那 (ウルバニャクの旦那), żona 〜のおかみさん. Nie mieszać kanji 爺 z hiraganą. Dzieci i rówieśników zostawiamy bez sufiksu (ヤロミル, ハンカ, アンテク), a dziecięce czułe formy tylko w dialogu.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• en „Mr Ignacy” (nie „Master”).</t>
+          <t xml:space="preserve">• Rodzina: 〜家 (スタシ家, コヴァルチク家).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• cs/sk „Staš” zamiast „Staś”.</t>
+          <t xml:space="preserve">• Zwroty: 「おじいさん！」, 「とうさん」 (Marysia do ojca), 「マリシャ！」.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• cs topielec = „utopec”.</t>
+          <t xml:space="preserve">• Święta: Wigilia 聖夜 (nie クリスマス・イブ), rozdziały 第一章 itd.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• es kapliczka = „humilladero”.</t>
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• sk „podhodenec” zostaje: podrzutek, dziecko podrzucone komuś, coś podrzuconego, obcego.</t>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Otwarte pytania do natywnych tłumaczy</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Dopisane hasła: Borowy, świta, gajowy, opłatek, kołacz.</t>
+          <t xml:space="preserve">1. cs: wołacz „Marysio!” (przyjęty) czy „Marysie!”?</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. pt: „hóstia de Natal” kojarzy się z hostią konsekrowaną — czy jest lepsze słowo na opłatek?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. es „terrateniente” (dziedzic), it „focaccia nuziale” (kołacz), de „Joppe” (kapota) — potwierdzić.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rozstrzygnięte przez autora</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• en „Mr Ignacy” (nie „Master”).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• cs/sk „Staš” zamiast „Staś”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• cs topielec = „utopec”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• es kapliczka = „humilladero”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• sk „podhodenec” zostaje: podrzutek, dziecko podrzucone komuś, coś podrzuconego, obcego.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Dopisane hasła: Borowy, świta, gajowy, opłatek, kołacz, błędne ognie, dziedzic, kożuch/kapota, drużba, ruble srebrem (szarwark pominięty — nie pada w tekście gry).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• cs/sk: Marysia i Jadwisia odmieniane jak imiona na -ia, dzierżawczość dopełniaczem („dřeváky Marysie”).</t>
         </is>
       </c>
     </row>

--- a/tools/Translations/slowniczek.xlsx
+++ b/tools/Translations/slowniczek.xlsx
@@ -2264,7 +2264,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Właściciel majątku i wsi (szlachcic z dworu); w tekście nie pojawia się osobiście. Prolog: oddaje pustki pod karczunek za niski czynsz; r4: sprzedał Urbaniakowi wyrąb; r11: „Jaśnie pan dziedzic zarządza obławę”, płaci za skórę wilka. „Jaśnie pan” = uniżona formuła chłopa lub sługi: en „His Lordship the squire”, de „der gnädige Herr”, cs/sk „milostpán”, ja 地主様. „Dwór” (strzelcy z dworu, dworska stodoła): en the manor, de der Gutshof, cs panský dvůr, sk kaštieľ. Bez współczesnych słów typu „właściciel ziemski”.</t>
+          <t xml:space="preserve">Właściciel majątku i wsi (szlachcic z dworu); w tekście nie pojawia się osobiście. Prolog: oddaje pustki pod karczunek za niski czynsz; r4: sprzedał Urbaniakowi wyrąb; r11: „Jaśnie pan dziedzic zarządza obławę”, płaci za skórę wilka. „Jaśnie pan” = uniżona formuła chłopa lub sługi: en „His Lordship the squire”, de „der gnädige Herr”, cs/sk „milostpán”, ja 地主様. „Dwór” (strzelcy z dworu, dworska stodoła): en the manor, de der Gutshof, cs panský dvůr, sk kaštieľ. Bez współczesnych słów typu „właściciel ziemski”. es: „el señor” w ustach postaci i w zwrotach, w narracji „el señor de la finca”; „terrateniente” tylko tam, gdzie narrator opisuje stosunki własnościowe (termin opisowy, z odcieniem krytycznym); „hacendado” brzmi latynoamerykańsko.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">el terrateniente</t>
+          <t xml:space="preserve">el señor</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kożuch: okrycie z owczej skóry, wełną do środka. Motyw „kożuch wywrócony włosiem na wierzch” (starzec / Pan Lasu r2, r9, r16, r20; Jaromir r3) oddać dosłownie: en „a sheepskin turned fleece-out”, de „mit dem Fell nach außen”, cs „kožich obrácený srstí ven”, sk „kožuch obrátený srsťou von”. Kapota: sukienne okrycie wierzchnie z podszewką (r9 kapota Franka „podszewką na wierzch”, r16 i r18 Jaromira „szwami na wierzch”) — zwykły wyraz na płaszcz lub kurtkę, bez egzotyzmu. To dwie różne rzeczy, nie mieszać. Sukmana (prolog, r3) — tak samo zwykły wyraz na chłopskie okrycie z grubego sukna. Uwaga: „tęczowy kożuch” na wodzie (r16) to warstwa na powierzchni (en film, de Schicht, cs povlak), nie ubranie.</t>
+          <t xml:space="preserve">Kożuch: okrycie z owczej skóry, wełną do środka. Motyw „kożuch wywrócony włosiem na wierzch” (starzec / Pan Lasu r2, r9, r16, r20; Jaromir r3) oddać dosłownie: en „a sheepskin turned fleece-out”, de „mit dem Fell nach außen”, cs „kožich obrácený srstí ven”, sk „kožuch obrátený srsťou von”. Kapota: sukienne okrycie wierzchnie z podszewką (r9 kapota Franka „podszewką na wierzch”, r16 i r18 Jaromira „szwami na wierzch”) — zwykły wyraz na płaszcz lub kurtkę, bez egzotyzmu. To dwie różne rzeczy, nie mieszać. Sukmana (prolog, r3) — tak samo zwykły wyraz na chłopskie okrycie z grubego sukna. Uwaga: „tęczowy kożuch” na wodzie (r16) to warstwa na powierzchni (en film, de Schicht, cs povlak), nie ubranie. de: kapota to długie okrycie — „langer Bauernrock” / „langer Rock”, nie „Joppe” (krótka kurtka bawarska).</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schafspelz / Joppe</t>
+          <t xml:space="preserve">Schafspelz / langer Bauernrock</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cienki biały wafel łamany w Wigilię; kładziony na talerzu dla wędrowca. W tekście też porównanie „cienki jak opłatek” (lód) — oddać naturalnym porównaniem (en „wafer-thin”, de „hauchdünn wie eine Oblate”).</t>
+          <t xml:space="preserve">Cienki biały wafel łamany w Wigilię; kładziony na talerzu dla wędrowca. W tekście też porównanie „cienki jak opłatek” (lód) — oddać naturalnym porównaniem (en „wafer-thin”, de „hauchdünn wie eine Oblate”). pt: „obreia” (niekonsekrowany wafel), nie „hóstia” (Eucharystia); przy pierwszym wystąpieniu można „opłatek (obreia de Natal)”, dalej „obreia”. Wariant docelowy: brazylijski.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a hóstia de Natal</t>
+          <t xml:space="preserve">obreia de Natal</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weselny placek drożdżowy (Hanka piecze je z miodem); poczęstunek dla starca w noc oczepin.</t>
+          <t xml:space="preserve">Weselny placek drożdżowy, słodki (Hanka piecze je z miodem); poczęstunek dla starca w noc oczepin. it: nie „focaccia” (płaski wytrawny chleb) ani „torta nuziale” (nowoczesny tort); przy pierwszym wystąpieniu można „kołacz, il pane nuziale”.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">focaccia nuziale</t>
+          <t xml:space="preserve">pane dolce nuziale</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -8664,77 +8664,77 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otwarte pytania do natywnych tłumaczy</t>
+          <t xml:space="preserve">Rozstrzygnięte przez autora</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. cs: wołacz „Marysio!” (przyjęty) czy „Marysie!”?</t>
+          <t xml:space="preserve">• en „Mr Ignacy” (nie „Master”).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. pt: „hóstia de Natal” kojarzy się z hostią konsekrowaną — czy jest lepsze słowo na opłatek?</t>
+          <t xml:space="preserve">• cs/sk „Staš” zamiast „Staś”.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. es „terrateniente” (dziedzic), it „focaccia nuziale” (kołacz), de „Joppe” (kapota) — potwierdzić.</t>
+          <t xml:space="preserve">• cs topielec = „utopec”.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• es kapliczka = „humilladero”.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rozstrzygnięte przez autora</t>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• sk „podhodenec” zostaje: podrzutek, dziecko podrzucone komuś, coś podrzuconego, obcego.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• en „Mr Ignacy” (nie „Master”).</t>
+          <t xml:space="preserve">• cs wołacz „Marysio!” — polskie imię na -a odmienia się jak czeskie żeńskie (Jana → Jano, Maria → Mario); „Marysie!” tylko przy sczeszczonym mianowniku, czego nie chcemy.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• cs/sk „Staš” zamiast „Staś”.</t>
+          <t xml:space="preserve">• pt opłatek = „obreia de Natal” (nie „hóstia”, kojarzy się z Eucharystią).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• cs topielec = „utopec”.</t>
+          <t xml:space="preserve">• es dziedzic = „el señor” (w narracji „el señor de la finca”), nie „terrateniente”.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• es kapliczka = „humilladero”.</t>
+          <t xml:space="preserve">• it kołacz = „pane dolce nuziale” (nie „focaccia”, nie „torta nuziale”).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• sk „podhodenec” zostaje: podrzutek, dziecko podrzucone komuś, coś podrzuconego, obcego.</t>
+          <t xml:space="preserve">• de kapota = „langer Bauernrock” (nie „Joppe” — to krótka kurtka).</t>
         </is>
       </c>
     </row>

--- a/tools/Translations/slowniczek.xlsx
+++ b/tools/Translations/slowniczek.xlsx
@@ -6016,7 +6016,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cienki biały wafel łamany w Wigilię; kładziony na talerzu dla wędrowca. W tekście też porównanie „cienki jak opłatek” (lód) — oddać naturalnym porównaniem (en „wafer-thin”, de „hauchdünn wie eine Oblate”). pt: „obreia” (niekonsekrowany wafel), nie „hóstia” (Eucharystia); przy pierwszym wystąpieniu można „opłatek (obreia de Natal)”, dalej „obreia”. Wariant docelowy: brazylijski.</t>
+          <t xml:space="preserve">Cienki biały wafel łamany w Wigilię; kładziony na talerzu dla wędrowca. W tekście też porównanie „cienki jak opłatek” (lód) — oddać naturalnym porównaniem (en „wafer-thin”, de „hauchdünn wie eine Oblate”). pt: „obreia” (niekonsekrowany wafel), nie „hóstia” (Eucharystia); przy pierwszym wystąpieniu można „opłatek (obreia de Natal)”, dalej „obreia”. Wariant docelowy: brazylijski. it: „cialda” (neutralny wafel; „ostia” i „oblata” kojarzą się z liturgią), porównanie „sottile come una cialda”. fr: polskie słowo „l’opłatek” (jedyny przedmiot, który zostaje po polsku — „hostie” = Eucharystia, „oublie” = dziś słodki rożek); przy pierwszym wystąpieniu „l’opłatek, la fine galette de pain azyme qu’on rompt à la veille de Noël”, porównanie z lodem „mince comme une feuille”.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">l’hostie de Noël</t>
+          <t xml:space="preserve">l’opłatek</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">l’ostia di Natale</t>
+          <t xml:space="preserve">la cialda di Natale</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -8720,33 +8720,40 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• es dziedzic = „el señor” (w narracji „el señor de la finca”), nie „terrateniente”.</t>
+          <t xml:space="preserve">• it opłatek = „la cialda di Natale”; fr opłatek = polskie „l’opłatek” z objaśnieniem przy pierwszym wystąpieniu (jedyny przedmiot, który zostaje po polsku).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• it kołacz = „pane dolce nuziale” (nie „focaccia”, nie „torta nuziale”).</t>
+          <t xml:space="preserve">• es dziedzic = „el señor” (w narracji „el señor de la finca”), nie „terrateniente”.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• de kapota = „langer Bauernrock” (nie „Joppe” — to krótka kurtka).</t>
+          <t xml:space="preserve">• it kołacz = „pane dolce nuziale” (nie „focaccia”, nie „torta nuziale”).</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Dopisane hasła: Borowy, świta, gajowy, opłatek, kołacz, błędne ognie, dziedzic, kożuch/kapota, drużba, ruble srebrem (szarwark pominięty — nie pada w tekście gry).</t>
+          <t xml:space="preserve">• de kapota = „langer Bauernrock” (nie „Joppe” — to krótka kurtka).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Dopisane hasła: Borowy, świta, gajowy, opłatek, kołacz, błędne ognie, dziedzic, kożuch/kapota, drużba, ruble srebrem (szarwark pominięty — nie pada w tekście gry).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">• cs/sk: Marysia i Jadwisia odmieniane jak imiona na -ia, dzierżawczość dopełniaczem („dřeváky Marysie”).</t>
         </is>
